--- a/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.9322033898305085</v>
+        <v>-0.2789317507418397</v>
       </c>
       <c r="H2">
-        <v>-0.9322033898305085</v>
+        <v>-0.2789317507418397</v>
       </c>
       <c r="I2">
-        <v>-0.9830508474576273</v>
+        <v>-0.008902077151335312</v>
       </c>
       <c r="J2">
-        <v>-0.9830508474576273</v>
+        <v>-0.008902077151335312</v>
       </c>
       <c r="K2">
-        <v>-0.118</v>
+        <v>-0.021</v>
       </c>
       <c r="L2">
-        <v>-1</v>
+        <v>-0.06231454005934718</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.464</v>
+        <v>0.169</v>
       </c>
       <c r="V2">
-        <v>0.032</v>
+        <v>0.0122463768115942</v>
+      </c>
+      <c r="W2">
+        <v>-0.003106508875739645</v>
       </c>
       <c r="X2">
-        <v>0.08964107456213496</v>
+        <v>0.1532257693750738</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1563322782508135</v>
+      </c>
+      <c r="Z2">
+        <v>0.05109931766489766</v>
+      </c>
+      <c r="AA2">
+        <v>-0.0004548900682335103</v>
       </c>
       <c r="AB2">
-        <v>0.0886409045541767</v>
+        <v>0.1513634691933604</v>
+      </c>
+      <c r="AC2">
+        <v>-0.151818359261594</v>
       </c>
       <c r="AD2">
-        <v>0.299</v>
+        <v>0.305</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.299</v>
+        <v>0.305</v>
       </c>
       <c r="AG2">
-        <v>-0.165</v>
+        <v>0.136</v>
       </c>
       <c r="AH2">
-        <v>0.02020406784242178</v>
+        <v>0.02162353775257001</v>
       </c>
       <c r="AI2">
-        <v>0.04235727440147329</v>
+        <v>0.04891740176423417</v>
       </c>
       <c r="AJ2">
-        <v>-0.01151028950122079</v>
+        <v>0.009758897818599311</v>
       </c>
       <c r="AK2">
-        <v>-0.02501895375284307</v>
+        <v>0.02242004615891856</v>
       </c>
       <c r="AL2">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="AN2">
-        <v>-3.082474226804123</v>
+        <v>7.439024390243902</v>
       </c>
       <c r="AO2">
-        <v>-8.285714285714286</v>
+        <v>-0.1363636363636364</v>
       </c>
       <c r="AP2">
-        <v>1.701030927835052</v>
+        <v>3.317073170731707</v>
       </c>
       <c r="AQ2">
-        <v>-8.285714285714286</v>
+        <v>-0.1363636363636364</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.9322033898305085</v>
+        <v>-0.2789317507418397</v>
       </c>
       <c r="H3">
-        <v>-0.9322033898305085</v>
+        <v>-0.2789317507418397</v>
       </c>
       <c r="I3">
-        <v>-0.9830508474576273</v>
+        <v>-0.008902077151335312</v>
       </c>
       <c r="J3">
-        <v>-0.9830508474576273</v>
+        <v>-0.008902077151335312</v>
       </c>
       <c r="K3">
-        <v>-0.118</v>
+        <v>-0.021</v>
       </c>
       <c r="L3">
-        <v>-1</v>
+        <v>-0.06231454005934718</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.464</v>
+        <v>0.169</v>
       </c>
       <c r="V3">
-        <v>0.032</v>
+        <v>0.0122463768115942</v>
+      </c>
+      <c r="W3">
+        <v>-0.003106508875739645</v>
       </c>
       <c r="X3">
-        <v>0.08964107456213496</v>
+        <v>0.1532257693750738</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1563322782508135</v>
+      </c>
+      <c r="Z3">
+        <v>0.05109931766489766</v>
+      </c>
+      <c r="AA3">
+        <v>-0.0004548900682335103</v>
       </c>
       <c r="AB3">
-        <v>0.0886409045541767</v>
+        <v>0.1513634691933604</v>
+      </c>
+      <c r="AC3">
+        <v>-0.151818359261594</v>
       </c>
       <c r="AD3">
-        <v>0.299</v>
+        <v>0.305</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.299</v>
+        <v>0.305</v>
       </c>
       <c r="AG3">
-        <v>-0.165</v>
+        <v>0.136</v>
       </c>
       <c r="AH3">
-        <v>0.02020406784242178</v>
+        <v>0.02162353775257001</v>
       </c>
       <c r="AI3">
-        <v>0.04235727440147329</v>
+        <v>0.04891740176423417</v>
       </c>
       <c r="AJ3">
-        <v>-0.01151028950122079</v>
+        <v>0.009758897818599311</v>
       </c>
       <c r="AK3">
-        <v>-0.02501895375284307</v>
+        <v>0.02242004615891856</v>
       </c>
       <c r="AL3">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="AN3">
-        <v>-3.082474226804123</v>
+        <v>7.439024390243902</v>
       </c>
       <c r="AO3">
-        <v>-8.285714285714286</v>
+        <v>-0.1363636363636364</v>
       </c>
       <c r="AP3">
-        <v>1.701030927835052</v>
+        <v>3.317073170731707</v>
       </c>
       <c r="AQ3">
-        <v>-8.285714285714286</v>
+        <v>-0.1363636363636364</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bul_slyg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,113 +589,122 @@
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.255</v>
+      </c>
+      <c r="E2">
+        <v>0.6459999999999999</v>
+      </c>
       <c r="G2">
-        <v>-0.2789317507418397</v>
+        <v>0.1700607305798109</v>
       </c>
       <c r="H2">
-        <v>-0.2789317507418397</v>
+        <v>0.1700607305798109</v>
       </c>
       <c r="I2">
-        <v>-0.008902077151335312</v>
+        <v>0.2527872616853491</v>
       </c>
       <c r="J2">
-        <v>-0.008902077151335312</v>
+        <v>0.2325798849024771</v>
       </c>
       <c r="K2">
-        <v>-0.021</v>
+        <v>13.515</v>
       </c>
       <c r="L2">
-        <v>-0.06231454005934718</v>
+        <v>0.2041725836178506</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.005047832281701608</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.1834998150203478</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.005047832281701608</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.1834998150203478</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.169</v>
+        <v>19.718</v>
       </c>
       <c r="V2">
-        <v>0.0122463768115942</v>
+        <v>0.04013433747201302</v>
       </c>
       <c r="W2">
-        <v>-0.003106508875739645</v>
+        <v>0.1650107417588764</v>
       </c>
       <c r="X2">
-        <v>0.1532257693750738</v>
+        <v>0.1291013815292553</v>
       </c>
       <c r="Y2">
-        <v>-0.1563322782508135</v>
+        <v>0.03590936022962107</v>
       </c>
       <c r="Z2">
-        <v>0.05109931766489766</v>
+        <v>2.111047327465238</v>
       </c>
       <c r="AA2">
-        <v>-0.0004548900682335103</v>
+        <v>0.2603586106770141</v>
       </c>
       <c r="AB2">
-        <v>0.1513634691933604</v>
+        <v>0.1276983938988253</v>
       </c>
       <c r="AC2">
-        <v>-0.151818359261594</v>
+        <v>0.1326602167781888</v>
       </c>
       <c r="AD2">
-        <v>0.305</v>
+        <v>1.856</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.305</v>
+        <v>1.856</v>
       </c>
       <c r="AG2">
-        <v>0.136</v>
+        <v>-17.862</v>
       </c>
       <c r="AH2">
-        <v>0.02162353775257001</v>
+        <v>0.003763514993227295</v>
       </c>
       <c r="AI2">
-        <v>0.04891740176423417</v>
+        <v>0.03072033898305084</v>
       </c>
       <c r="AJ2">
-        <v>0.009758897818599311</v>
+        <v>-0.03772827698663817</v>
       </c>
       <c r="AK2">
-        <v>0.02242004615891856</v>
+        <v>-0.4388913460120891</v>
       </c>
       <c r="AL2">
-        <v>0.022</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.022</v>
+        <v>0.09799999999999999</v>
       </c>
       <c r="AN2">
-        <v>7.439024390243902</v>
+        <v>0.107469600463231</v>
       </c>
       <c r="AO2">
-        <v>-0.1363636363636364</v>
+        <v>170.7448979591837</v>
       </c>
       <c r="AP2">
-        <v>3.317073170731707</v>
+        <v>-1.034279096699479</v>
       </c>
       <c r="AQ2">
-        <v>-0.1363636363636364</v>
+        <v>170.7448979591837</v>
       </c>
     </row>
     <row r="3">
@@ -704,121 +715,9027 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Shelly Group AD (BUL:SLYG)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.255</v>
+      </c>
+      <c r="E3">
+        <v>0.6459999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.1732522796352584</v>
+      </c>
+      <c r="H3">
+        <v>0.1732522796352584</v>
+      </c>
+      <c r="I3">
+        <v>0.2583586626139818</v>
+      </c>
+      <c r="J3">
+        <v>0.2170531727269316</v>
+      </c>
+      <c r="K3">
+        <v>13.8</v>
+      </c>
+      <c r="L3">
+        <v>0.209726443768997</v>
+      </c>
+      <c r="M3">
+        <v>2.48</v>
+      </c>
+      <c r="N3">
+        <v>0.005168820341809087</v>
+      </c>
+      <c r="O3">
+        <v>0.1797101449275362</v>
+      </c>
+      <c r="P3">
+        <v>2.48</v>
+      </c>
+      <c r="Q3">
+        <v>0.005168820341809087</v>
+      </c>
+      <c r="R3">
+        <v>0.1797101449275362</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>19.1</v>
+      </c>
+      <c r="V3">
+        <v>0.03980825343893289</v>
+      </c>
+      <c r="W3">
+        <v>0.3780821917808219</v>
+      </c>
+      <c r="X3">
+        <v>0.1276017784282895</v>
+      </c>
+      <c r="Y3">
+        <v>0.2504804133525325</v>
+      </c>
+      <c r="Z3">
+        <v>2.601818900751284</v>
+      </c>
+      <c r="AA3">
+        <v>0.5647330472689639</v>
+      </c>
+      <c r="AB3">
+        <v>0.1273955549604067</v>
+      </c>
+      <c r="AC3">
+        <v>0.4373374923085572</v>
+      </c>
+      <c r="AD3">
+        <v>1.39</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.39</v>
+      </c>
+      <c r="AG3">
+        <v>-17.71</v>
+      </c>
+      <c r="AH3">
+        <v>0.002888671834410524</v>
+      </c>
+      <c r="AI3">
+        <v>0.02618195517046525</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.03832586725529659</v>
+      </c>
+      <c r="AK3">
+        <v>-0.5210355987055016</v>
+      </c>
+      <c r="AL3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AM3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>0.07942857142857142</v>
+      </c>
+      <c r="AO3">
+        <v>239.4366197183099</v>
+      </c>
+      <c r="AP3">
+        <v>-1.012</v>
+      </c>
+      <c r="AQ3">
+        <v>239.4366197183099</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Biodit AD (BUL:BDT)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Electronics (General)</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-0.3629441624365482</v>
+      </c>
+      <c r="H4">
+        <v>-0.3629441624365482</v>
+      </c>
+      <c r="I4">
+        <v>-0.6776649746192893</v>
+      </c>
+      <c r="J4">
+        <v>-0.6776649746192893</v>
+      </c>
+      <c r="K4">
+        <v>-0.285</v>
+      </c>
+      <c r="L4">
+        <v>-0.7233502538071065</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.618</v>
+      </c>
+      <c r="V4">
+        <v>0.05373913043478261</v>
+      </c>
+      <c r="W4">
+        <v>-0.04806070826306914</v>
+      </c>
+      <c r="X4">
+        <v>0.1306009846302212</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1786616928932903</v>
+      </c>
+      <c r="Z4">
+        <v>0.06495219254863173</v>
+      </c>
+      <c r="AA4">
+        <v>-0.04401582591493571</v>
+      </c>
+      <c r="AB4">
+        <v>0.1280012328372438</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1720170587521795</v>
+      </c>
+      <c r="AD4">
+        <v>0.466</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.466</v>
+      </c>
+      <c r="AG4">
+        <v>-0.152</v>
+      </c>
+      <c r="AH4">
+        <v>0.03894367374226977</v>
+      </c>
+      <c r="AI4">
+        <v>0.06360906360906361</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.01339443073669369</v>
+      </c>
+      <c r="AK4">
+        <v>-0.02265951103160405</v>
+      </c>
+      <c r="AL4">
+        <v>0.027</v>
+      </c>
+      <c r="AM4">
+        <v>0.027</v>
+      </c>
+      <c r="AN4">
+        <v>-2.026086956521739</v>
+      </c>
+      <c r="AO4">
+        <v>-9.888888888888889</v>
+      </c>
+      <c r="AP4">
+        <v>0.6608695652173912</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.888888888888889</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shelly Group AD (BUL:SLYG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUL:SLYG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>239.43661971831</v>
+      </c>
+      <c r="F2">
+        <v>11.0196756048638</v>
+      </c>
+      <c r="G2">
+        <v>0.0794285714285714</v>
+      </c>
+      <c r="H2">
+        <v>1.92476</v>
+      </c>
+      <c r="I2">
+        <v>0.00288867183441052</v>
+      </c>
+      <c r="J2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K2">
+        <v>479.8</v>
+      </c>
+      <c r="L2">
+        <v>449.999139041583</v>
+      </c>
+      <c r="M2">
+        <v>462.09</v>
+      </c>
+      <c r="N2">
+        <v>464.582439041583</v>
+      </c>
+      <c r="O2">
+        <v>1.39</v>
+      </c>
+      <c r="P2">
+        <v>33.6833</v>
+      </c>
+      <c r="Q2">
+        <v>0.127395554960407</v>
+      </c>
+      <c r="R2">
+        <v>0.12692024853137</v>
+      </c>
+      <c r="S2">
+        <v>0.05621136798909</v>
+      </c>
+      <c r="T2">
+        <v>0.04122</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.127601778428289</v>
+      </c>
+      <c r="X2">
+        <v>0.133370804872441</v>
+      </c>
+      <c r="Y2">
+        <v>1.2799823807528</v>
+      </c>
+      <c r="Z2">
+        <v>1.36313670866498</v>
+      </c>
+      <c r="AA2">
+        <v>1.39</v>
+      </c>
+      <c r="AB2">
+        <v>0.06245707554343334</v>
+      </c>
+      <c r="AC2">
+        <v>239.4366197183099</v>
+      </c>
+      <c r="AD2">
+        <v>1.39</v>
+      </c>
+      <c r="AE2">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>0.5</v>
+      </c>
+      <c r="AG2">
+        <v>17.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>479.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.06937734437880483</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.1</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.539999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>1.39</v>
+      </c>
+      <c r="AT2">
+        <v>19.1</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1273708444424672</v>
+      </c>
+      <c r="C2">
+        <v>481.318919209324</v>
+      </c>
+      <c r="D2">
+        <v>462.218919209324</v>
+      </c>
+      <c r="E2">
+        <v>-1.39</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>19.1</v>
+      </c>
+      <c r="H2">
+        <v>479.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>17.5</v>
+      </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
+      <c r="L2">
+        <v>17</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>17</v>
+      </c>
+      <c r="O2">
+        <v>1.7</v>
+      </c>
+      <c r="P2">
+        <v>15.3</v>
+      </c>
+      <c r="Q2">
+        <v>15.8</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1273708444424672</v>
+      </c>
+      <c r="T2">
+        <v>1.276653715063877</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.1</v>
+      </c>
+      <c r="W2">
+        <v>0.04023</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1272965735980247</v>
+      </c>
+      <c r="C3">
+        <v>476.8949369337197</v>
+      </c>
+      <c r="D3">
+        <v>462.6068369337196</v>
+      </c>
+      <c r="E3">
+        <v>3.421900000000001</v>
+      </c>
+      <c r="F3">
+        <v>4.811900000000001</v>
+      </c>
       <c r="G3">
-        <v>-0.2789317507418397</v>
+        <v>19.1</v>
       </c>
       <c r="H3">
-        <v>-0.2789317507418397</v>
+        <v>479.8</v>
       </c>
       <c r="I3">
-        <v>-0.008902077151335312</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.008902077151335312</v>
+        <v>17.5</v>
       </c>
       <c r="K3">
-        <v>-0.021</v>
+        <v>0.5</v>
       </c>
       <c r="L3">
-        <v>-0.06231454005934718</v>
+        <v>17</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.21509193</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>16.78490807</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.678490807</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>15.106417263</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>15.606417263</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1281760339373987</v>
+      </c>
+      <c r="T3">
+        <v>1.288259657928094</v>
       </c>
       <c r="U3">
-        <v>0.169</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0.0122463768115942</v>
+        <v>0.1</v>
       </c>
       <c r="W3">
-        <v>-0.003106508875739645</v>
-      </c>
-      <c r="X3">
-        <v>0.1532257693750738</v>
+        <v>0.04023</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.1563322782508135</v>
+        <v>79.03597313018669</v>
       </c>
       <c r="Z3">
-        <v>0.05109931766489766</v>
-      </c>
-      <c r="AA3">
-        <v>-0.0004548900682335103</v>
-      </c>
-      <c r="AB3">
-        <v>0.1513634691933604</v>
-      </c>
-      <c r="AC3">
-        <v>-0.151818359261594</v>
-      </c>
-      <c r="AD3">
-        <v>0.305</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.305</v>
-      </c>
-      <c r="AG3">
-        <v>0.136</v>
-      </c>
-      <c r="AH3">
-        <v>0.02162353775257001</v>
-      </c>
-      <c r="AI3">
-        <v>0.04891740176423417</v>
-      </c>
-      <c r="AJ3">
-        <v>0.009758897818599311</v>
-      </c>
-      <c r="AK3">
-        <v>0.02242004615891856</v>
-      </c>
-      <c r="AL3">
-        <v>0.022</v>
-      </c>
-      <c r="AM3">
-        <v>0.022</v>
-      </c>
-      <c r="AN3">
-        <v>7.439024390243902</v>
-      </c>
-      <c r="AO3">
-        <v>-0.1363636363636364</v>
-      </c>
-      <c r="AP3">
-        <v>3.317073170731707</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.1363636363636364</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1272223027535823</v>
+      </c>
+      <c r="C4">
+        <v>472.4716063257617</v>
+      </c>
+      <c r="D4">
+        <v>462.9954063257617</v>
+      </c>
+      <c r="E4">
+        <v>8.2338</v>
+      </c>
+      <c r="F4">
+        <v>9.623800000000001</v>
+      </c>
+      <c r="G4">
+        <v>19.1</v>
+      </c>
+      <c r="H4">
+        <v>479.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>17.5</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>17</v>
+      </c>
+      <c r="M4">
+        <v>0.4301838600000001</v>
+      </c>
+      <c r="N4">
+        <v>16.56981614</v>
+      </c>
+      <c r="O4">
+        <v>1.656981614</v>
+      </c>
+      <c r="P4">
+        <v>14.912834526</v>
+      </c>
+      <c r="Q4">
+        <v>15.412834526</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1289976558710023</v>
+      </c>
+      <c r="T4">
+        <v>1.300102456769132</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.1</v>
+      </c>
+      <c r="W4">
+        <v>0.04023</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>39.51798656509335</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1271480319091398</v>
+      </c>
+      <c r="C5">
+        <v>468.0489290289475</v>
+      </c>
+      <c r="D5">
+        <v>463.3846290289475</v>
+      </c>
+      <c r="E5">
+        <v>13.0457</v>
+      </c>
+      <c r="F5">
+        <v>14.4357</v>
+      </c>
+      <c r="G5">
+        <v>19.1</v>
+      </c>
+      <c r="H5">
+        <v>479.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>17.5</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>17</v>
+      </c>
+      <c r="M5">
+        <v>0.64527579</v>
+      </c>
+      <c r="N5">
+        <v>16.35472421</v>
+      </c>
+      <c r="O5">
+        <v>1.635472421</v>
+      </c>
+      <c r="P5">
+        <v>14.719251789</v>
+      </c>
+      <c r="Q5">
+        <v>15.219251789</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1298362184630307</v>
+      </c>
+      <c r="T5">
+        <v>1.312189437029573</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.1</v>
+      </c>
+      <c r="W5">
+        <v>0.04023</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>26.3453243767289</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1270737610646973</v>
+      </c>
+      <c r="C6">
+        <v>463.6269066923043</v>
+      </c>
+      <c r="D6">
+        <v>463.7745066923042</v>
+      </c>
+      <c r="E6">
+        <v>17.8576</v>
+      </c>
+      <c r="F6">
+        <v>19.2476</v>
+      </c>
+      <c r="G6">
+        <v>19.1</v>
+      </c>
+      <c r="H6">
+        <v>479.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>17.5</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>0.8603677200000002</v>
+      </c>
+      <c r="N6">
+        <v>16.13963228</v>
+      </c>
+      <c r="O6">
+        <v>1.613963228</v>
+      </c>
+      <c r="P6">
+        <v>14.525669052</v>
+      </c>
+      <c r="Q6">
+        <v>15.025669052</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1306922511090597</v>
+      </c>
+      <c r="T6">
+        <v>1.324528229378773</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.1</v>
+      </c>
+      <c r="W6">
+        <v>0.04023</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>19.75899328254667</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1269994902202548</v>
+      </c>
+      <c r="C7">
+        <v>459.2055409704155</v>
+      </c>
+      <c r="D7">
+        <v>464.1650409704155</v>
+      </c>
+      <c r="E7">
+        <v>22.6695</v>
+      </c>
+      <c r="F7">
+        <v>24.0595</v>
+      </c>
+      <c r="G7">
+        <v>19.1</v>
+      </c>
+      <c r="H7">
+        <v>479.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>17.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>1.07545965</v>
+      </c>
+      <c r="N7">
+        <v>15.92454035</v>
+      </c>
+      <c r="O7">
+        <v>1.592454035</v>
+      </c>
+      <c r="P7">
+        <v>14.332086315</v>
+      </c>
+      <c r="Q7">
+        <v>14.832086315</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1315663054950051</v>
+      </c>
+      <c r="T7">
+        <v>1.337126785777429</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.1</v>
+      </c>
+      <c r="W7">
+        <v>0.04023</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>15.80719462603734</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1269252193758124</v>
+      </c>
+      <c r="C8">
+        <v>454.7848335234407</v>
+      </c>
+      <c r="D8">
+        <v>464.5562335234407</v>
+      </c>
+      <c r="E8">
+        <v>27.4814</v>
+      </c>
+      <c r="F8">
+        <v>28.8714</v>
+      </c>
+      <c r="G8">
+        <v>19.1</v>
+      </c>
+      <c r="H8">
+        <v>479.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>17.5</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>1.29055158</v>
+      </c>
+      <c r="N8">
+        <v>15.70944842</v>
+      </c>
+      <c r="O8">
+        <v>1.570944842</v>
+      </c>
+      <c r="P8">
+        <v>14.138503578</v>
+      </c>
+      <c r="Q8">
+        <v>14.638503578</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1324589567827791</v>
+      </c>
+      <c r="T8">
+        <v>1.349993396567547</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.1</v>
+      </c>
+      <c r="W8">
+        <v>0.04023</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>13.17266218836445</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1269202485313699</v>
+      </c>
+      <c r="C9">
+        <v>449.9991390415832</v>
+      </c>
+      <c r="D9">
+        <v>464.5824390415832</v>
+      </c>
+      <c r="E9">
+        <v>32.2933</v>
+      </c>
+      <c r="F9">
+        <v>33.6833</v>
+      </c>
+      <c r="G9">
+        <v>19.1</v>
+      </c>
+      <c r="H9">
+        <v>479.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>17.5</v>
+      </c>
+      <c r="K9">
+        <v>0.5</v>
+      </c>
+      <c r="L9">
+        <v>17</v>
+      </c>
+      <c r="M9">
+        <v>1.54269514</v>
+      </c>
+      <c r="N9">
+        <v>15.45730486</v>
+      </c>
+      <c r="O9">
+        <v>1.545730486</v>
+      </c>
+      <c r="P9">
+        <v>13.911574374</v>
+      </c>
+      <c r="Q9">
+        <v>14.411574374</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1333708048724408</v>
+      </c>
+      <c r="T9">
+        <v>1.363136708664979</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.1</v>
+      </c>
+      <c r="W9">
+        <v>0.04122</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.01967560486383</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1270142776869274</v>
+      </c>
+      <c r="C10">
+        <v>444.6920324199866</v>
+      </c>
+      <c r="D10">
+        <v>464.0872324199866</v>
+      </c>
+      <c r="E10">
+        <v>37.1052</v>
+      </c>
+      <c r="F10">
+        <v>38.4952</v>
+      </c>
+      <c r="G10">
+        <v>19.1</v>
+      </c>
+      <c r="H10">
+        <v>479.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>17.5</v>
+      </c>
+      <c r="K10">
+        <v>0.5</v>
+      </c>
+      <c r="L10">
+        <v>17</v>
+      </c>
+      <c r="M10">
+        <v>1.8477696</v>
+      </c>
+      <c r="N10">
+        <v>15.1522304</v>
+      </c>
+      <c r="O10">
+        <v>1.51522304</v>
+      </c>
+      <c r="P10">
+        <v>13.63700736</v>
+      </c>
+      <c r="Q10">
+        <v>14.13700736</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1343024757466603</v>
+      </c>
+      <c r="T10">
+        <v>1.376565744938442</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.1</v>
+      </c>
+      <c r="W10">
+        <v>0.0432</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>9.200281247185796</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.126969706842485</v>
+      </c>
+      <c r="C11">
+        <v>440.1147340829011</v>
+      </c>
+      <c r="D11">
+        <v>464.3218340829011</v>
+      </c>
+      <c r="E11">
+        <v>41.9171</v>
+      </c>
+      <c r="F11">
+        <v>43.3071</v>
+      </c>
+      <c r="G11">
+        <v>19.1</v>
+      </c>
+      <c r="H11">
+        <v>479.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>17.5</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <v>17</v>
+      </c>
+      <c r="M11">
+        <v>2.0787408</v>
+      </c>
+      <c r="N11">
+        <v>14.9212592</v>
+      </c>
+      <c r="O11">
+        <v>1.49212592</v>
+      </c>
+      <c r="P11">
+        <v>13.42913328</v>
+      </c>
+      <c r="Q11">
+        <v>13.92913328</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1352546229038296</v>
+      </c>
+      <c r="T11">
+        <v>1.390289924866266</v>
+      </c>
+      <c r="U11">
+        <v>0.048</v>
+      </c>
+      <c r="V11">
+        <v>0.1</v>
+      </c>
+      <c r="W11">
+        <v>0.0432</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.178027775276263</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1270601359980425</v>
+      </c>
+      <c r="C12">
+        <v>434.82710139919</v>
+      </c>
+      <c r="D12">
+        <v>463.84610139919</v>
+      </c>
+      <c r="E12">
+        <v>46.729</v>
+      </c>
+      <c r="F12">
+        <v>48.119</v>
+      </c>
+      <c r="G12">
+        <v>19.1</v>
+      </c>
+      <c r="H12">
+        <v>479.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>17.5</v>
+      </c>
+      <c r="K12">
+        <v>0.5</v>
+      </c>
+      <c r="L12">
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <v>2.3818905</v>
+      </c>
+      <c r="N12">
+        <v>14.6181095</v>
+      </c>
+      <c r="O12">
+        <v>1.46181095</v>
+      </c>
+      <c r="P12">
+        <v>13.15629855</v>
+      </c>
+      <c r="Q12">
+        <v>13.65629855</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1362279288867139</v>
+      </c>
+      <c r="T12">
+        <v>1.404319086570265</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.1</v>
+      </c>
+      <c r="W12">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.137187876604739</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1270290651536</v>
+      </c>
+      <c r="C13">
+        <v>430.1785499514697</v>
+      </c>
+      <c r="D13">
+        <v>464.0094499514697</v>
+      </c>
+      <c r="E13">
+        <v>51.5409</v>
+      </c>
+      <c r="F13">
+        <v>52.9309</v>
+      </c>
+      <c r="G13">
+        <v>19.1</v>
+      </c>
+      <c r="H13">
+        <v>479.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>17.5</v>
+      </c>
+      <c r="K13">
+        <v>0.5</v>
+      </c>
+      <c r="L13">
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <v>2.62007955</v>
+      </c>
+      <c r="N13">
+        <v>14.37992045</v>
+      </c>
+      <c r="O13">
+        <v>1.437992045</v>
+      </c>
+      <c r="P13">
+        <v>12.941928405</v>
+      </c>
+      <c r="Q13">
+        <v>13.441928405</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1372231069141573</v>
+      </c>
+      <c r="T13">
+        <v>1.418663510335028</v>
+      </c>
+      <c r="U13">
+        <v>0.0495</v>
+      </c>
+      <c r="V13">
+        <v>0.1</v>
+      </c>
+      <c r="W13">
+        <v>0.04455000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.488352615095216</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1271491943091576</v>
+      </c>
+      <c r="C14">
+        <v>424.7357323315723</v>
+      </c>
+      <c r="D14">
+        <v>463.3785323315723</v>
+      </c>
+      <c r="E14">
+        <v>56.35279999999999</v>
+      </c>
+      <c r="F14">
+        <v>57.7428</v>
+      </c>
+      <c r="G14">
+        <v>19.1</v>
+      </c>
+      <c r="H14">
+        <v>479.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>17.5</v>
+      </c>
+      <c r="K14">
+        <v>0.5</v>
+      </c>
+      <c r="L14">
+        <v>17</v>
+      </c>
+      <c r="M14">
+        <v>2.93910852</v>
+      </c>
+      <c r="N14">
+        <v>14.06089148</v>
+      </c>
+      <c r="O14">
+        <v>1.406089148</v>
+      </c>
+      <c r="P14">
+        <v>12.654802332</v>
+      </c>
+      <c r="Q14">
+        <v>13.154802332</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1382409026240427</v>
+      </c>
+      <c r="T14">
+        <v>1.433333943730808</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.1</v>
+      </c>
+      <c r="W14">
+        <v>0.04581</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.784066795873192</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1271307234647151</v>
+      </c>
+      <c r="C15">
+        <v>420.0207294524488</v>
+      </c>
+      <c r="D15">
+        <v>463.4754294524488</v>
+      </c>
+      <c r="E15">
+        <v>61.1647</v>
+      </c>
+      <c r="F15">
+        <v>62.5547</v>
+      </c>
+      <c r="G15">
+        <v>19.1</v>
+      </c>
+      <c r="H15">
+        <v>479.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>17.5</v>
+      </c>
+      <c r="K15">
+        <v>0.5</v>
+      </c>
+      <c r="L15">
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>3.18403423</v>
+      </c>
+      <c r="N15">
+        <v>13.81596577</v>
+      </c>
+      <c r="O15">
+        <v>1.381596577</v>
+      </c>
+      <c r="P15">
+        <v>12.434369193</v>
+      </c>
+      <c r="Q15">
+        <v>12.934369193</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1392820959364542</v>
+      </c>
+      <c r="T15">
+        <v>1.448341628469019</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.1</v>
+      </c>
+      <c r="W15">
+        <v>0.04581</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.339138580806023</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1271122526202726</v>
+      </c>
+      <c r="C16">
+        <v>415.3057671061303</v>
+      </c>
+      <c r="D16">
+        <v>463.5723671061303</v>
+      </c>
+      <c r="E16">
+        <v>65.9766</v>
+      </c>
+      <c r="F16">
+        <v>67.36660000000001</v>
+      </c>
+      <c r="G16">
+        <v>19.1</v>
+      </c>
+      <c r="H16">
+        <v>479.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>17.5</v>
+      </c>
+      <c r="K16">
+        <v>0.5</v>
+      </c>
+      <c r="L16">
+        <v>17</v>
+      </c>
+      <c r="M16">
+        <v>3.42895994</v>
+      </c>
+      <c r="N16">
+        <v>13.57104006</v>
+      </c>
+      <c r="O16">
+        <v>1.357104006</v>
+      </c>
+      <c r="P16">
+        <v>12.213936054</v>
+      </c>
+      <c r="Q16">
+        <v>12.713936054</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1403475030468286</v>
+      </c>
+      <c r="T16">
+        <v>1.463698329131375</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.1</v>
+      </c>
+      <c r="W16">
+        <v>0.04581</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.957771539319879</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1270937817758302</v>
+      </c>
+      <c r="C17">
+        <v>410.5908453180544</v>
+      </c>
+      <c r="D17">
+        <v>463.6693453180544</v>
+      </c>
+      <c r="E17">
+        <v>70.7885</v>
+      </c>
+      <c r="F17">
+        <v>72.1785</v>
+      </c>
+      <c r="G17">
+        <v>19.1</v>
+      </c>
+      <c r="H17">
+        <v>479.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>17.5</v>
+      </c>
+      <c r="K17">
+        <v>0.5</v>
+      </c>
+      <c r="L17">
+        <v>17</v>
+      </c>
+      <c r="M17">
+        <v>3.67388565</v>
+      </c>
+      <c r="N17">
+        <v>13.32611435</v>
+      </c>
+      <c r="O17">
+        <v>1.332611435</v>
+      </c>
+      <c r="P17">
+        <v>11.993502915</v>
+      </c>
+      <c r="Q17">
+        <v>12.493502915</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1414379785598002</v>
+      </c>
+      <c r="T17">
+        <v>1.479416363926964</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.1</v>
+      </c>
+      <c r="W17">
+        <v>0.04581</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.627253436698554</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1274497109313877</v>
+      </c>
+      <c r="C18">
+        <v>403.9173099353434</v>
+      </c>
+      <c r="D18">
+        <v>461.8077099353434</v>
+      </c>
+      <c r="E18">
+        <v>75.60040000000001</v>
+      </c>
+      <c r="F18">
+        <v>76.99040000000001</v>
+      </c>
+      <c r="G18">
+        <v>19.1</v>
+      </c>
+      <c r="H18">
+        <v>479.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>17.5</v>
+      </c>
+      <c r="K18">
+        <v>0.5</v>
+      </c>
+      <c r="L18">
+        <v>17</v>
+      </c>
+      <c r="M18">
+        <v>4.118986400000001</v>
+      </c>
+      <c r="N18">
+        <v>12.8810136</v>
+      </c>
+      <c r="O18">
+        <v>1.28810136</v>
+      </c>
+      <c r="P18">
+        <v>11.59291224</v>
+      </c>
+      <c r="Q18">
+        <v>12.09291224</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1425544177754616</v>
+      </c>
+      <c r="T18">
+        <v>1.495508637646256</v>
+      </c>
+      <c r="U18">
+        <v>0.0535</v>
+      </c>
+      <c r="V18">
+        <v>0.1</v>
+      </c>
+      <c r="W18">
+        <v>0.04815</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.12722897070017</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1278677400869452</v>
+      </c>
+      <c r="C19">
+        <v>396.9379687627508</v>
+      </c>
+      <c r="D19">
+        <v>459.6402687627508</v>
+      </c>
+      <c r="E19">
+        <v>80.4123</v>
+      </c>
+      <c r="F19">
+        <v>81.8023</v>
+      </c>
+      <c r="G19">
+        <v>19.1</v>
+      </c>
+      <c r="H19">
+        <v>479.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>17.5</v>
+      </c>
+      <c r="K19">
+        <v>0.5</v>
+      </c>
+      <c r="L19">
+        <v>17</v>
+      </c>
+      <c r="M19">
+        <v>4.59728926</v>
+      </c>
+      <c r="N19">
+        <v>12.40271074</v>
+      </c>
+      <c r="O19">
+        <v>1.240271074</v>
+      </c>
+      <c r="P19">
+        <v>11.162439666</v>
+      </c>
+      <c r="Q19">
+        <v>11.662439666</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1436977591408979</v>
+      </c>
+      <c r="T19">
+        <v>1.511988676997339</v>
+      </c>
+      <c r="U19">
+        <v>0.0562</v>
+      </c>
+      <c r="V19">
+        <v>0.1</v>
+      </c>
+      <c r="W19">
+        <v>0.05058</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.697831273727596</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1286583692425028</v>
+      </c>
+      <c r="C20">
+        <v>388.0818712036852</v>
+      </c>
+      <c r="D20">
+        <v>455.5960712036852</v>
+      </c>
+      <c r="E20">
+        <v>85.2242</v>
+      </c>
+      <c r="F20">
+        <v>86.6142</v>
+      </c>
+      <c r="G20">
+        <v>19.1</v>
+      </c>
+      <c r="H20">
+        <v>479.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>17.5</v>
+      </c>
+      <c r="K20">
+        <v>0.5</v>
+      </c>
+      <c r="L20">
+        <v>17</v>
+      </c>
+      <c r="M20">
+        <v>5.27480478</v>
+      </c>
+      <c r="N20">
+        <v>11.72519522</v>
+      </c>
+      <c r="O20">
+        <v>1.172519522</v>
+      </c>
+      <c r="P20">
+        <v>10.552675698</v>
+      </c>
+      <c r="Q20">
+        <v>11.052675698</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1448689868811009</v>
+      </c>
+      <c r="T20">
+        <v>1.528870668527716</v>
+      </c>
+      <c r="U20">
+        <v>0.0609</v>
+      </c>
+      <c r="V20">
+        <v>0.1</v>
+      </c>
+      <c r="W20">
+        <v>0.05481</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.222868088778823</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1287298983980603</v>
+      </c>
+      <c r="C21">
+        <v>382.907595588578</v>
+      </c>
+      <c r="D21">
+        <v>455.233695588578</v>
+      </c>
+      <c r="E21">
+        <v>90.0361</v>
+      </c>
+      <c r="F21">
+        <v>91.42610000000001</v>
+      </c>
+      <c r="G21">
+        <v>19.1</v>
+      </c>
+      <c r="H21">
+        <v>479.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>17.5</v>
+      </c>
+      <c r="K21">
+        <v>0.5</v>
+      </c>
+      <c r="L21">
+        <v>17</v>
+      </c>
+      <c r="M21">
+        <v>5.56784949</v>
+      </c>
+      <c r="N21">
+        <v>11.43215051</v>
+      </c>
+      <c r="O21">
+        <v>1.143215051</v>
+      </c>
+      <c r="P21">
+        <v>10.288935459</v>
+      </c>
+      <c r="Q21">
+        <v>10.788935459</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1460691338247658</v>
+      </c>
+      <c r="T21">
+        <v>1.54616949935514</v>
+      </c>
+      <c r="U21">
+        <v>0.0609</v>
+      </c>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+      <c r="W21">
+        <v>0.05481</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.053243452527306</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1304754275536179</v>
+      </c>
+      <c r="C22">
+        <v>369.4279019447762</v>
+      </c>
+      <c r="D22">
+        <v>446.5659019447762</v>
+      </c>
+      <c r="E22">
+        <v>94.848</v>
+      </c>
+      <c r="F22">
+        <v>96.238</v>
+      </c>
+      <c r="G22">
+        <v>19.1</v>
+      </c>
+      <c r="H22">
+        <v>479.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>17.5</v>
+      </c>
+      <c r="K22">
+        <v>0.5</v>
+      </c>
+      <c r="L22">
+        <v>17</v>
+      </c>
+      <c r="M22">
+        <v>6.7559076</v>
+      </c>
+      <c r="N22">
+        <v>10.2440924</v>
+      </c>
+      <c r="O22">
+        <v>1.02440924</v>
+      </c>
+      <c r="P22">
+        <v>9.219683159999999</v>
+      </c>
+      <c r="Q22">
+        <v>9.719683159999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1472992844420223</v>
+      </c>
+      <c r="T22">
+        <v>1.56390080095325</v>
+      </c>
+      <c r="U22">
+        <v>0.0702</v>
+      </c>
+      <c r="V22">
+        <v>0.1</v>
+      </c>
+      <c r="W22">
+        <v>0.06318</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.516316238546542</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1315189567091754</v>
+      </c>
+      <c r="C23">
+        <v>359.5900120598932</v>
+      </c>
+      <c r="D23">
+        <v>441.5399120598932</v>
+      </c>
+      <c r="E23">
+        <v>99.65989999999999</v>
+      </c>
+      <c r="F23">
+        <v>101.0499</v>
+      </c>
+      <c r="G23">
+        <v>19.1</v>
+      </c>
+      <c r="H23">
+        <v>479.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>17.5</v>
+      </c>
+      <c r="K23">
+        <v>0.5</v>
+      </c>
+      <c r="L23">
+        <v>17</v>
+      </c>
+      <c r="M23">
+        <v>7.568637509999999</v>
+      </c>
+      <c r="N23">
+        <v>9.431362490000001</v>
+      </c>
+      <c r="O23">
+        <v>0.9431362490000001</v>
+      </c>
+      <c r="P23">
+        <v>8.488226241000001</v>
+      </c>
+      <c r="Q23">
+        <v>8.988226241000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1485605781128802</v>
+      </c>
+      <c r="T23">
+        <v>1.582080996262704</v>
+      </c>
+      <c r="U23">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+      <c r="W23">
+        <v>0.06741</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.246111004462678</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1317164858647329</v>
+      </c>
+      <c r="C24">
+        <v>353.8394518731411</v>
+      </c>
+      <c r="D24">
+        <v>440.6012518731411</v>
+      </c>
+      <c r="E24">
+        <v>104.4718</v>
+      </c>
+      <c r="F24">
+        <v>105.8618</v>
+      </c>
+      <c r="G24">
+        <v>19.1</v>
+      </c>
+      <c r="H24">
+        <v>479.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>17.5</v>
+      </c>
+      <c r="K24">
+        <v>0.5</v>
+      </c>
+      <c r="L24">
+        <v>17</v>
+      </c>
+      <c r="M24">
+        <v>7.929048819999999</v>
+      </c>
+      <c r="N24">
+        <v>9.070951180000002</v>
+      </c>
+      <c r="O24">
+        <v>0.9070951180000002</v>
+      </c>
+      <c r="P24">
+        <v>8.163856062000001</v>
+      </c>
+      <c r="Q24">
+        <v>8.663856062000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1498542126470935</v>
+      </c>
+      <c r="T24">
+        <v>1.600727350426246</v>
+      </c>
+      <c r="U24">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+      <c r="W24">
+        <v>0.06741</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.144015049714374</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1319140150202904</v>
+      </c>
+      <c r="C25">
+        <v>348.0928741750403</v>
+      </c>
+      <c r="D25">
+        <v>439.6665741750403</v>
+      </c>
+      <c r="E25">
+        <v>109.2837</v>
+      </c>
+      <c r="F25">
+        <v>110.6737</v>
+      </c>
+      <c r="G25">
+        <v>19.1</v>
+      </c>
+      <c r="H25">
+        <v>479.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>17.5</v>
+      </c>
+      <c r="K25">
+        <v>0.5</v>
+      </c>
+      <c r="L25">
+        <v>17</v>
+      </c>
+      <c r="M25">
+        <v>8.28946013</v>
+      </c>
+      <c r="N25">
+        <v>8.71053987</v>
+      </c>
+      <c r="O25">
+        <v>0.871053987</v>
+      </c>
+      <c r="P25">
+        <v>7.839485883</v>
+      </c>
+      <c r="Q25">
+        <v>8.339485883</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1511814480782993</v>
+      </c>
+      <c r="T25">
+        <v>1.619858025477153</v>
+      </c>
+      <c r="U25">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+      <c r="W25">
+        <v>0.06741</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.050797004074619</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.135632344175848</v>
+      </c>
+      <c r="C26">
+        <v>326.3979269309263</v>
+      </c>
+      <c r="D26">
+        <v>422.7835269309263</v>
+      </c>
+      <c r="E26">
+        <v>114.0956</v>
+      </c>
+      <c r="F26">
+        <v>115.4856</v>
+      </c>
+      <c r="G26">
+        <v>19.1</v>
+      </c>
+      <c r="H26">
+        <v>479.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>17.5</v>
+      </c>
+      <c r="K26">
+        <v>0.5</v>
+      </c>
+      <c r="L26">
+        <v>17</v>
+      </c>
+      <c r="M26">
+        <v>10.53228672</v>
+      </c>
+      <c r="N26">
+        <v>6.46771328</v>
+      </c>
+      <c r="O26">
+        <v>0.646771328</v>
+      </c>
+      <c r="P26">
+        <v>5.820941952</v>
+      </c>
+      <c r="Q26">
+        <v>6.320941952</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1525436107576947</v>
+      </c>
+      <c r="T26">
+        <v>1.63949213934519</v>
+      </c>
+      <c r="U26">
+        <v>0.0912</v>
+      </c>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+      <c r="W26">
+        <v>0.08208</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>1.614084429330841</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1359765733314055</v>
+      </c>
+      <c r="C27">
+        <v>320.0883983207597</v>
+      </c>
+      <c r="D27">
+        <v>421.2858983207597</v>
+      </c>
+      <c r="E27">
+        <v>118.9075</v>
+      </c>
+      <c r="F27">
+        <v>120.2975</v>
+      </c>
+      <c r="G27">
+        <v>19.1</v>
+      </c>
+      <c r="H27">
+        <v>479.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>17.5</v>
+      </c>
+      <c r="K27">
+        <v>0.5</v>
+      </c>
+      <c r="L27">
+        <v>17</v>
+      </c>
+      <c r="M27">
+        <v>10.971132</v>
+      </c>
+      <c r="N27">
+        <v>6.028867999999999</v>
+      </c>
+      <c r="O27">
+        <v>0.6028867999999999</v>
+      </c>
+      <c r="P27">
+        <v>5.425981199999999</v>
+      </c>
+      <c r="Q27">
+        <v>5.925981199999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1539420977752073</v>
+      </c>
+      <c r="T27">
+        <v>1.65964982958304</v>
+      </c>
+      <c r="U27">
+        <v>0.0912</v>
+      </c>
+      <c r="V27">
+        <v>0.1</v>
+      </c>
+      <c r="W27">
+        <v>0.08208</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.549521052157608</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1524677714064991</v>
+      </c>
+      <c r="C28">
+        <v>254.1553105866773</v>
+      </c>
+      <c r="D28">
+        <v>360.1647105866773</v>
+      </c>
+      <c r="E28">
+        <v>123.7194</v>
+      </c>
+      <c r="F28">
+        <v>125.1094</v>
+      </c>
+      <c r="G28">
+        <v>19.1</v>
+      </c>
+      <c r="H28">
+        <v>479.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>17.5</v>
+      </c>
+      <c r="K28">
+        <v>0.5</v>
+      </c>
+      <c r="L28">
+        <v>17</v>
+      </c>
+      <c r="M28">
+        <v>19.59213204</v>
+      </c>
+      <c r="N28">
+        <v>-2.592132040000003</v>
+      </c>
+      <c r="O28">
+        <v>-0.2592132040000003</v>
+      </c>
+      <c r="P28">
+        <v>-2.332918836000002</v>
+      </c>
+      <c r="Q28">
+        <v>-1.832918836000002</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1557901073046195</v>
+      </c>
+      <c r="T28">
+        <v>1.686286904639156</v>
+      </c>
+      <c r="U28">
+        <v>0.1566</v>
+      </c>
+      <c r="V28">
+        <v>0.08676952546712215</v>
+      </c>
+      <c r="W28">
+        <v>0.1430118923118487</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8676952546712214</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1536457714064991</v>
+      </c>
+      <c r="C29">
+        <v>245.6491167186917</v>
+      </c>
+      <c r="D29">
+        <v>356.4704167186917</v>
+      </c>
+      <c r="E29">
+        <v>128.5313</v>
+      </c>
+      <c r="F29">
+        <v>129.9213</v>
+      </c>
+      <c r="G29">
+        <v>19.1</v>
+      </c>
+      <c r="H29">
+        <v>479.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>17.5</v>
+      </c>
+      <c r="K29">
+        <v>0.5</v>
+      </c>
+      <c r="L29">
+        <v>17</v>
+      </c>
+      <c r="M29">
+        <v>20.34567558</v>
+      </c>
+      <c r="N29">
+        <v>-3.345675580000002</v>
+      </c>
+      <c r="O29">
+        <v>-0.3345675580000002</v>
+      </c>
+      <c r="P29">
+        <v>-3.011108022000001</v>
+      </c>
+      <c r="Q29">
+        <v>-2.511108022000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1573927115142718</v>
+      </c>
+      <c r="T29">
+        <v>1.709386725250651</v>
+      </c>
+      <c r="U29">
+        <v>0.1566</v>
+      </c>
+      <c r="V29">
+        <v>0.08355583933871022</v>
+      </c>
+      <c r="W29">
+        <v>0.143515155559558</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8355583933871022</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1548237714064991</v>
+      </c>
+      <c r="C30">
+        <v>237.2179398601298</v>
+      </c>
+      <c r="D30">
+        <v>352.8511398601298</v>
+      </c>
+      <c r="E30">
+        <v>133.3432</v>
+      </c>
+      <c r="F30">
+        <v>134.7332</v>
+      </c>
+      <c r="G30">
+        <v>19.1</v>
+      </c>
+      <c r="H30">
+        <v>479.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>17.5</v>
+      </c>
+      <c r="K30">
+        <v>0.5</v>
+      </c>
+      <c r="L30">
+        <v>17</v>
+      </c>
+      <c r="M30">
+        <v>21.09921912</v>
+      </c>
+      <c r="N30">
+        <v>-4.099219120000004</v>
+      </c>
+      <c r="O30">
+        <v>-0.4099219120000004</v>
+      </c>
+      <c r="P30">
+        <v>-3.689297208000004</v>
+      </c>
+      <c r="Q30">
+        <v>-3.189297208000004</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1590398325075256</v>
+      </c>
+      <c r="T30">
+        <v>1.733128207545799</v>
+      </c>
+      <c r="U30">
+        <v>0.1566</v>
+      </c>
+      <c r="V30">
+        <v>0.08057170221947056</v>
+      </c>
+      <c r="W30">
+        <v>0.1439824714324309</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8057170221947056</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1716393126657613</v>
+      </c>
+      <c r="C31">
+        <v>187.7401741489396</v>
+      </c>
+      <c r="D31">
+        <v>308.1852741489396</v>
+      </c>
+      <c r="E31">
+        <v>138.1551</v>
+      </c>
+      <c r="F31">
+        <v>139.5451</v>
+      </c>
+      <c r="G31">
+        <v>19.1</v>
+      </c>
+      <c r="H31">
+        <v>479.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>17.5</v>
+      </c>
+      <c r="K31">
+        <v>0.5</v>
+      </c>
+      <c r="L31">
+        <v>17</v>
+      </c>
+      <c r="M31">
+        <v>29.13701688</v>
+      </c>
+      <c r="N31">
+        <v>-12.13701688</v>
+      </c>
+      <c r="O31">
+        <v>-1.213701688</v>
+      </c>
+      <c r="P31">
+        <v>-10.923315192</v>
+      </c>
+      <c r="Q31">
+        <v>-10.423315192</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1614369305136347</v>
+      </c>
+      <c r="T31">
+        <v>1.767679804000987</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.05834502574513387</v>
+      </c>
+      <c r="W31">
+        <v>0.196617558624416</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5834502574513386</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1733393126657613</v>
+      </c>
+      <c r="C32">
+        <v>179.0341337993842</v>
+      </c>
+      <c r="D32">
+        <v>304.2911337993842</v>
+      </c>
+      <c r="E32">
+        <v>142.967</v>
+      </c>
+      <c r="F32">
+        <v>144.357</v>
+      </c>
+      <c r="G32">
+        <v>19.1</v>
+      </c>
+      <c r="H32">
+        <v>479.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>17.5</v>
+      </c>
+      <c r="K32">
+        <v>0.5</v>
+      </c>
+      <c r="L32">
+        <v>17</v>
+      </c>
+      <c r="M32">
+        <v>30.1417416</v>
+      </c>
+      <c r="N32">
+        <v>-13.1417416</v>
+      </c>
+      <c r="O32">
+        <v>-1.31417416</v>
+      </c>
+      <c r="P32">
+        <v>-11.82756744</v>
+      </c>
+      <c r="Q32">
+        <v>-11.32756744</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1631888866638295</v>
+      </c>
+      <c r="T32">
+        <v>1.792932372629573</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.0564001915536294</v>
+      </c>
+      <c r="W32">
+        <v>0.1970236400036022</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.564001915536294</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1750393126657613</v>
+      </c>
+      <c r="C33">
+        <v>170.4252759511892</v>
+      </c>
+      <c r="D33">
+        <v>300.4941759511892</v>
+      </c>
+      <c r="E33">
+        <v>147.7789</v>
+      </c>
+      <c r="F33">
+        <v>149.1689</v>
+      </c>
+      <c r="G33">
+        <v>19.1</v>
+      </c>
+      <c r="H33">
+        <v>479.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>17.5</v>
+      </c>
+      <c r="K33">
+        <v>0.5</v>
+      </c>
+      <c r="L33">
+        <v>17</v>
+      </c>
+      <c r="M33">
+        <v>31.14646632000001</v>
+      </c>
+      <c r="N33">
+        <v>-14.14646632000001</v>
+      </c>
+      <c r="O33">
+        <v>-1.414646632000001</v>
+      </c>
+      <c r="P33">
+        <v>-12.73181968800001</v>
+      </c>
+      <c r="Q33">
+        <v>-12.23181968800001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1649916241517111</v>
+      </c>
+      <c r="T33">
+        <v>1.818916899769131</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.05458083053577038</v>
+      </c>
+      <c r="W33">
+        <v>0.1974035225841312</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5458083053577039</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1767393126657613</v>
+      </c>
+      <c r="C34">
+        <v>161.9100074970137</v>
+      </c>
+      <c r="D34">
+        <v>296.7908074970136</v>
+      </c>
+      <c r="E34">
+        <v>152.5908</v>
+      </c>
+      <c r="F34">
+        <v>153.9808</v>
+      </c>
+      <c r="G34">
+        <v>19.1</v>
+      </c>
+      <c r="H34">
+        <v>479.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>17.5</v>
+      </c>
+      <c r="K34">
+        <v>0.5</v>
+      </c>
+      <c r="L34">
+        <v>17</v>
+      </c>
+      <c r="M34">
+        <v>32.15119104000001</v>
+      </c>
+      <c r="N34">
+        <v>-15.15119104000001</v>
+      </c>
+      <c r="O34">
+        <v>-1.515119104000001</v>
+      </c>
+      <c r="P34">
+        <v>-13.63607193600001</v>
+      </c>
+      <c r="Q34">
+        <v>-13.13607193600001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1668473833304127</v>
+      </c>
+      <c r="T34">
+        <v>1.845665677706913</v>
+      </c>
+      <c r="U34">
+        <v>0.2088</v>
+      </c>
+      <c r="V34">
+        <v>0.05287517958152756</v>
+      </c>
+      <c r="W34">
+        <v>0.1977596625033771</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5287517958152755</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1784393126657613</v>
+      </c>
+      <c r="C35">
+        <v>153.4849103026635</v>
+      </c>
+      <c r="D35">
+        <v>293.1776103026635</v>
+      </c>
+      <c r="E35">
+        <v>157.4027</v>
+      </c>
+      <c r="F35">
+        <v>158.7927</v>
+      </c>
+      <c r="G35">
+        <v>19.1</v>
+      </c>
+      <c r="H35">
+        <v>479.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>17.5</v>
+      </c>
+      <c r="K35">
+        <v>0.5</v>
+      </c>
+      <c r="L35">
+        <v>17</v>
+      </c>
+      <c r="M35">
+        <v>33.15591576</v>
+      </c>
+      <c r="N35">
+        <v>-16.15591576</v>
+      </c>
+      <c r="O35">
+        <v>-1.615591576</v>
+      </c>
+      <c r="P35">
+        <v>-14.540324184</v>
+      </c>
+      <c r="Q35">
+        <v>-14.040324184</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1687585383054935</v>
+      </c>
+      <c r="T35">
+        <v>1.873212926627912</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.05127290141239037</v>
+      </c>
+      <c r="W35">
+        <v>0.1980942181850929</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5127290141239036</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1905275819845787</v>
+      </c>
+      <c r="C36">
+        <v>125.3152933653033</v>
+      </c>
+      <c r="D36">
+        <v>269.8198933653033</v>
+      </c>
+      <c r="E36">
+        <v>162.2146</v>
+      </c>
+      <c r="F36">
+        <v>163.6046</v>
+      </c>
+      <c r="G36">
+        <v>19.1</v>
+      </c>
+      <c r="H36">
+        <v>479.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>17.5</v>
+      </c>
+      <c r="K36">
+        <v>0.5</v>
+      </c>
+      <c r="L36">
+        <v>17</v>
+      </c>
+      <c r="M36">
+        <v>39.06877848000001</v>
+      </c>
+      <c r="N36">
+        <v>-22.06877848000001</v>
+      </c>
+      <c r="O36">
+        <v>-2.206877848000001</v>
+      </c>
+      <c r="P36">
+        <v>-19.861900632</v>
+      </c>
+      <c r="Q36">
+        <v>-19.361900632</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1710128636113607</v>
+      </c>
+      <c r="T36">
+        <v>1.905706607757567</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.04351300619419826</v>
+      </c>
+      <c r="W36">
+        <v>0.2284090941208255</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.4351300619419826</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1925275819845787</v>
+      </c>
+      <c r="C37">
+        <v>116.9930292539057</v>
+      </c>
+      <c r="D37">
+        <v>266.3095292539057</v>
+      </c>
+      <c r="E37">
+        <v>167.0265</v>
+      </c>
+      <c r="F37">
+        <v>168.4165</v>
+      </c>
+      <c r="G37">
+        <v>19.1</v>
+      </c>
+      <c r="H37">
+        <v>479.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>17.5</v>
+      </c>
+      <c r="K37">
+        <v>0.5</v>
+      </c>
+      <c r="L37">
+        <v>17</v>
+      </c>
+      <c r="M37">
+        <v>40.2178602</v>
+      </c>
+      <c r="N37">
+        <v>-23.2178602</v>
+      </c>
+      <c r="O37">
+        <v>-2.321786020000001</v>
+      </c>
+      <c r="P37">
+        <v>-20.89607418</v>
+      </c>
+      <c r="Q37">
+        <v>-20.39607418</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.17304690766692</v>
+      </c>
+      <c r="T37">
+        <v>1.935025170953837</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.04226977744579261</v>
+      </c>
+      <c r="W37">
+        <v>0.2287059771459447</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.422697774457926</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1945275819845787</v>
+      </c>
+      <c r="C38">
+        <v>108.7609319342006</v>
+      </c>
+      <c r="D38">
+        <v>262.8893319342006</v>
+      </c>
+      <c r="E38">
+        <v>171.8384</v>
+      </c>
+      <c r="F38">
+        <v>173.2284</v>
+      </c>
+      <c r="G38">
+        <v>19.1</v>
+      </c>
+      <c r="H38">
+        <v>479.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>17.5</v>
+      </c>
+      <c r="K38">
+        <v>0.5</v>
+      </c>
+      <c r="L38">
+        <v>17</v>
+      </c>
+      <c r="M38">
+        <v>41.36694192</v>
+      </c>
+      <c r="N38">
+        <v>-24.36694192</v>
+      </c>
+      <c r="O38">
+        <v>-2.436694192</v>
+      </c>
+      <c r="P38">
+        <v>-21.930247728</v>
+      </c>
+      <c r="Q38">
+        <v>-21.430247728</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1751445155992157</v>
+      </c>
+      <c r="T38">
+        <v>1.965259939249991</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.04109561696118726</v>
+      </c>
+      <c r="W38">
+        <v>0.2289863666696685</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.4109561696118725</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1965275819845787</v>
+      </c>
+      <c r="C39">
+        <v>100.6155714369756</v>
+      </c>
+      <c r="D39">
+        <v>259.5558714369756</v>
+      </c>
+      <c r="E39">
+        <v>176.6503</v>
+      </c>
+      <c r="F39">
+        <v>178.0403</v>
+      </c>
+      <c r="G39">
+        <v>19.1</v>
+      </c>
+      <c r="H39">
+        <v>479.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>17.5</v>
+      </c>
+      <c r="K39">
+        <v>0.5</v>
+      </c>
+      <c r="L39">
+        <v>17</v>
+      </c>
+      <c r="M39">
+        <v>42.51602364</v>
+      </c>
+      <c r="N39">
+        <v>-25.51602364</v>
+      </c>
+      <c r="O39">
+        <v>-2.551602364</v>
+      </c>
+      <c r="P39">
+        <v>-22.964421276</v>
+      </c>
+      <c r="Q39">
+        <v>-22.464421276</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1773087142595207</v>
+      </c>
+      <c r="T39">
+        <v>1.996454541460308</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0399849246108849</v>
+      </c>
+      <c r="W39">
+        <v>0.2292516000029207</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.399849246108849</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1985275819845787</v>
+      </c>
+      <c r="C40">
+        <v>92.55368958397244</v>
+      </c>
+      <c r="D40">
+        <v>256.3058895839724</v>
+      </c>
+      <c r="E40">
+        <v>181.4622</v>
+      </c>
+      <c r="F40">
+        <v>182.8522</v>
+      </c>
+      <c r="G40">
+        <v>19.1</v>
+      </c>
+      <c r="H40">
+        <v>479.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>17.5</v>
+      </c>
+      <c r="K40">
+        <v>0.5</v>
+      </c>
+      <c r="L40">
+        <v>17</v>
+      </c>
+      <c r="M40">
+        <v>43.66510536000001</v>
+      </c>
+      <c r="N40">
+        <v>-26.66510536000001</v>
+      </c>
+      <c r="O40">
+        <v>-2.666510536000001</v>
+      </c>
+      <c r="P40">
+        <v>-23.998594824</v>
+      </c>
+      <c r="Q40">
+        <v>-23.498594824</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1795427257798355</v>
+      </c>
+      <c r="T40">
+        <v>2.028655421161281</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.03893268975270371</v>
+      </c>
+      <c r="W40">
+        <v>0.2295028736870544</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3893268975270371</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2005275819845787</v>
+      </c>
+      <c r="C41">
+        <v>84.5721893656447</v>
+      </c>
+      <c r="D41">
+        <v>253.1362893656447</v>
+      </c>
+      <c r="E41">
+        <v>186.2741</v>
+      </c>
+      <c r="F41">
+        <v>187.6641</v>
+      </c>
+      <c r="G41">
+        <v>19.1</v>
+      </c>
+      <c r="H41">
+        <v>479.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>17.5</v>
+      </c>
+      <c r="K41">
+        <v>0.5</v>
+      </c>
+      <c r="L41">
+        <v>17</v>
+      </c>
+      <c r="M41">
+        <v>44.81418708</v>
+      </c>
+      <c r="N41">
+        <v>-27.81418708</v>
+      </c>
+      <c r="O41">
+        <v>-2.781418708</v>
+      </c>
+      <c r="P41">
+        <v>-25.032768372</v>
+      </c>
+      <c r="Q41">
+        <v>-24.532768372</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.181849983579505</v>
+      </c>
+      <c r="T41">
+        <v>2.061912067409827</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.03793441565648054</v>
+      </c>
+      <c r="W41">
+        <v>0.2297412615412324</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3793441565648054</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2025275819845787</v>
+      </c>
+      <c r="C42">
+        <v>76.66812509744597</v>
+      </c>
+      <c r="D42">
+        <v>250.0441250974459</v>
+      </c>
+      <c r="E42">
+        <v>191.086</v>
+      </c>
+      <c r="F42">
+        <v>192.476</v>
+      </c>
+      <c r="G42">
+        <v>19.1</v>
+      </c>
+      <c r="H42">
+        <v>479.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>17.5</v>
+      </c>
+      <c r="K42">
+        <v>0.5</v>
+      </c>
+      <c r="L42">
+        <v>17</v>
+      </c>
+      <c r="M42">
+        <v>45.9632688</v>
+      </c>
+      <c r="N42">
+        <v>-28.9632688</v>
+      </c>
+      <c r="O42">
+        <v>-2.89632688</v>
+      </c>
+      <c r="P42">
+        <v>-26.06694192</v>
+      </c>
+      <c r="Q42">
+        <v>-25.56694192</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1842341499724967</v>
+      </c>
+      <c r="T42">
+        <v>2.096277268533324</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.03698605526506853</v>
+      </c>
+      <c r="W42">
+        <v>0.2299677300027017</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3698605526506853</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2045275819845787</v>
+      </c>
+      <c r="C43">
+        <v>68.83869328888184</v>
+      </c>
+      <c r="D43">
+        <v>247.0265932888818</v>
+      </c>
+      <c r="E43">
+        <v>195.8979</v>
+      </c>
+      <c r="F43">
+        <v>197.2879</v>
+      </c>
+      <c r="G43">
+        <v>19.1</v>
+      </c>
+      <c r="H43">
+        <v>479.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>17.5</v>
+      </c>
+      <c r="K43">
+        <v>0.5</v>
+      </c>
+      <c r="L43">
+        <v>17</v>
+      </c>
+      <c r="M43">
+        <v>47.11235052000001</v>
+      </c>
+      <c r="N43">
+        <v>-30.11235052000001</v>
+      </c>
+      <c r="O43">
+        <v>-3.011235052000001</v>
+      </c>
+      <c r="P43">
+        <v>-27.10111546800001</v>
+      </c>
+      <c r="Q43">
+        <v>-26.60111546800001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1866991355652509</v>
+      </c>
+      <c r="T43">
+        <v>2.131807391728804</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03608395635616442</v>
+      </c>
+      <c r="W43">
+        <v>0.2301831512221479</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3608395635616441</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2065275819845787</v>
+      </c>
+      <c r="C44">
+        <v>61.08122416583095</v>
+      </c>
+      <c r="D44">
+        <v>244.0810241658309</v>
+      </c>
+      <c r="E44">
+        <v>200.7098</v>
+      </c>
+      <c r="F44">
+        <v>202.0998</v>
+      </c>
+      <c r="G44">
+        <v>19.1</v>
+      </c>
+      <c r="H44">
+        <v>479.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>17.5</v>
+      </c>
+      <c r="K44">
+        <v>0.5</v>
+      </c>
+      <c r="L44">
+        <v>17</v>
+      </c>
+      <c r="M44">
+        <v>48.26143224</v>
+      </c>
+      <c r="N44">
+        <v>-31.26143224</v>
+      </c>
+      <c r="O44">
+        <v>-3.126143224</v>
+      </c>
+      <c r="P44">
+        <v>-28.135289016</v>
+      </c>
+      <c r="Q44">
+        <v>-27.635289016</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1892491206612035</v>
+      </c>
+      <c r="T44">
+        <v>2.168562691586196</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.0352248145381605</v>
+      </c>
+      <c r="W44">
+        <v>0.2303883142882873</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3522481453816051</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2085275819845787</v>
+      </c>
+      <c r="C45">
+        <v>53.39317379225162</v>
+      </c>
+      <c r="D45">
+        <v>241.2048737922516</v>
+      </c>
+      <c r="E45">
+        <v>205.5217</v>
+      </c>
+      <c r="F45">
+        <v>206.9117</v>
+      </c>
+      <c r="G45">
+        <v>19.1</v>
+      </c>
+      <c r="H45">
+        <v>479.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>17.5</v>
+      </c>
+      <c r="K45">
+        <v>0.5</v>
+      </c>
+      <c r="L45">
+        <v>17</v>
+      </c>
+      <c r="M45">
+        <v>49.41051396</v>
+      </c>
+      <c r="N45">
+        <v>-32.41051396</v>
+      </c>
+      <c r="O45">
+        <v>-3.241051396</v>
+      </c>
+      <c r="P45">
+        <v>-29.169462564</v>
+      </c>
+      <c r="Q45">
+        <v>-28.669462564</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1918885789184176</v>
+      </c>
+      <c r="T45">
+        <v>2.206607651087709</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03440563280471491</v>
+      </c>
+      <c r="W45">
+        <v>0.2305839348862341</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.344056328047149</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2105275819845787</v>
+      </c>
+      <c r="C46">
+        <v>45.77211674240837</v>
+      </c>
+      <c r="D46">
+        <v>238.3957167424084</v>
+      </c>
+      <c r="E46">
+        <v>210.3336</v>
+      </c>
+      <c r="F46">
+        <v>211.7236</v>
+      </c>
+      <c r="G46">
+        <v>19.1</v>
+      </c>
+      <c r="H46">
+        <v>479.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>17.5</v>
+      </c>
+      <c r="K46">
+        <v>0.5</v>
+      </c>
+      <c r="L46">
+        <v>17</v>
+      </c>
+      <c r="M46">
+        <v>50.55959568</v>
+      </c>
+      <c r="N46">
+        <v>-33.55959568</v>
+      </c>
+      <c r="O46">
+        <v>-3.355959568</v>
+      </c>
+      <c r="P46">
+        <v>-30.203636112</v>
+      </c>
+      <c r="Q46">
+        <v>-29.703636112</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1946223035419608</v>
+      </c>
+      <c r="T46">
+        <v>2.246011359142847</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03362368660460775</v>
+      </c>
+      <c r="W46">
+        <v>0.2307706636388197</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3362368660460775</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2125275819845787</v>
+      </c>
+      <c r="C47">
+        <v>38.21573927925493</v>
+      </c>
+      <c r="D47">
+        <v>235.651239279255</v>
+      </c>
+      <c r="E47">
+        <v>215.1455</v>
+      </c>
+      <c r="F47">
+        <v>216.5355</v>
+      </c>
+      <c r="G47">
+        <v>19.1</v>
+      </c>
+      <c r="H47">
+        <v>479.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>17.5</v>
+      </c>
+      <c r="K47">
+        <v>0.5</v>
+      </c>
+      <c r="L47">
+        <v>17</v>
+      </c>
+      <c r="M47">
+        <v>51.70867740000001</v>
+      </c>
+      <c r="N47">
+        <v>-34.70867740000001</v>
+      </c>
+      <c r="O47">
+        <v>-3.470867740000001</v>
+      </c>
+      <c r="P47">
+        <v>-31.23780966</v>
+      </c>
+      <c r="Q47">
+        <v>-30.73780966</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1974554363336328</v>
+      </c>
+      <c r="T47">
+        <v>2.28684792930908</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.0328764935689498</v>
+      </c>
+      <c r="W47">
+        <v>0.2309490933357348</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3287649356894979</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2145275819845787</v>
+      </c>
+      <c r="C48">
+        <v>30.72183299864795</v>
+      </c>
+      <c r="D48">
+        <v>232.969232998648</v>
+      </c>
+      <c r="E48">
+        <v>219.9574</v>
+      </c>
+      <c r="F48">
+        <v>221.3474</v>
+      </c>
+      <c r="G48">
+        <v>19.1</v>
+      </c>
+      <c r="H48">
+        <v>479.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>17.5</v>
+      </c>
+      <c r="K48">
+        <v>0.5</v>
+      </c>
+      <c r="L48">
+        <v>17</v>
+      </c>
+      <c r="M48">
+        <v>52.85775912000001</v>
+      </c>
+      <c r="N48">
+        <v>-35.85775912000001</v>
+      </c>
+      <c r="O48">
+        <v>-3.585775912000001</v>
+      </c>
+      <c r="P48">
+        <v>-32.27198320800001</v>
+      </c>
+      <c r="Q48">
+        <v>-31.77198320800001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2003934999694408</v>
+      </c>
+      <c r="T48">
+        <v>2.329196965037026</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03216178718701611</v>
+      </c>
+      <c r="W48">
+        <v>0.2311197652197406</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.321617871870161</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2165275819845787</v>
+      </c>
+      <c r="C49">
+        <v>23.28828890269824</v>
+      </c>
+      <c r="D49">
+        <v>230.3475889026982</v>
+      </c>
+      <c r="E49">
+        <v>224.7693</v>
+      </c>
+      <c r="F49">
+        <v>226.1593</v>
+      </c>
+      <c r="G49">
+        <v>19.1</v>
+      </c>
+      <c r="H49">
+        <v>479.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>17.5</v>
+      </c>
+      <c r="K49">
+        <v>0.5</v>
+      </c>
+      <c r="L49">
+        <v>17</v>
+      </c>
+      <c r="M49">
+        <v>54.00684084</v>
+      </c>
+      <c r="N49">
+        <v>-37.00684084</v>
+      </c>
+      <c r="O49">
+        <v>-3.700684084000001</v>
+      </c>
+      <c r="P49">
+        <v>-33.306156756</v>
+      </c>
+      <c r="Q49">
+        <v>-32.806156756</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2034424339311284</v>
+      </c>
+      <c r="T49">
+        <v>2.373144077584895</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.03147749384261151</v>
+      </c>
+      <c r="W49">
+        <v>0.2312831744703844</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3147749384261151</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2185275819845787</v>
+      </c>
+      <c r="C50">
+        <v>15.91309186883001</v>
+      </c>
+      <c r="D50">
+        <v>227.78429186883</v>
+      </c>
+      <c r="E50">
+        <v>229.5812</v>
+      </c>
+      <c r="F50">
+        <v>230.9712</v>
+      </c>
+      <c r="G50">
+        <v>19.1</v>
+      </c>
+      <c r="H50">
+        <v>479.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>17.5</v>
+      </c>
+      <c r="K50">
+        <v>0.5</v>
+      </c>
+      <c r="L50">
+        <v>17</v>
+      </c>
+      <c r="M50">
+        <v>55.15592256</v>
+      </c>
+      <c r="N50">
+        <v>-38.15592256</v>
+      </c>
+      <c r="O50">
+        <v>-3.815592256</v>
+      </c>
+      <c r="P50">
+        <v>-34.340330304</v>
+      </c>
+      <c r="Q50">
+        <v>-33.840330304</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2066086345836501</v>
+      </c>
+      <c r="T50">
+        <v>2.418781463692297</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03082171272089044</v>
+      </c>
+      <c r="W50">
+        <v>0.2314397750022514</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3082171272089044</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2205275819845787</v>
+      </c>
+      <c r="C51">
+        <v>8.594315484064566</v>
+      </c>
+      <c r="D51">
+        <v>225.2774154840646</v>
+      </c>
+      <c r="E51">
+        <v>234.3931</v>
+      </c>
+      <c r="F51">
+        <v>235.7831</v>
+      </c>
+      <c r="G51">
+        <v>19.1</v>
+      </c>
+      <c r="H51">
+        <v>479.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>17.5</v>
+      </c>
+      <c r="K51">
+        <v>0.5</v>
+      </c>
+      <c r="L51">
+        <v>17</v>
+      </c>
+      <c r="M51">
+        <v>56.30500428</v>
+      </c>
+      <c r="N51">
+        <v>-39.30500428</v>
+      </c>
+      <c r="O51">
+        <v>-3.930500428</v>
+      </c>
+      <c r="P51">
+        <v>-35.374503852</v>
+      </c>
+      <c r="Q51">
+        <v>-34.874503852</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2098989999676432</v>
+      </c>
+      <c r="T51">
+        <v>2.466208551215675</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03019269817556615</v>
+      </c>
+      <c r="W51">
+        <v>0.2315899836756748</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3019269817556615</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2225275819845787</v>
+      </c>
+      <c r="C52">
+        <v>1.33011721669854</v>
+      </c>
+      <c r="D52">
+        <v>222.8251172166985</v>
+      </c>
+      <c r="E52">
+        <v>239.205</v>
+      </c>
+      <c r="F52">
+        <v>240.595</v>
+      </c>
+      <c r="G52">
+        <v>19.1</v>
+      </c>
+      <c r="H52">
+        <v>479.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>17.5</v>
+      </c>
+      <c r="K52">
+        <v>0.5</v>
+      </c>
+      <c r="L52">
+        <v>17</v>
+      </c>
+      <c r="M52">
+        <v>57.454086</v>
+      </c>
+      <c r="N52">
+        <v>-40.454086</v>
+      </c>
+      <c r="O52">
+        <v>-4.045408600000001</v>
+      </c>
+      <c r="P52">
+        <v>-36.4086774</v>
+      </c>
+      <c r="Q52">
+        <v>-35.9086774</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2133209799669961</v>
+      </c>
+      <c r="T52">
+        <v>2.515532722239988</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.02958884421205482</v>
+      </c>
+      <c r="W52">
+        <v>0.2317341840021613</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2958884421205482</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2245275819845787</v>
+      </c>
+      <c r="C53">
+        <v>-5.881266100057275</v>
+      </c>
+      <c r="D53">
+        <v>220.4256338999427</v>
+      </c>
+      <c r="E53">
+        <v>244.0169</v>
+      </c>
+      <c r="F53">
+        <v>245.4069</v>
+      </c>
+      <c r="G53">
+        <v>19.1</v>
+      </c>
+      <c r="H53">
+        <v>479.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>17.5</v>
+      </c>
+      <c r="K53">
+        <v>0.5</v>
+      </c>
+      <c r="L53">
+        <v>17</v>
+      </c>
+      <c r="M53">
+        <v>58.60316772</v>
+      </c>
+      <c r="N53">
+        <v>-41.60316772</v>
+      </c>
+      <c r="O53">
+        <v>-4.160316772000001</v>
+      </c>
+      <c r="P53">
+        <v>-37.442850948</v>
+      </c>
+      <c r="Q53">
+        <v>-36.942850948</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2168826326193837</v>
+      </c>
+      <c r="T53">
+        <v>2.566870124734682</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02900867079613218</v>
+      </c>
+      <c r="W53">
+        <v>0.2318727294138836</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2900867079613217</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2265275819845787</v>
+      </c>
+      <c r="C54">
+        <v>-13.0415224957419</v>
+      </c>
+      <c r="D54">
+        <v>218.0772775042581</v>
+      </c>
+      <c r="E54">
+        <v>248.8288</v>
+      </c>
+      <c r="F54">
+        <v>250.2188</v>
+      </c>
+      <c r="G54">
+        <v>19.1</v>
+      </c>
+      <c r="H54">
+        <v>479.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>17.5</v>
+      </c>
+      <c r="K54">
+        <v>0.5</v>
+      </c>
+      <c r="L54">
+        <v>17</v>
+      </c>
+      <c r="M54">
+        <v>59.75224944000001</v>
+      </c>
+      <c r="N54">
+        <v>-42.75224944000001</v>
+      </c>
+      <c r="O54">
+        <v>-4.275224944000001</v>
+      </c>
+      <c r="P54">
+        <v>-38.47702449600001</v>
+      </c>
+      <c r="Q54">
+        <v>-37.97702449600001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2205926874656209</v>
+      </c>
+      <c r="T54">
+        <v>2.620346585666655</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02845081174236041</v>
+      </c>
+      <c r="W54">
+        <v>0.2320059461559243</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.284508117423604</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2285275819845787</v>
+      </c>
+      <c r="C55">
+        <v>-20.15226882291412</v>
+      </c>
+      <c r="D55">
+        <v>215.7784311770859</v>
+      </c>
+      <c r="E55">
+        <v>253.6407</v>
+      </c>
+      <c r="F55">
+        <v>255.0307</v>
+      </c>
+      <c r="G55">
+        <v>19.1</v>
+      </c>
+      <c r="H55">
+        <v>479.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>17.5</v>
+      </c>
+      <c r="K55">
+        <v>0.5</v>
+      </c>
+      <c r="L55">
+        <v>17</v>
+      </c>
+      <c r="M55">
+        <v>60.90133116000001</v>
+      </c>
+      <c r="N55">
+        <v>-43.90133116000001</v>
+      </c>
+      <c r="O55">
+        <v>-4.390133116000001</v>
+      </c>
+      <c r="P55">
+        <v>-39.51119804400001</v>
+      </c>
+      <c r="Q55">
+        <v>-39.01119804400001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2244606169861661</v>
+      </c>
+      <c r="T55">
+        <v>2.676098640680839</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02791400397363662</v>
+      </c>
+      <c r="W55">
+        <v>0.2321341358510956</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2791400397363661</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2305275819845787</v>
+      </c>
+      <c r="C56">
+        <v>-27.21505446955453</v>
+      </c>
+      <c r="D56">
+        <v>213.5275455304455</v>
+      </c>
+      <c r="E56">
+        <v>258.4526</v>
+      </c>
+      <c r="F56">
+        <v>259.8426</v>
+      </c>
+      <c r="G56">
+        <v>19.1</v>
+      </c>
+      <c r="H56">
+        <v>479.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>17.5</v>
+      </c>
+      <c r="K56">
+        <v>0.5</v>
+      </c>
+      <c r="L56">
+        <v>17</v>
+      </c>
+      <c r="M56">
+        <v>62.05041288</v>
+      </c>
+      <c r="N56">
+        <v>-45.05041288</v>
+      </c>
+      <c r="O56">
+        <v>-4.505041288</v>
+      </c>
+      <c r="P56">
+        <v>-40.545371592</v>
+      </c>
+      <c r="Q56">
+        <v>-40.045371592</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2284967173554305</v>
+      </c>
+      <c r="T56">
+        <v>2.734274698086944</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02739707797412484</v>
+      </c>
+      <c r="W56">
+        <v>0.232257577779779</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2739707797412484</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2325275819845787</v>
+      </c>
+      <c r="C57">
+        <v>-34.23136484151129</v>
+      </c>
+      <c r="D57">
+        <v>211.3231351584888</v>
+      </c>
+      <c r="E57">
+        <v>263.2645000000001</v>
+      </c>
+      <c r="F57">
+        <v>264.6545</v>
+      </c>
+      <c r="G57">
+        <v>19.1</v>
+      </c>
+      <c r="H57">
+        <v>479.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>17.5</v>
+      </c>
+      <c r="K57">
+        <v>0.5</v>
+      </c>
+      <c r="L57">
+        <v>17</v>
+      </c>
+      <c r="M57">
+        <v>63.19949460000002</v>
+      </c>
+      <c r="N57">
+        <v>-46.19949460000002</v>
+      </c>
+      <c r="O57">
+        <v>-4.619949460000002</v>
+      </c>
+      <c r="P57">
+        <v>-41.57954514000001</v>
+      </c>
+      <c r="Q57">
+        <v>-41.07954514000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.232712199963329</v>
+      </c>
+      <c r="T57">
+        <v>2.795036358044432</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0268989492836862</v>
+      </c>
+      <c r="W57">
+        <v>0.2323765309110558</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2689894928368619</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2345275819845787</v>
+      </c>
+      <c r="C58">
+        <v>-41.2026246314374</v>
+      </c>
+      <c r="D58">
+        <v>209.1637753685626</v>
+      </c>
+      <c r="E58">
+        <v>268.0764</v>
+      </c>
+      <c r="F58">
+        <v>269.4664</v>
+      </c>
+      <c r="G58">
+        <v>19.1</v>
+      </c>
+      <c r="H58">
+        <v>479.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>17.5</v>
+      </c>
+      <c r="K58">
+        <v>0.5</v>
+      </c>
+      <c r="L58">
+        <v>17</v>
+      </c>
+      <c r="M58">
+        <v>64.34857632000001</v>
+      </c>
+      <c r="N58">
+        <v>-47.34857632000001</v>
+      </c>
+      <c r="O58">
+        <v>-4.734857632000001</v>
+      </c>
+      <c r="P58">
+        <v>-42.61371868800001</v>
+      </c>
+      <c r="Q58">
+        <v>-42.11371868800001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.237119295417041</v>
+      </c>
+      <c r="T58">
+        <v>2.85855991163635</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02641861090362038</v>
+      </c>
+      <c r="W58">
+        <v>0.2324912357162155</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2641861090362038</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2365275819845787</v>
+      </c>
+      <c r="C59">
+        <v>-48.13020088933936</v>
+      </c>
+      <c r="D59">
+        <v>207.0480991106606</v>
+      </c>
+      <c r="E59">
+        <v>272.8883</v>
+      </c>
+      <c r="F59">
+        <v>274.2783</v>
+      </c>
+      <c r="G59">
+        <v>19.1</v>
+      </c>
+      <c r="H59">
+        <v>479.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>17.5</v>
+      </c>
+      <c r="K59">
+        <v>0.5</v>
+      </c>
+      <c r="L59">
+        <v>17</v>
+      </c>
+      <c r="M59">
+        <v>65.49765804</v>
+      </c>
+      <c r="N59">
+        <v>-48.49765804</v>
+      </c>
+      <c r="O59">
+        <v>-4.849765804</v>
+      </c>
+      <c r="P59">
+        <v>-43.647892236</v>
+      </c>
+      <c r="Q59">
+        <v>-43.147892236</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2417313720546466</v>
+      </c>
+      <c r="T59">
+        <v>2.925038049116266</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02595512650180247</v>
+      </c>
+      <c r="W59">
+        <v>0.2326019157913696</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2595512650180247</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2385275819845787</v>
+      </c>
+      <c r="C60">
+        <v>-55.01540590863948</v>
+      </c>
+      <c r="D60">
+        <v>204.9747940913605</v>
+      </c>
+      <c r="E60">
+        <v>277.7002</v>
+      </c>
+      <c r="F60">
+        <v>279.0902</v>
+      </c>
+      <c r="G60">
+        <v>19.1</v>
+      </c>
+      <c r="H60">
+        <v>479.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>17.5</v>
+      </c>
+      <c r="K60">
+        <v>0.5</v>
+      </c>
+      <c r="L60">
+        <v>17</v>
+      </c>
+      <c r="M60">
+        <v>66.64673976</v>
+      </c>
+      <c r="N60">
+        <v>-49.64673976</v>
+      </c>
+      <c r="O60">
+        <v>-4.964673976</v>
+      </c>
+      <c r="P60">
+        <v>-44.682065784</v>
+      </c>
+      <c r="Q60">
+        <v>-44.182065784</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.246563071389281</v>
+      </c>
+      <c r="T60">
+        <v>2.994681812190462</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02550762432073692</v>
+      </c>
+      <c r="W60">
+        <v>0.232708779312208</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2550762432073691</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2405275819845787</v>
+      </c>
+      <c r="C61">
+        <v>-61.85949994055952</v>
+      </c>
+      <c r="D61">
+        <v>202.9426000594405</v>
+      </c>
+      <c r="E61">
+        <v>282.5121</v>
+      </c>
+      <c r="F61">
+        <v>283.9021</v>
+      </c>
+      <c r="G61">
+        <v>19.1</v>
+      </c>
+      <c r="H61">
+        <v>479.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>17.5</v>
+      </c>
+      <c r="K61">
+        <v>0.5</v>
+      </c>
+      <c r="L61">
+        <v>17</v>
+      </c>
+      <c r="M61">
+        <v>67.79582148</v>
+      </c>
+      <c r="N61">
+        <v>-50.79582148</v>
+      </c>
+      <c r="O61">
+        <v>-5.079582148</v>
+      </c>
+      <c r="P61">
+        <v>-45.716239332</v>
+      </c>
+      <c r="Q61">
+        <v>-45.216239332</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2516304633743854</v>
+      </c>
+      <c r="T61">
+        <v>3.067722831999986</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0250752917051312</v>
+      </c>
+      <c r="W61">
+        <v>0.2328120203408147</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2507529170513121</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2425275819845787</v>
+      </c>
+      <c r="C62">
+        <v>-68.66369374861938</v>
+      </c>
+      <c r="D62">
+        <v>200.9503062513806</v>
+      </c>
+      <c r="E62">
+        <v>287.324</v>
+      </c>
+      <c r="F62">
+        <v>288.714</v>
+      </c>
+      <c r="G62">
+        <v>19.1</v>
+      </c>
+      <c r="H62">
+        <v>479.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>17.5</v>
+      </c>
+      <c r="K62">
+        <v>0.5</v>
+      </c>
+      <c r="L62">
+        <v>17</v>
+      </c>
+      <c r="M62">
+        <v>68.9449032</v>
+      </c>
+      <c r="N62">
+        <v>-51.9449032</v>
+      </c>
+      <c r="O62">
+        <v>-5.19449032</v>
+      </c>
+      <c r="P62">
+        <v>-46.75041288</v>
+      </c>
+      <c r="Q62">
+        <v>-46.25041288</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2569512249587451</v>
+      </c>
+      <c r="T62">
+        <v>3.144415902799985</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02465737017671235</v>
+      </c>
+      <c r="W62">
+        <v>0.2329118200018011</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2465737017671236</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2445275819845787</v>
+      </c>
+      <c r="C63">
+        <v>-75.42915101413416</v>
+      </c>
+      <c r="D63">
+        <v>198.9967489858658</v>
+      </c>
+      <c r="E63">
+        <v>292.1359</v>
+      </c>
+      <c r="F63">
+        <v>293.5259</v>
+      </c>
+      <c r="G63">
+        <v>19.1</v>
+      </c>
+      <c r="H63">
+        <v>479.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>17.5</v>
+      </c>
+      <c r="K63">
+        <v>0.5</v>
+      </c>
+      <c r="L63">
+        <v>17</v>
+      </c>
+      <c r="M63">
+        <v>70.09398492</v>
+      </c>
+      <c r="N63">
+        <v>-53.09398492</v>
+      </c>
+      <c r="O63">
+        <v>-5.309398492</v>
+      </c>
+      <c r="P63">
+        <v>-47.784586428</v>
+      </c>
+      <c r="Q63">
+        <v>-47.284586428</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2625448461115334</v>
+      </c>
+      <c r="T63">
+        <v>3.225041951589729</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02425315099348756</v>
+      </c>
+      <c r="W63">
+        <v>0.2330083475427552</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2425315099348756</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2465275819845787</v>
+      </c>
+      <c r="C64">
+        <v>-82.15699060275017</v>
+      </c>
+      <c r="D64">
+        <v>197.0808093972499</v>
+      </c>
+      <c r="E64">
+        <v>296.9478</v>
+      </c>
+      <c r="F64">
+        <v>298.3378</v>
+      </c>
+      <c r="G64">
+        <v>19.1</v>
+      </c>
+      <c r="H64">
+        <v>479.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>17.5</v>
+      </c>
+      <c r="K64">
+        <v>0.5</v>
+      </c>
+      <c r="L64">
+        <v>17</v>
+      </c>
+      <c r="M64">
+        <v>71.24306664000001</v>
+      </c>
+      <c r="N64">
+        <v>-54.24306664000001</v>
+      </c>
+      <c r="O64">
+        <v>-5.424306664000001</v>
+      </c>
+      <c r="P64">
+        <v>-48.81875997600001</v>
+      </c>
+      <c r="Q64">
+        <v>-48.31875997600001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2684328683776264</v>
+      </c>
+      <c r="T64">
+        <v>3.309911476631564</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02386197113875389</v>
+      </c>
+      <c r="W64">
+        <v>0.2331017612920656</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2386197113875389</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2485275819845787</v>
+      </c>
+      <c r="C65">
+        <v>-88.84828870129633</v>
+      </c>
+      <c r="D65">
+        <v>195.2014112987037</v>
+      </c>
+      <c r="E65">
+        <v>301.7597</v>
+      </c>
+      <c r="F65">
+        <v>303.1497</v>
+      </c>
+      <c r="G65">
+        <v>19.1</v>
+      </c>
+      <c r="H65">
+        <v>479.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>17.5</v>
+      </c>
+      <c r="K65">
+        <v>0.5</v>
+      </c>
+      <c r="L65">
+        <v>17</v>
+      </c>
+      <c r="M65">
+        <v>72.39214836000001</v>
+      </c>
+      <c r="N65">
+        <v>-55.39214836000001</v>
+      </c>
+      <c r="O65">
+        <v>-5.539214836000001</v>
+      </c>
+      <c r="P65">
+        <v>-49.85293352400001</v>
+      </c>
+      <c r="Q65">
+        <v>-49.35293352400001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2746391621175622</v>
+      </c>
+      <c r="T65">
+        <v>3.399368543567551</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.023483209692107</v>
+      </c>
+      <c r="W65">
+        <v>0.2331922095255249</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.23483209692107</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2505275819845787</v>
+      </c>
+      <c r="C66">
+        <v>-95.50408083352616</v>
+      </c>
+      <c r="D66">
+        <v>193.3575191664739</v>
+      </c>
+      <c r="E66">
+        <v>306.5716</v>
+      </c>
+      <c r="F66">
+        <v>307.9616</v>
+      </c>
+      <c r="G66">
+        <v>19.1</v>
+      </c>
+      <c r="H66">
+        <v>479.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>17.5</v>
+      </c>
+      <c r="K66">
+        <v>0.5</v>
+      </c>
+      <c r="L66">
+        <v>17</v>
+      </c>
+      <c r="M66">
+        <v>73.54123008000001</v>
+      </c>
+      <c r="N66">
+        <v>-56.54123008000001</v>
+      </c>
+      <c r="O66">
+        <v>-5.654123008000001</v>
+      </c>
+      <c r="P66">
+        <v>-50.88710707200001</v>
+      </c>
+      <c r="Q66">
+        <v>-50.38710707200001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2811902499541612</v>
+      </c>
+      <c r="T66">
+        <v>3.493795447555539</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02311628454066783</v>
+      </c>
+      <c r="W66">
+        <v>0.2332798312516885</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2311628454066783</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2525275819845787</v>
+      </c>
+      <c r="C67">
+        <v>-102.1253637626834</v>
+      </c>
+      <c r="D67">
+        <v>191.5481362373166</v>
+      </c>
+      <c r="E67">
+        <v>311.3835</v>
+      </c>
+      <c r="F67">
+        <v>312.7735</v>
+      </c>
+      <c r="G67">
+        <v>19.1</v>
+      </c>
+      <c r="H67">
+        <v>479.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>17.5</v>
+      </c>
+      <c r="K67">
+        <v>0.5</v>
+      </c>
+      <c r="L67">
+        <v>17</v>
+      </c>
+      <c r="M67">
+        <v>74.6903118</v>
+      </c>
+      <c r="N67">
+        <v>-57.6903118</v>
+      </c>
+      <c r="O67">
+        <v>-5.769031180000001</v>
+      </c>
+      <c r="P67">
+        <v>-51.92128062</v>
+      </c>
+      <c r="Q67">
+        <v>-51.42128062</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2881156856671373</v>
+      </c>
+      <c r="T67">
+        <v>3.593618174628555</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02276064939388833</v>
+      </c>
+      <c r="W67">
+        <v>0.2333647569247395</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2276064939388832</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2545275819845787</v>
+      </c>
+      <c r="C68">
+        <v>-108.713097288236</v>
+      </c>
+      <c r="D68">
+        <v>189.772302711764</v>
+      </c>
+      <c r="E68">
+        <v>316.1954</v>
+      </c>
+      <c r="F68">
+        <v>317.5854</v>
+      </c>
+      <c r="G68">
+        <v>19.1</v>
+      </c>
+      <c r="H68">
+        <v>479.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>17.5</v>
+      </c>
+      <c r="K68">
+        <v>0.5</v>
+      </c>
+      <c r="L68">
+        <v>17</v>
+      </c>
+      <c r="M68">
+        <v>75.83939352</v>
+      </c>
+      <c r="N68">
+        <v>-58.83939352</v>
+      </c>
+      <c r="O68">
+        <v>-5.883939352000001</v>
+      </c>
+      <c r="P68">
+        <v>-52.955454168</v>
+      </c>
+      <c r="Q68">
+        <v>-52.455454168</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2954484999514649</v>
+      </c>
+      <c r="T68">
+        <v>3.699312826823513</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0224157910697385</v>
+      </c>
+      <c r="W68">
+        <v>0.2334471090925465</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.224157910697385</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2565275819845787</v>
+      </c>
+      <c r="C69">
+        <v>-115.2682059435842</v>
+      </c>
+      <c r="D69">
+        <v>188.0290940564159</v>
+      </c>
+      <c r="E69">
+        <v>321.0073</v>
+      </c>
+      <c r="F69">
+        <v>322.3973</v>
+      </c>
+      <c r="G69">
+        <v>19.1</v>
+      </c>
+      <c r="H69">
+        <v>479.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>17.5</v>
+      </c>
+      <c r="K69">
+        <v>0.5</v>
+      </c>
+      <c r="L69">
+        <v>17</v>
+      </c>
+      <c r="M69">
+        <v>76.98847524000001</v>
+      </c>
+      <c r="N69">
+        <v>-59.98847524000001</v>
+      </c>
+      <c r="O69">
+        <v>-5.998847524000002</v>
+      </c>
+      <c r="P69">
+        <v>-53.98962771600002</v>
+      </c>
+      <c r="Q69">
+        <v>-53.48962771600002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3032257272227213</v>
+      </c>
+      <c r="T69">
+        <v>3.811413215515135</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02208122702392151</v>
+      </c>
+      <c r="W69">
+        <v>0.2335270029866876</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.220812270239215</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2585275819845787</v>
+      </c>
+      <c r="C70">
+        <v>-121.7915806010499</v>
+      </c>
+      <c r="D70">
+        <v>186.3176193989501</v>
+      </c>
+      <c r="E70">
+        <v>325.8192</v>
+      </c>
+      <c r="F70">
+        <v>327.2092</v>
+      </c>
+      <c r="G70">
+        <v>19.1</v>
+      </c>
+      <c r="H70">
+        <v>479.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>17.5</v>
+      </c>
+      <c r="K70">
+        <v>0.5</v>
+      </c>
+      <c r="L70">
+        <v>17</v>
+      </c>
+      <c r="M70">
+        <v>78.13755696000001</v>
+      </c>
+      <c r="N70">
+        <v>-61.13755696000001</v>
+      </c>
+      <c r="O70">
+        <v>-6.113755696000002</v>
+      </c>
+      <c r="P70">
+        <v>-55.02380126400001</v>
+      </c>
+      <c r="Q70">
+        <v>-54.52380126400001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3114890311984314</v>
+      </c>
+      <c r="T70">
+        <v>3.930519878499982</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02175650309709913</v>
+      </c>
+      <c r="W70">
+        <v>0.2336045470604128</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2175650309709913</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2605275819845787</v>
+      </c>
+      <c r="C71">
+        <v>-128.2840799900056</v>
+      </c>
+      <c r="D71">
+        <v>184.6370200099944</v>
+      </c>
+      <c r="E71">
+        <v>330.6311000000001</v>
+      </c>
+      <c r="F71">
+        <v>332.0211</v>
+      </c>
+      <c r="G71">
+        <v>19.1</v>
+      </c>
+      <c r="H71">
+        <v>479.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>17.5</v>
+      </c>
+      <c r="K71">
+        <v>0.5</v>
+      </c>
+      <c r="L71">
+        <v>17</v>
+      </c>
+      <c r="M71">
+        <v>79.28663868000001</v>
+      </c>
+      <c r="N71">
+        <v>-62.28663868000001</v>
+      </c>
+      <c r="O71">
+        <v>-6.228663868000002</v>
+      </c>
+      <c r="P71">
+        <v>-56.05797481200001</v>
+      </c>
+      <c r="Q71">
+        <v>-55.55797481200001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3202854515596711</v>
+      </c>
+      <c r="T71">
+        <v>4.057310842322563</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02144119145801074</v>
+      </c>
+      <c r="W71">
+        <v>0.2336798434798271</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2144119145801073</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2625275819845787</v>
+      </c>
+      <c r="C72">
+        <v>-134.7465321335739</v>
+      </c>
+      <c r="D72">
+        <v>182.9864678664262</v>
+      </c>
+      <c r="E72">
+        <v>335.443</v>
+      </c>
+      <c r="F72">
+        <v>336.833</v>
+      </c>
+      <c r="G72">
+        <v>19.1</v>
+      </c>
+      <c r="H72">
+        <v>479.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>17.5</v>
+      </c>
+      <c r="K72">
+        <v>0.5</v>
+      </c>
+      <c r="L72">
+        <v>17</v>
+      </c>
+      <c r="M72">
+        <v>80.43572040000001</v>
+      </c>
+      <c r="N72">
+        <v>-63.43572040000001</v>
+      </c>
+      <c r="O72">
+        <v>-6.343572040000002</v>
+      </c>
+      <c r="P72">
+        <v>-57.09214836000001</v>
+      </c>
+      <c r="Q72">
+        <v>-56.59214836000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3296682999449935</v>
+      </c>
+      <c r="T72">
+        <v>4.192554537066648</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0211348887228963</v>
+      </c>
+      <c r="W72">
+        <v>0.2337529885729724</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2113488872289629</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2645275819845787</v>
+      </c>
+      <c r="C73">
+        <v>-141.1797357089511</v>
+      </c>
+      <c r="D73">
+        <v>181.365164291049</v>
+      </c>
+      <c r="E73">
+        <v>340.2549</v>
+      </c>
+      <c r="F73">
+        <v>341.6449</v>
+      </c>
+      <c r="G73">
+        <v>19.1</v>
+      </c>
+      <c r="H73">
+        <v>479.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>17.5</v>
+      </c>
+      <c r="K73">
+        <v>0.5</v>
+      </c>
+      <c r="L73">
+        <v>17</v>
+      </c>
+      <c r="M73">
+        <v>81.58480212000001</v>
+      </c>
+      <c r="N73">
+        <v>-64.58480212000001</v>
+      </c>
+      <c r="O73">
+        <v>-6.458480212000001</v>
+      </c>
+      <c r="P73">
+        <v>-58.12632190800001</v>
+      </c>
+      <c r="Q73">
+        <v>-57.62632190800001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.339698241322407</v>
+      </c>
+      <c r="T73">
+        <v>4.337125383172394</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02083721423384143</v>
+      </c>
+      <c r="W73">
+        <v>0.2338240732409587</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2083721423384143</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2665275819845787</v>
+      </c>
+      <c r="C74">
+        <v>-147.5844613360491</v>
+      </c>
+      <c r="D74">
+        <v>179.7723386639509</v>
+      </c>
+      <c r="E74">
+        <v>345.0668</v>
+      </c>
+      <c r="F74">
+        <v>346.4568</v>
+      </c>
+      <c r="G74">
+        <v>19.1</v>
+      </c>
+      <c r="H74">
+        <v>479.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>17.5</v>
+      </c>
+      <c r="K74">
+        <v>0.5</v>
+      </c>
+      <c r="L74">
+        <v>17</v>
+      </c>
+      <c r="M74">
+        <v>82.73388384</v>
+      </c>
+      <c r="N74">
+        <v>-65.73388384</v>
+      </c>
+      <c r="O74">
+        <v>-6.573388384000001</v>
+      </c>
+      <c r="P74">
+        <v>-59.16049545600001</v>
+      </c>
+      <c r="Q74">
+        <v>-58.66049545600001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3504446070839216</v>
+      </c>
+      <c r="T74">
+        <v>4.492022718285694</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02054780848059363</v>
+      </c>
+      <c r="W74">
+        <v>0.2338931833348342</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2054780848059362</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2685275819845787</v>
+      </c>
+      <c r="C75">
+        <v>-153.9614527988236</v>
+      </c>
+      <c r="D75">
+        <v>178.2072472011764</v>
+      </c>
+      <c r="E75">
+        <v>349.8787</v>
+      </c>
+      <c r="F75">
+        <v>351.2687</v>
+      </c>
+      <c r="G75">
+        <v>19.1</v>
+      </c>
+      <c r="H75">
+        <v>479.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>17.5</v>
+      </c>
+      <c r="K75">
+        <v>0.5</v>
+      </c>
+      <c r="L75">
+        <v>17</v>
+      </c>
+      <c r="M75">
+        <v>83.88296556</v>
+      </c>
+      <c r="N75">
+        <v>-66.88296556</v>
+      </c>
+      <c r="O75">
+        <v>-6.688296556000001</v>
+      </c>
+      <c r="P75">
+        <v>-60.194669004</v>
+      </c>
+      <c r="Q75">
+        <v>-59.694669004</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3619869999388816</v>
+      </c>
+      <c r="T75">
+        <v>4.658393930074052</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02026633165209234</v>
+      </c>
+      <c r="W75">
+        <v>0.2339604000014804</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2026633165209234</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2705275819845787</v>
+      </c>
+      <c r="C76">
+        <v>-160.3114282033564</v>
+      </c>
+      <c r="D76">
+        <v>176.6691717966436</v>
+      </c>
+      <c r="E76">
+        <v>354.6906</v>
+      </c>
+      <c r="F76">
+        <v>356.0806</v>
+      </c>
+      <c r="G76">
+        <v>19.1</v>
+      </c>
+      <c r="H76">
+        <v>479.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>17.5</v>
+      </c>
+      <c r="K76">
+        <v>0.5</v>
+      </c>
+      <c r="L76">
+        <v>17</v>
+      </c>
+      <c r="M76">
+        <v>85.03204728</v>
+      </c>
+      <c r="N76">
+        <v>-68.03204728</v>
+      </c>
+      <c r="O76">
+        <v>-6.803204728000001</v>
+      </c>
+      <c r="P76">
+        <v>-61.228842552</v>
+      </c>
+      <c r="Q76">
+        <v>-60.728842552</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3744172691673001</v>
+      </c>
+      <c r="T76">
+        <v>4.837562927384592</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.01999246230544245</v>
+      </c>
+      <c r="W76">
+        <v>0.2340258000014603</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1999246230544245</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2725275819845787</v>
+      </c>
+      <c r="C77">
+        <v>-166.6350810764795</v>
+      </c>
+      <c r="D77">
+        <v>175.1574189235205</v>
+      </c>
+      <c r="E77">
+        <v>359.5025</v>
+      </c>
+      <c r="F77">
+        <v>360.8925</v>
+      </c>
+      <c r="G77">
+        <v>19.1</v>
+      </c>
+      <c r="H77">
+        <v>479.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>17.5</v>
+      </c>
+      <c r="K77">
+        <v>0.5</v>
+      </c>
+      <c r="L77">
+        <v>17</v>
+      </c>
+      <c r="M77">
+        <v>86.181129</v>
+      </c>
+      <c r="N77">
+        <v>-69.181129</v>
+      </c>
+      <c r="O77">
+        <v>-6.918112900000001</v>
+      </c>
+      <c r="P77">
+        <v>-62.2630161</v>
+      </c>
+      <c r="Q77">
+        <v>-61.7630161</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3878419599339921</v>
+      </c>
+      <c r="T77">
+        <v>5.031065444479976</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.01972589614136988</v>
+      </c>
+      <c r="W77">
+        <v>0.2340894560014409</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1972589614136988</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2745275819845787</v>
+      </c>
+      <c r="C78">
+        <v>-172.9330814084719</v>
+      </c>
+      <c r="D78">
+        <v>173.6713185915281</v>
+      </c>
+      <c r="E78">
+        <v>364.3144</v>
+      </c>
+      <c r="F78">
+        <v>365.7044</v>
+      </c>
+      <c r="G78">
+        <v>19.1</v>
+      </c>
+      <c r="H78">
+        <v>479.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>17.5</v>
+      </c>
+      <c r="K78">
+        <v>0.5</v>
+      </c>
+      <c r="L78">
+        <v>17</v>
+      </c>
+      <c r="M78">
+        <v>87.33021072000001</v>
+      </c>
+      <c r="N78">
+        <v>-70.33021072000001</v>
+      </c>
+      <c r="O78">
+        <v>-7.033021072000001</v>
+      </c>
+      <c r="P78">
+        <v>-63.29718964800001</v>
+      </c>
+      <c r="Q78">
+        <v>-62.79718964800001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4023853749312418</v>
+      </c>
+      <c r="T78">
+        <v>5.24069317133331</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01946634487635186</v>
+      </c>
+      <c r="W78">
+        <v>0.2341514368435272</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1946634487635186</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2765275819845787</v>
+      </c>
+      <c r="C79">
+        <v>-179.206076643124</v>
+      </c>
+      <c r="D79">
+        <v>172.210223356876</v>
+      </c>
+      <c r="E79">
+        <v>369.1263</v>
+      </c>
+      <c r="F79">
+        <v>370.5163</v>
+      </c>
+      <c r="G79">
+        <v>19.1</v>
+      </c>
+      <c r="H79">
+        <v>479.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>17.5</v>
+      </c>
+      <c r="K79">
+        <v>0.5</v>
+      </c>
+      <c r="L79">
+        <v>17</v>
+      </c>
+      <c r="M79">
+        <v>88.47929244000001</v>
+      </c>
+      <c r="N79">
+        <v>-71.47929244000001</v>
+      </c>
+      <c r="O79">
+        <v>-7.147929244000001</v>
+      </c>
+      <c r="P79">
+        <v>-64.33136319600001</v>
+      </c>
+      <c r="Q79">
+        <v>-63.83136319600001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.418193434710861</v>
+      </c>
+      <c r="T79">
+        <v>5.468549396173888</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.019213535202633</v>
+      </c>
+      <c r="W79">
+        <v>0.2342118077936113</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.19213535202633</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2785275819845787</v>
+      </c>
+      <c r="C80">
+        <v>-185.4546926182425</v>
+      </c>
+      <c r="D80">
+        <v>170.7735073817575</v>
+      </c>
+      <c r="E80">
+        <v>373.9382000000001</v>
+      </c>
+      <c r="F80">
+        <v>375.3282</v>
+      </c>
+      <c r="G80">
+        <v>19.1</v>
+      </c>
+      <c r="H80">
+        <v>479.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>17.5</v>
+      </c>
+      <c r="K80">
+        <v>0.5</v>
+      </c>
+      <c r="L80">
+        <v>17</v>
+      </c>
+      <c r="M80">
+        <v>89.62837416000001</v>
+      </c>
+      <c r="N80">
+        <v>-72.62837416000001</v>
+      </c>
+      <c r="O80">
+        <v>-7.262837416000001</v>
+      </c>
+      <c r="P80">
+        <v>-65.36553674400001</v>
+      </c>
+      <c r="Q80">
+        <v>-64.86553674400001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.435438590834082</v>
+      </c>
+      <c r="T80">
+        <v>5.717119823272701</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01896720782824027</v>
+      </c>
+      <c r="W80">
+        <v>0.2342706307706162</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1896720782824027</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2805275819845787</v>
+      </c>
+      <c r="C81">
+        <v>-191.6795344594648</v>
+      </c>
+      <c r="D81">
+        <v>169.3605655405352</v>
+      </c>
+      <c r="E81">
+        <v>378.7501</v>
+      </c>
+      <c r="F81">
+        <v>380.1401</v>
+      </c>
+      <c r="G81">
+        <v>19.1</v>
+      </c>
+      <c r="H81">
+        <v>479.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>17.5</v>
+      </c>
+      <c r="K81">
+        <v>0.5</v>
+      </c>
+      <c r="L81">
+        <v>17</v>
+      </c>
+      <c r="M81">
+        <v>90.77745588000001</v>
+      </c>
+      <c r="N81">
+        <v>-73.77745588000001</v>
+      </c>
+      <c r="O81">
+        <v>-7.377745588000001</v>
+      </c>
+      <c r="P81">
+        <v>-66.39971029200001</v>
+      </c>
+      <c r="Q81">
+        <v>-65.89971029200001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4543261427785622</v>
+      </c>
+      <c r="T81">
+        <v>5.989363624380927</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01872711658990811</v>
+      </c>
+      <c r="W81">
+        <v>0.23432796455833</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1872711658990811</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2825275819845787</v>
+      </c>
+      <c r="C82">
+        <v>-197.8811874300683</v>
+      </c>
+      <c r="D82">
+        <v>167.9708125699317</v>
+      </c>
+      <c r="E82">
+        <v>383.562</v>
+      </c>
+      <c r="F82">
+        <v>384.952</v>
+      </c>
+      <c r="G82">
+        <v>19.1</v>
+      </c>
+      <c r="H82">
+        <v>479.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>17.5</v>
+      </c>
+      <c r="K82">
+        <v>0.5</v>
+      </c>
+      <c r="L82">
+        <v>17</v>
+      </c>
+      <c r="M82">
+        <v>91.9265376</v>
+      </c>
+      <c r="N82">
+        <v>-74.9265376</v>
+      </c>
+      <c r="O82">
+        <v>-7.49265376</v>
+      </c>
+      <c r="P82">
+        <v>-67.43388384000001</v>
+      </c>
+      <c r="Q82">
+        <v>-66.93388384000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4751024499174903</v>
+      </c>
+      <c r="T82">
+        <v>6.288831805599973</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01849302763253427</v>
+      </c>
+      <c r="W82">
+        <v>0.2343838650013508</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1849302763253426</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2845275819845787</v>
+      </c>
+      <c r="C83">
+        <v>-204.0602177392778</v>
+      </c>
+      <c r="D83">
+        <v>166.6036822607223</v>
+      </c>
+      <c r="E83">
+        <v>388.3739</v>
+      </c>
+      <c r="F83">
+        <v>389.7639</v>
+      </c>
+      <c r="G83">
+        <v>19.1</v>
+      </c>
+      <c r="H83">
+        <v>479.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>17.5</v>
+      </c>
+      <c r="K83">
+        <v>0.5</v>
+      </c>
+      <c r="L83">
+        <v>17</v>
+      </c>
+      <c r="M83">
+        <v>93.07561932000002</v>
+      </c>
+      <c r="N83">
+        <v>-76.07561932000002</v>
+      </c>
+      <c r="O83">
+        <v>-7.607561932000002</v>
+      </c>
+      <c r="P83">
+        <v>-68.46805738800002</v>
+      </c>
+      <c r="Q83">
+        <v>-67.96805738800002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4980657367552529</v>
+      </c>
+      <c r="T83">
+        <v>6.619822953263129</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01826471864941655</v>
+      </c>
+      <c r="W83">
+        <v>0.2344383851865193</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1826471864941656</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2865275819845787</v>
+      </c>
+      <c r="C84">
+        <v>-210.217173311419</v>
+      </c>
+      <c r="D84">
+        <v>165.258626688581</v>
+      </c>
+      <c r="E84">
+        <v>393.1858</v>
+      </c>
+      <c r="F84">
+        <v>394.5758</v>
+      </c>
+      <c r="G84">
+        <v>19.1</v>
+      </c>
+      <c r="H84">
+        <v>479.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>17.5</v>
+      </c>
+      <c r="K84">
+        <v>0.5</v>
+      </c>
+      <c r="L84">
+        <v>17</v>
+      </c>
+      <c r="M84">
+        <v>94.22470104000001</v>
+      </c>
+      <c r="N84">
+        <v>-77.22470104000001</v>
+      </c>
+      <c r="O84">
+        <v>-7.722470104000002</v>
+      </c>
+      <c r="P84">
+        <v>-69.50223093600002</v>
+      </c>
+      <c r="Q84">
+        <v>-69.00223093600002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5235804999083224</v>
+      </c>
+      <c r="T84">
+        <v>6.98759089511108</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01804197817808221</v>
+      </c>
+      <c r="W84">
+        <v>0.234491575611074</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1804197817808221</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2885275819845787</v>
+      </c>
+      <c r="C85">
+        <v>-216.352584518113</v>
+      </c>
+      <c r="D85">
+        <v>163.9351154818871</v>
+      </c>
+      <c r="E85">
+        <v>397.9977000000001</v>
+      </c>
+      <c r="F85">
+        <v>399.3877000000001</v>
+      </c>
+      <c r="G85">
+        <v>19.1</v>
+      </c>
+      <c r="H85">
+        <v>479.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>17.5</v>
+      </c>
+      <c r="K85">
+        <v>0.5</v>
+      </c>
+      <c r="L85">
+        <v>17</v>
+      </c>
+      <c r="M85">
+        <v>95.37378276000001</v>
+      </c>
+      <c r="N85">
+        <v>-78.37378276000001</v>
+      </c>
+      <c r="O85">
+        <v>-7.837378276000002</v>
+      </c>
+      <c r="P85">
+        <v>-70.53640448400002</v>
+      </c>
+      <c r="Q85">
+        <v>-70.03640448400002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5520969999029297</v>
+      </c>
+      <c r="T85">
+        <v>7.398625653647027</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01782460494702098</v>
+      </c>
+      <c r="W85">
+        <v>0.2345434843386514</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1782460494702097</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2905275819845787</v>
+      </c>
+      <c r="C86">
+        <v>-222.4669648755648</v>
+      </c>
+      <c r="D86">
+        <v>162.6326351244352</v>
+      </c>
+      <c r="E86">
+        <v>402.8096</v>
+      </c>
+      <c r="F86">
+        <v>404.1996</v>
+      </c>
+      <c r="G86">
+        <v>19.1</v>
+      </c>
+      <c r="H86">
+        <v>479.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>17.5</v>
+      </c>
+      <c r="K86">
+        <v>0.5</v>
+      </c>
+      <c r="L86">
+        <v>17</v>
+      </c>
+      <c r="M86">
+        <v>96.52286448</v>
+      </c>
+      <c r="N86">
+        <v>-79.52286448</v>
+      </c>
+      <c r="O86">
+        <v>-7.952286448</v>
+      </c>
+      <c r="P86">
+        <v>-71.570578032</v>
+      </c>
+      <c r="Q86">
+        <v>-71.070578032</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5841780623968627</v>
+      </c>
+      <c r="T86">
+        <v>7.861039756999963</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01761240726908025</v>
+      </c>
+      <c r="W86">
+        <v>0.2345941571441437</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1761240726908025</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2925275819845787</v>
+      </c>
+      <c r="C87">
+        <v>-228.5608117088761</v>
+      </c>
+      <c r="D87">
+        <v>161.3506882911239</v>
+      </c>
+      <c r="E87">
+        <v>407.6215</v>
+      </c>
+      <c r="F87">
+        <v>409.0115</v>
+      </c>
+      <c r="G87">
+        <v>19.1</v>
+      </c>
+      <c r="H87">
+        <v>479.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>17.5</v>
+      </c>
+      <c r="K87">
+        <v>0.5</v>
+      </c>
+      <c r="L87">
+        <v>17</v>
+      </c>
+      <c r="M87">
+        <v>97.67194620000001</v>
+      </c>
+      <c r="N87">
+        <v>-80.67194620000001</v>
+      </c>
+      <c r="O87">
+        <v>-8.06719462</v>
+      </c>
+      <c r="P87">
+        <v>-72.60475158000001</v>
+      </c>
+      <c r="Q87">
+        <v>-72.10475158000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.620536599889987</v>
+      </c>
+      <c r="T87">
+        <v>8.385109074133295</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0174052024776793</v>
+      </c>
+      <c r="W87">
+        <v>0.2346436376483302</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.174052024776793</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2945275819845787</v>
+      </c>
+      <c r="C88">
+        <v>-234.6346067851832</v>
+      </c>
+      <c r="D88">
+        <v>160.0887932148168</v>
+      </c>
+      <c r="E88">
+        <v>412.4334</v>
+      </c>
+      <c r="F88">
+        <v>413.8234</v>
+      </c>
+      <c r="G88">
+        <v>19.1</v>
+      </c>
+      <c r="H88">
+        <v>479.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>17.5</v>
+      </c>
+      <c r="K88">
+        <v>0.5</v>
+      </c>
+      <c r="L88">
+        <v>17</v>
+      </c>
+      <c r="M88">
+        <v>98.82102792000001</v>
+      </c>
+      <c r="N88">
+        <v>-81.82102792000001</v>
+      </c>
+      <c r="O88">
+        <v>-8.182102792</v>
+      </c>
+      <c r="P88">
+        <v>-73.63892512800001</v>
+      </c>
+      <c r="Q88">
+        <v>-73.13892512800001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6620892141678432</v>
+      </c>
+      <c r="T88">
+        <v>8.984045436571387</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01720281640235746</v>
+      </c>
+      <c r="W88">
+        <v>0.234691967443117</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1720281640235746</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2965275819845787</v>
+      </c>
+      <c r="C89">
+        <v>-240.6888169173164</v>
+      </c>
+      <c r="D89">
+        <v>158.8464830826836</v>
+      </c>
+      <c r="E89">
+        <v>417.2453</v>
+      </c>
+      <c r="F89">
+        <v>418.6353</v>
+      </c>
+      <c r="G89">
+        <v>19.1</v>
+      </c>
+      <c r="H89">
+        <v>479.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>17.5</v>
+      </c>
+      <c r="K89">
+        <v>0.5</v>
+      </c>
+      <c r="L89">
+        <v>17</v>
+      </c>
+      <c r="M89">
+        <v>99.97010964</v>
+      </c>
+      <c r="N89">
+        <v>-82.97010964</v>
+      </c>
+      <c r="O89">
+        <v>-8.297010964</v>
+      </c>
+      <c r="P89">
+        <v>-74.67309867600001</v>
+      </c>
+      <c r="Q89">
+        <v>-74.17309867600001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7100345383346001</v>
+      </c>
+      <c r="T89">
+        <v>9.675125854769185</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01700508288049128</v>
+      </c>
+      <c r="W89">
+        <v>0.2347391862081387</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1700508288049127</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2985275819845787</v>
+      </c>
+      <c r="C90">
+        <v>-246.7238945395692</v>
+      </c>
+      <c r="D90">
+        <v>157.6233054604308</v>
+      </c>
+      <c r="E90">
+        <v>422.0572</v>
+      </c>
+      <c r="F90">
+        <v>423.4472</v>
+      </c>
+      <c r="G90">
+        <v>19.1</v>
+      </c>
+      <c r="H90">
+        <v>479.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>17.5</v>
+      </c>
+      <c r="K90">
+        <v>0.5</v>
+      </c>
+      <c r="L90">
+        <v>17</v>
+      </c>
+      <c r="M90">
+        <v>101.11919136</v>
+      </c>
+      <c r="N90">
+        <v>-84.11919136</v>
+      </c>
+      <c r="O90">
+        <v>-8.411919136</v>
+      </c>
+      <c r="P90">
+        <v>-75.70727222400001</v>
+      </c>
+      <c r="Q90">
+        <v>-75.20727222400001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7659707498624837</v>
+      </c>
+      <c r="T90">
+        <v>10.48138634266662</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01681184330230388</v>
+      </c>
+      <c r="W90">
+        <v>0.2347853318194098</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1681184330230387</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3005275819845787</v>
+      </c>
+      <c r="C91">
+        <v>-252.7402782570683</v>
+      </c>
+      <c r="D91">
+        <v>156.4188217429317</v>
+      </c>
+      <c r="E91">
+        <v>426.8691</v>
+      </c>
+      <c r="F91">
+        <v>428.2591</v>
+      </c>
+      <c r="G91">
+        <v>19.1</v>
+      </c>
+      <c r="H91">
+        <v>479.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>17.5</v>
+      </c>
+      <c r="K91">
+        <v>0.5</v>
+      </c>
+      <c r="L91">
+        <v>17</v>
+      </c>
+      <c r="M91">
+        <v>102.26827308</v>
+      </c>
+      <c r="N91">
+        <v>-85.26827308</v>
+      </c>
+      <c r="O91">
+        <v>-8.526827308</v>
+      </c>
+      <c r="P91">
+        <v>-76.74144577200001</v>
+      </c>
+      <c r="Q91">
+        <v>-76.24144577200001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.832077181668164</v>
+      </c>
+      <c r="T91">
+        <v>11.4342396465454</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01662294618654765</v>
+      </c>
+      <c r="W91">
+        <v>0.2348304404506524</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1662294618654765</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3025275819845787</v>
+      </c>
+      <c r="C92">
+        <v>-258.7383933701473</v>
+      </c>
+      <c r="D92">
+        <v>155.2326066298527</v>
+      </c>
+      <c r="E92">
+        <v>431.681</v>
+      </c>
+      <c r="F92">
+        <v>433.071</v>
+      </c>
+      <c r="G92">
+        <v>19.1</v>
+      </c>
+      <c r="H92">
+        <v>479.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>17.5</v>
+      </c>
+      <c r="K92">
+        <v>0.5</v>
+      </c>
+      <c r="L92">
+        <v>17</v>
+      </c>
+      <c r="M92">
+        <v>103.4173548</v>
+      </c>
+      <c r="N92">
+        <v>-86.41735480000001</v>
+      </c>
+      <c r="O92">
+        <v>-8.641735480000001</v>
+      </c>
+      <c r="P92">
+        <v>-77.77561932</v>
+      </c>
+      <c r="Q92">
+        <v>-77.27561932</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.9114048998349804</v>
+      </c>
+      <c r="T92">
+        <v>12.57766361119994</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0164382467844749</v>
+      </c>
+      <c r="W92">
+        <v>0.2348745466678674</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.164382467844749</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3045275819845787</v>
+      </c>
+      <c r="C93">
+        <v>-264.7186523750387</v>
+      </c>
+      <c r="D93">
+        <v>154.0642476249613</v>
+      </c>
+      <c r="E93">
+        <v>436.4929</v>
+      </c>
+      <c r="F93">
+        <v>437.8829</v>
+      </c>
+      <c r="G93">
+        <v>19.1</v>
+      </c>
+      <c r="H93">
+        <v>479.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>17.5</v>
+      </c>
+      <c r="K93">
+        <v>0.5</v>
+      </c>
+      <c r="L93">
+        <v>17</v>
+      </c>
+      <c r="M93">
+        <v>104.56643652</v>
+      </c>
+      <c r="N93">
+        <v>-87.56643652000001</v>
+      </c>
+      <c r="O93">
+        <v>-8.756643652000001</v>
+      </c>
+      <c r="P93">
+        <v>-78.80979286800002</v>
+      </c>
+      <c r="Q93">
+        <v>-78.30979286800002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.008360999816645</v>
+      </c>
+      <c r="T93">
+        <v>13.97518179022216</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01625760670992023</v>
+      </c>
+      <c r="W93">
+        <v>0.2349176835176711</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1625760670992024</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3065275819845787</v>
+      </c>
+      <c r="C94">
+        <v>-270.6814554421261</v>
+      </c>
+      <c r="D94">
+        <v>152.913344557874</v>
+      </c>
+      <c r="E94">
+        <v>441.3048000000001</v>
+      </c>
+      <c r="F94">
+        <v>442.6948</v>
+      </c>
+      <c r="G94">
+        <v>19.1</v>
+      </c>
+      <c r="H94">
+        <v>479.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>17.5</v>
+      </c>
+      <c r="K94">
+        <v>0.5</v>
+      </c>
+      <c r="L94">
+        <v>17</v>
+      </c>
+      <c r="M94">
+        <v>105.71551824</v>
+      </c>
+      <c r="N94">
+        <v>-88.71551824000002</v>
+      </c>
+      <c r="O94">
+        <v>-8.871551824000003</v>
+      </c>
+      <c r="P94">
+        <v>-79.84396641600001</v>
+      </c>
+      <c r="Q94">
+        <v>-79.34396641600001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.129556124793726</v>
+      </c>
+      <c r="T94">
+        <v>15.72207951399994</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01608089359350805</v>
+      </c>
+      <c r="W94">
+        <v>0.2349598826098703</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1608089359350805</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3085275819845787</v>
+      </c>
+      <c r="C95">
+        <v>-276.6271908729172</v>
+      </c>
+      <c r="D95">
+        <v>151.7795091270828</v>
+      </c>
+      <c r="E95">
+        <v>446.1167</v>
+      </c>
+      <c r="F95">
+        <v>447.5067</v>
+      </c>
+      <c r="G95">
+        <v>19.1</v>
+      </c>
+      <c r="H95">
+        <v>479.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>17.5</v>
+      </c>
+      <c r="K95">
+        <v>0.5</v>
+      </c>
+      <c r="L95">
+        <v>17</v>
+      </c>
+      <c r="M95">
+        <v>106.86459996</v>
+      </c>
+      <c r="N95">
+        <v>-89.86459996000001</v>
+      </c>
+      <c r="O95">
+        <v>-8.986459996000001</v>
+      </c>
+      <c r="P95">
+        <v>-80.87813996400001</v>
+      </c>
+      <c r="Q95">
+        <v>-80.37813996400001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.285378428335687</v>
+      </c>
+      <c r="T95">
+        <v>17.96809087314278</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01590798075916926</v>
+      </c>
+      <c r="W95">
+        <v>0.2350011741947104</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1590798075916926</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3105275819845787</v>
+      </c>
+      <c r="C96">
+        <v>-282.556235536838</v>
+      </c>
+      <c r="D96">
+        <v>150.662364463162</v>
+      </c>
+      <c r="E96">
+        <v>450.9286</v>
+      </c>
+      <c r="F96">
+        <v>452.3186</v>
+      </c>
+      <c r="G96">
+        <v>19.1</v>
+      </c>
+      <c r="H96">
+        <v>479.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>17.5</v>
+      </c>
+      <c r="K96">
+        <v>0.5</v>
+      </c>
+      <c r="L96">
+        <v>17</v>
+      </c>
+      <c r="M96">
+        <v>108.01368168</v>
+      </c>
+      <c r="N96">
+        <v>-91.01368168</v>
+      </c>
+      <c r="O96">
+        <v>-9.101368168</v>
+      </c>
+      <c r="P96">
+        <v>-81.912313512</v>
+      </c>
+      <c r="Q96">
+        <v>-81.412313512</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.493141499724969</v>
+      </c>
+      <c r="T96">
+        <v>20.96277268533326</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01573874692130576</v>
+      </c>
+      <c r="W96">
+        <v>0.2350415872351922</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1573874692130576</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3125275819845788</v>
+      </c>
+      <c r="C97">
+        <v>-288.4689552888764</v>
+      </c>
+      <c r="D97">
+        <v>149.5615447111236</v>
+      </c>
+      <c r="E97">
+        <v>455.7405000000001</v>
+      </c>
+      <c r="F97">
+        <v>457.1305</v>
+      </c>
+      <c r="G97">
+        <v>19.1</v>
+      </c>
+      <c r="H97">
+        <v>479.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>17.5</v>
+      </c>
+      <c r="K97">
+        <v>0.5</v>
+      </c>
+      <c r="L97">
+        <v>17</v>
+      </c>
+      <c r="M97">
+        <v>109.1627634</v>
+      </c>
+      <c r="N97">
+        <v>-92.16276340000002</v>
+      </c>
+      <c r="O97">
+        <v>-9.216276340000002</v>
+      </c>
+      <c r="P97">
+        <v>-82.94648706000001</v>
+      </c>
+      <c r="Q97">
+        <v>-82.44648706000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.784009799669963</v>
+      </c>
+      <c r="T97">
+        <v>25.15532722239992</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01557307590108148</v>
+      </c>
+      <c r="W97">
+        <v>0.2350811494748218</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1557307590108148</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3145275819845787</v>
+      </c>
+      <c r="C98">
+        <v>-294.3657053690506</v>
+      </c>
+      <c r="D98">
+        <v>148.4766946309493</v>
+      </c>
+      <c r="E98">
+        <v>460.5524</v>
+      </c>
+      <c r="F98">
+        <v>461.9424</v>
+      </c>
+      <c r="G98">
+        <v>19.1</v>
+      </c>
+      <c r="H98">
+        <v>479.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>17.5</v>
+      </c>
+      <c r="K98">
+        <v>0.5</v>
+      </c>
+      <c r="L98">
+        <v>17</v>
+      </c>
+      <c r="M98">
+        <v>110.31184512</v>
+      </c>
+      <c r="N98">
+        <v>-93.31184512</v>
+      </c>
+      <c r="O98">
+        <v>-9.331184512</v>
+      </c>
+      <c r="P98">
+        <v>-83.98066060799999</v>
+      </c>
+      <c r="Q98">
+        <v>-83.48066060799999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.220312249587449</v>
+      </c>
+      <c r="T98">
+        <v>31.44415902799983</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01541085636044522</v>
+      </c>
+      <c r="W98">
+        <v>0.2351198875011257</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1541085636044522</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3165275819845788</v>
+      </c>
+      <c r="C99">
+        <v>-300.2468307846178</v>
+      </c>
+      <c r="D99">
+        <v>147.4074692153822</v>
+      </c>
+      <c r="E99">
+        <v>465.3643</v>
+      </c>
+      <c r="F99">
+        <v>466.7543</v>
+      </c>
+      <c r="G99">
+        <v>19.1</v>
+      </c>
+      <c r="H99">
+        <v>479.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>17.5</v>
+      </c>
+      <c r="K99">
+        <v>0.5</v>
+      </c>
+      <c r="L99">
+        <v>17</v>
+      </c>
+      <c r="M99">
+        <v>111.46092684</v>
+      </c>
+      <c r="N99">
+        <v>-94.46092684</v>
+      </c>
+      <c r="O99">
+        <v>-9.446092684</v>
+      </c>
+      <c r="P99">
+        <v>-85.01483415600001</v>
+      </c>
+      <c r="Q99">
+        <v>-84.51483415600001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.947482999449933</v>
+      </c>
+      <c r="T99">
+        <v>41.92554537066644</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01525198155260558</v>
+      </c>
+      <c r="W99">
+        <v>0.2351578268052378</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1525198155260558</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3185275819845787</v>
+      </c>
+      <c r="C100">
+        <v>-306.1126666758843</v>
+      </c>
+      <c r="D100">
+        <v>146.3535333241157</v>
+      </c>
+      <c r="E100">
+        <v>470.1762</v>
+      </c>
+      <c r="F100">
+        <v>471.5662</v>
+      </c>
+      <c r="G100">
+        <v>19.1</v>
+      </c>
+      <c r="H100">
+        <v>479.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>17.5</v>
+      </c>
+      <c r="K100">
+        <v>0.5</v>
+      </c>
+      <c r="L100">
+        <v>17</v>
+      </c>
+      <c r="M100">
+        <v>112.61000856</v>
+      </c>
+      <c r="N100">
+        <v>-95.61000856</v>
+      </c>
+      <c r="O100">
+        <v>-9.561000856</v>
+      </c>
+      <c r="P100">
+        <v>-86.04900770399999</v>
+      </c>
+      <c r="Q100">
+        <v>-85.54900770399999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.401824499174898</v>
+      </c>
+      <c r="T100">
+        <v>62.88831805599965</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01509634908778307</v>
+      </c>
+      <c r="W100">
+        <v>0.2351949918378374</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1509634908778307</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3205275819845787</v>
+      </c>
+      <c r="C101">
+        <v>-311.9635386664374</v>
+      </c>
+      <c r="D101">
+        <v>145.3145613335626</v>
+      </c>
+      <c r="E101">
+        <v>474.9881</v>
+      </c>
+      <c r="F101">
+        <v>476.3781</v>
+      </c>
+      <c r="G101">
+        <v>19.1</v>
+      </c>
+      <c r="H101">
+        <v>479.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>17.5</v>
+      </c>
+      <c r="K101">
+        <v>0.5</v>
+      </c>
+      <c r="L101">
+        <v>17</v>
+      </c>
+      <c r="M101">
+        <v>113.75909028</v>
+      </c>
+      <c r="N101">
+        <v>-96.75909028000001</v>
+      </c>
+      <c r="O101">
+        <v>-9.675909028000001</v>
+      </c>
+      <c r="P101">
+        <v>-87.083181252</v>
+      </c>
+      <c r="Q101">
+        <v>-86.583181252</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.764848998349796</v>
+      </c>
+      <c r="T101">
+        <v>125.7766361119993</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.014943860713159</v>
+      </c>
+      <c r="W101">
+        <v>0.2352314060616977</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.14943860713159</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_electronics_general.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1283261772161178</v>
+        <v>0.1282383510389017</v>
       </c>
       <c r="C2">
-        <v>630.5957995549571</v>
+        <v>624.949128442258</v>
       </c>
       <c r="D2">
-        <v>617.8957995549571</v>
+        <v>618.5540784422579</v>
       </c>
       <c r="E2">
-        <v>-0.695</v>
+        <v>5.60995</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.30495</v>
       </c>
       <c r="G2">
         <v>12.7</v>
@@ -1576,28 +1576,28 @@
         <v>26.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.317138985</v>
       </c>
       <c r="N2">
-        <v>26.2</v>
+        <v>25.882861015</v>
       </c>
       <c r="O2">
-        <v>2.62</v>
+        <v>2.5882861015</v>
       </c>
       <c r="P2">
-        <v>23.58</v>
+        <v>23.2945749135</v>
       </c>
       <c r="Q2">
-        <v>24.18</v>
+        <v>23.8945749135</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1283261772161178</v>
+        <v>0.1290764151908098</v>
       </c>
       <c r="T2">
-        <v>1.276653715063877</v>
+        <v>1.288259657928094</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>82.61362128027244</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1282383510389017</v>
+        <v>0.1281505248616856</v>
       </c>
       <c r="C3">
-        <v>624.949128442258</v>
+        <v>619.303861427913</v>
       </c>
       <c r="D3">
-        <v>618.5540784422579</v>
+        <v>619.213761427913</v>
       </c>
       <c r="E3">
-        <v>5.60995</v>
+        <v>11.9149</v>
       </c>
       <c r="F3">
-        <v>6.30495</v>
+        <v>12.6099</v>
       </c>
       <c r="G3">
         <v>12.7</v>
@@ -1658,28 +1658,28 @@
         <v>26.2</v>
       </c>
       <c r="M3">
-        <v>0.317138985</v>
+        <v>0.63427797</v>
       </c>
       <c r="N3">
-        <v>25.882861015</v>
+        <v>25.56572203</v>
       </c>
       <c r="O3">
-        <v>2.5882861015</v>
+        <v>2.556572203</v>
       </c>
       <c r="P3">
-        <v>23.2945749135</v>
+        <v>23.009149827</v>
       </c>
       <c r="Q3">
-        <v>23.8945749135</v>
+        <v>23.609149827</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1290764151908098</v>
+        <v>0.1298419641445771</v>
       </c>
       <c r="T3">
-        <v>1.288259657928094</v>
+        <v>1.300102456769132</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>82.61362128027244</v>
+        <v>41.30681064013622</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1281505248616856</v>
+        <v>0.1280626986844695</v>
       </c>
       <c r="C4">
-        <v>619.303861427913</v>
+        <v>613.6600030090976</v>
       </c>
       <c r="D4">
-        <v>619.213761427913</v>
+        <v>619.8748530090976</v>
       </c>
       <c r="E4">
-        <v>11.9149</v>
+        <v>18.21985</v>
       </c>
       <c r="F4">
-        <v>12.6099</v>
+        <v>18.91485</v>
       </c>
       <c r="G4">
         <v>12.7</v>
@@ -1740,28 +1740,28 @@
         <v>26.2</v>
       </c>
       <c r="M4">
-        <v>0.63427797</v>
+        <v>0.9514169549999998</v>
       </c>
       <c r="N4">
-        <v>25.56572203</v>
+        <v>25.248583045</v>
       </c>
       <c r="O4">
-        <v>2.556572203</v>
+        <v>2.5248583045</v>
       </c>
       <c r="P4">
-        <v>23.009149827</v>
+        <v>22.7237247405</v>
       </c>
       <c r="Q4">
-        <v>23.609149827</v>
+        <v>23.3237247405</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1298419641445771</v>
+        <v>0.1306232976128551</v>
       </c>
       <c r="T4">
-        <v>1.300102456769132</v>
+        <v>1.312189437029573</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.30681064013622</v>
+        <v>27.53787376009082</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1280626986844695</v>
+        <v>0.1279748725072534</v>
       </c>
       <c r="C5">
-        <v>613.6600030090976</v>
+        <v>608.0175577022129</v>
       </c>
       <c r="D5">
-        <v>619.8748530090976</v>
+        <v>620.5373577022128</v>
       </c>
       <c r="E5">
-        <v>18.21985</v>
+        <v>24.5248</v>
       </c>
       <c r="F5">
-        <v>18.91485</v>
+        <v>25.2198</v>
       </c>
       <c r="G5">
         <v>12.7</v>
@@ -1822,28 +1822,28 @@
         <v>26.2</v>
       </c>
       <c r="M5">
-        <v>0.9514169549999998</v>
+        <v>1.26855594</v>
       </c>
       <c r="N5">
-        <v>25.248583045</v>
+        <v>24.93144406</v>
       </c>
       <c r="O5">
-        <v>2.5248583045</v>
+        <v>2.493144406</v>
       </c>
       <c r="P5">
-        <v>22.7237247405</v>
+        <v>22.438299654</v>
       </c>
       <c r="Q5">
-        <v>23.3237247405</v>
+        <v>23.038299654</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1306232976128551</v>
+        <v>0.1314209088617223</v>
       </c>
       <c r="T5">
-        <v>1.312189437029573</v>
+        <v>1.324528229378773</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.53787376009082</v>
+        <v>20.65340532006811</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1279748725072534</v>
+        <v>0.1278870463300372</v>
       </c>
       <c r="C6">
-        <v>608.0175577022129</v>
+        <v>602.3765300429884</v>
       </c>
       <c r="D6">
-        <v>620.5373577022128</v>
+        <v>621.2012800429884</v>
       </c>
       <c r="E6">
-        <v>24.5248</v>
+        <v>30.82975</v>
       </c>
       <c r="F6">
-        <v>25.2198</v>
+        <v>31.52475</v>
       </c>
       <c r="G6">
         <v>12.7</v>
@@ -1904,28 +1904,28 @@
         <v>26.2</v>
       </c>
       <c r="M6">
-        <v>1.26855594</v>
+        <v>1.585694925</v>
       </c>
       <c r="N6">
-        <v>24.93144406</v>
+        <v>24.614305075</v>
       </c>
       <c r="O6">
-        <v>2.493144406</v>
+        <v>2.4614305075</v>
       </c>
       <c r="P6">
-        <v>22.438299654</v>
+        <v>22.1528745675</v>
       </c>
       <c r="Q6">
-        <v>23.038299654</v>
+        <v>22.7528745675</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1314209088617223</v>
+        <v>0.132235311926355</v>
       </c>
       <c r="T6">
-        <v>1.324528229378773</v>
+        <v>1.337126785777429</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.65340532006811</v>
+        <v>16.52272425605449</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1278870463300372</v>
+        <v>0.1277992201528211</v>
       </c>
       <c r="C7">
-        <v>602.3765300429884</v>
+        <v>596.7369245865859</v>
       </c>
       <c r="D7">
-        <v>621.2012800429884</v>
+        <v>621.8666245865859</v>
       </c>
       <c r="E7">
-        <v>30.82975</v>
+        <v>37.1347</v>
       </c>
       <c r="F7">
-        <v>31.52475</v>
+        <v>37.8297</v>
       </c>
       <c r="G7">
         <v>12.7</v>
@@ -1986,28 +1986,28 @@
         <v>26.2</v>
       </c>
       <c r="M7">
-        <v>1.585694925</v>
+        <v>1.90283391</v>
       </c>
       <c r="N7">
-        <v>24.614305075</v>
+        <v>24.29716609</v>
       </c>
       <c r="O7">
-        <v>2.4614305075</v>
+        <v>2.429716609</v>
       </c>
       <c r="P7">
-        <v>22.1528745675</v>
+        <v>21.867449481</v>
       </c>
       <c r="Q7">
-        <v>22.7528745675</v>
+        <v>22.467449481</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.132235311926355</v>
+        <v>0.1330670427157671</v>
       </c>
       <c r="T7">
-        <v>1.337126785777429</v>
+        <v>1.349993396567547</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.52272425605449</v>
+        <v>13.7689368800454</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1277992201528211</v>
+        <v>0.127805893975605</v>
       </c>
       <c r="C8">
-        <v>596.7369245865859</v>
+        <v>590.3813656919505</v>
       </c>
       <c r="D8">
-        <v>621.8666245865859</v>
+        <v>621.8160156919504</v>
       </c>
       <c r="E8">
-        <v>37.1347</v>
+        <v>43.43964999999999</v>
       </c>
       <c r="F8">
-        <v>37.8297</v>
+        <v>44.13464999999999</v>
       </c>
       <c r="G8">
         <v>12.7</v>
@@ -2068,45 +2068,45 @@
         <v>26.2</v>
       </c>
       <c r="M8">
-        <v>1.90283391</v>
+        <v>2.28617487</v>
       </c>
       <c r="N8">
-        <v>24.29716609</v>
+        <v>23.91382513</v>
       </c>
       <c r="O8">
-        <v>2.429716609</v>
+        <v>2.391382513</v>
       </c>
       <c r="P8">
-        <v>21.867449481</v>
+        <v>21.522442617</v>
       </c>
       <c r="Q8">
-        <v>22.467449481</v>
+        <v>22.122442617</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1330670427157671</v>
+        <v>0.1339166601888226</v>
       </c>
       <c r="T8">
-        <v>1.349993396567547</v>
+        <v>1.363136708664978</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.76893688004541</v>
+        <v>11.46019070710895</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.127805893975605</v>
+        <v>0.1277315677983889</v>
       </c>
       <c r="C9">
-        <v>590.3813656919502</v>
+        <v>584.6405109316735</v>
       </c>
       <c r="D9">
-        <v>621.8160156919502</v>
+        <v>622.3801109316735</v>
       </c>
       <c r="E9">
-        <v>43.43965000000001</v>
+        <v>49.7446</v>
       </c>
       <c r="F9">
-        <v>44.13465000000001</v>
+        <v>50.4396</v>
       </c>
       <c r="G9">
         <v>12.7</v>
@@ -2150,28 +2150,28 @@
         <v>26.2</v>
       </c>
       <c r="M9">
-        <v>2.28617487</v>
+        <v>2.61277128</v>
       </c>
       <c r="N9">
-        <v>23.91382513</v>
+        <v>23.58722872</v>
       </c>
       <c r="O9">
-        <v>2.391382513</v>
+        <v>2.358722872</v>
       </c>
       <c r="P9">
-        <v>21.522442617</v>
+        <v>21.228505848</v>
       </c>
       <c r="Q9">
-        <v>22.122442617</v>
+        <v>21.828505848</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1339166601888226</v>
+        <v>0.1347847476069444</v>
       </c>
       <c r="T9">
-        <v>1.363136708664979</v>
+        <v>1.376565744938442</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.46019070710894</v>
+        <v>10.02766686872033</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1277315677983889</v>
+        <v>0.1277949416211728</v>
       </c>
       <c r="C10">
-        <v>584.6405109316735</v>
+        <v>577.8545238570132</v>
       </c>
       <c r="D10">
-        <v>622.3801109316735</v>
+        <v>621.8990738570131</v>
       </c>
       <c r="E10">
-        <v>49.7446</v>
+        <v>56.04955</v>
       </c>
       <c r="F10">
-        <v>50.4396</v>
+        <v>56.74455</v>
       </c>
       <c r="G10">
         <v>12.7</v>
@@ -2232,45 +2232,45 @@
         <v>26.2</v>
       </c>
       <c r="M10">
-        <v>2.61277128</v>
+        <v>3.035833425</v>
       </c>
       <c r="N10">
-        <v>23.58722872</v>
+        <v>23.164166575</v>
       </c>
       <c r="O10">
-        <v>2.358722872</v>
+        <v>2.3164166575</v>
       </c>
       <c r="P10">
-        <v>21.228505848</v>
+        <v>20.8477499175</v>
       </c>
       <c r="Q10">
-        <v>21.828505848</v>
+        <v>21.4477499175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1347847476069444</v>
+        <v>0.1356719138694206</v>
       </c>
       <c r="T10">
-        <v>1.376565744938442</v>
+        <v>1.390289924866266</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.02766686872033</v>
+        <v>8.630249533536247</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1277949416211728</v>
+        <v>0.1277359154439567</v>
       </c>
       <c r="C11">
-        <v>577.8545238570132</v>
+        <v>571.9975864867023</v>
       </c>
       <c r="D11">
-        <v>621.8990738570131</v>
+        <v>622.3470864867022</v>
       </c>
       <c r="E11">
-        <v>56.04955</v>
+        <v>62.35449999999999</v>
       </c>
       <c r="F11">
-        <v>56.74455</v>
+        <v>63.04949999999999</v>
       </c>
       <c r="G11">
         <v>12.7</v>
@@ -2314,28 +2314,28 @@
         <v>26.2</v>
       </c>
       <c r="M11">
-        <v>3.035833425</v>
+        <v>3.37314825</v>
       </c>
       <c r="N11">
-        <v>23.164166575</v>
+        <v>22.82685175</v>
       </c>
       <c r="O11">
-        <v>2.3164166575</v>
+        <v>2.282685175</v>
       </c>
       <c r="P11">
-        <v>20.8477499175</v>
+        <v>20.544166575</v>
       </c>
       <c r="Q11">
-        <v>21.4477499175</v>
+        <v>21.144166575</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1356719138694206</v>
+        <v>0.1365787949377296</v>
       </c>
       <c r="T11">
-        <v>1.390289924866266</v>
+        <v>1.404319086570265</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.630249533536247</v>
+        <v>7.767224580182623</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1277359154439567</v>
+        <v>0.1277560892667405</v>
       </c>
       <c r="C12">
-        <v>571.9975864867023</v>
+        <v>565.5394432347404</v>
       </c>
       <c r="D12">
-        <v>622.3470864867022</v>
+        <v>622.1938932347404</v>
       </c>
       <c r="E12">
-        <v>62.3545</v>
+        <v>68.65945000000001</v>
       </c>
       <c r="F12">
-        <v>63.0495</v>
+        <v>69.35445</v>
       </c>
       <c r="G12">
         <v>12.7</v>
@@ -2396,45 +2396,45 @@
         <v>26.2</v>
       </c>
       <c r="M12">
-        <v>3.37314825</v>
+        <v>3.765946635</v>
       </c>
       <c r="N12">
-        <v>22.82685175</v>
+        <v>22.434053365</v>
       </c>
       <c r="O12">
-        <v>2.282685175</v>
+        <v>2.2434053365</v>
       </c>
       <c r="P12">
-        <v>20.544166575</v>
+        <v>20.1906480285</v>
       </c>
       <c r="Q12">
-        <v>21.144166575</v>
+        <v>20.7906480285</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1365787949377296</v>
+        <v>0.1375060553558882</v>
       </c>
       <c r="T12">
-        <v>1.404319086570265</v>
+        <v>1.418663510335028</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.767224580182623</v>
+        <v>6.957082120203756</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1277560892667405</v>
+        <v>0.1277042630895244</v>
       </c>
       <c r="C13">
-        <v>565.5394432347404</v>
+        <v>559.6281959524892</v>
       </c>
       <c r="D13">
-        <v>622.1938932347404</v>
+        <v>622.5875959524892</v>
       </c>
       <c r="E13">
-        <v>68.65945000000001</v>
+        <v>74.9644</v>
       </c>
       <c r="F13">
-        <v>69.35445</v>
+        <v>75.65939999999999</v>
       </c>
       <c r="G13">
         <v>12.7</v>
@@ -2478,28 +2478,28 @@
         <v>26.2</v>
       </c>
       <c r="M13">
-        <v>3.765946635</v>
+        <v>4.10830542</v>
       </c>
       <c r="N13">
-        <v>22.434053365</v>
+        <v>22.09169458</v>
       </c>
       <c r="O13">
-        <v>2.2434053365</v>
+        <v>2.209169458</v>
       </c>
       <c r="P13">
-        <v>20.1906480285</v>
+        <v>19.882525122</v>
       </c>
       <c r="Q13">
-        <v>20.7906480285</v>
+        <v>20.482525122</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1375060553558882</v>
+        <v>0.1384543898744596</v>
       </c>
       <c r="T13">
-        <v>1.418663510335028</v>
+        <v>1.433333943730808</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.957082120203756</v>
+        <v>6.377325276853443</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1277042630895244</v>
+        <v>0.1277694369123083</v>
       </c>
       <c r="C14">
-        <v>559.6281959524892</v>
+        <v>552.8282271360315</v>
       </c>
       <c r="D14">
-        <v>622.5875959524892</v>
+        <v>622.0925771360314</v>
       </c>
       <c r="E14">
-        <v>74.9644</v>
+        <v>81.26935000000002</v>
       </c>
       <c r="F14">
-        <v>75.65939999999999</v>
+        <v>81.96435000000001</v>
       </c>
       <c r="G14">
         <v>12.7</v>
@@ -2560,45 +2560,45 @@
         <v>26.2</v>
       </c>
       <c r="M14">
-        <v>4.10830542</v>
+        <v>4.532628555000001</v>
       </c>
       <c r="N14">
-        <v>22.09169458</v>
+        <v>21.667371445</v>
       </c>
       <c r="O14">
-        <v>2.209169458</v>
+        <v>2.1667371445</v>
       </c>
       <c r="P14">
-        <v>19.882525122</v>
+        <v>19.5006343005</v>
       </c>
       <c r="Q14">
-        <v>20.482525122</v>
+        <v>20.1006343005</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1384543898744596</v>
+        <v>0.1394245251865613</v>
       </c>
       <c r="T14">
-        <v>1.433333943730808</v>
+        <v>1.448341628469019</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.377325276853443</v>
+        <v>5.780310405338299</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1277694369123083</v>
+        <v>0.1277266107350922</v>
       </c>
       <c r="C15">
-        <v>552.8282271360315</v>
+        <v>546.8484687522134</v>
       </c>
       <c r="D15">
-        <v>622.0925771360314</v>
+        <v>622.4177687522134</v>
       </c>
       <c r="E15">
-        <v>81.26935000000002</v>
+        <v>87.57430000000002</v>
       </c>
       <c r="F15">
-        <v>81.96435000000001</v>
+        <v>88.26930000000002</v>
       </c>
       <c r="G15">
         <v>12.7</v>
@@ -2642,28 +2642,28 @@
         <v>26.2</v>
       </c>
       <c r="M15">
-        <v>4.532628555000001</v>
+        <v>4.881292290000001</v>
       </c>
       <c r="N15">
-        <v>21.667371445</v>
+        <v>21.31870771</v>
       </c>
       <c r="O15">
-        <v>2.1667371445</v>
+        <v>2.131870771</v>
       </c>
       <c r="P15">
-        <v>19.5006343005</v>
+        <v>19.186836939</v>
       </c>
       <c r="Q15">
-        <v>20.1006343005</v>
+        <v>19.786836939</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1394245251865613</v>
+        <v>0.1404172217849909</v>
       </c>
       <c r="T15">
-        <v>1.448341628469019</v>
+        <v>1.463698329131375</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.780310405338299</v>
+        <v>5.367431090671277</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1277266107350922</v>
+        <v>0.1276837845578761</v>
       </c>
       <c r="C16">
-        <v>546.8484687522134</v>
+        <v>540.8690505264342</v>
       </c>
       <c r="D16">
-        <v>622.4177687522134</v>
+        <v>622.7433005264342</v>
       </c>
       <c r="E16">
-        <v>87.57430000000002</v>
+        <v>93.87925000000003</v>
       </c>
       <c r="F16">
-        <v>88.26930000000002</v>
+        <v>94.57425000000002</v>
       </c>
       <c r="G16">
         <v>12.7</v>
@@ -2724,28 +2724,28 @@
         <v>26.2</v>
       </c>
       <c r="M16">
-        <v>4.881292290000001</v>
+        <v>5.229956025000002</v>
       </c>
       <c r="N16">
-        <v>21.31870771</v>
+        <v>20.970043975</v>
       </c>
       <c r="O16">
-        <v>2.131870771</v>
+        <v>2.0970043975</v>
       </c>
       <c r="P16">
-        <v>19.186836939</v>
+        <v>18.87303957749999</v>
       </c>
       <c r="Q16">
-        <v>19.786836939</v>
+        <v>19.4730395775</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1404172217849909</v>
+        <v>0.1414332759504424</v>
       </c>
       <c r="T16">
-        <v>1.463698329131375</v>
+        <v>1.479416363926964</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.367431090671277</v>
+        <v>5.009602351293191</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1276837845578761</v>
+        <v>0.1276409583806599</v>
       </c>
       <c r="C17">
-        <v>540.8690505264342</v>
+        <v>534.8899729926932</v>
       </c>
       <c r="D17">
-        <v>622.7433005264342</v>
+        <v>623.0691729926931</v>
       </c>
       <c r="E17">
-        <v>93.87925</v>
+        <v>100.1842</v>
       </c>
       <c r="F17">
-        <v>94.57424999999999</v>
+        <v>100.8792</v>
       </c>
       <c r="G17">
         <v>12.7</v>
@@ -2806,28 +2806,28 @@
         <v>26.2</v>
       </c>
       <c r="M17">
-        <v>5.229956025</v>
+        <v>5.57861976</v>
       </c>
       <c r="N17">
-        <v>20.970043975</v>
+        <v>20.62138024</v>
       </c>
       <c r="O17">
-        <v>2.0970043975</v>
+        <v>2.062138024</v>
       </c>
       <c r="P17">
-        <v>18.8730395775</v>
+        <v>18.559242216</v>
       </c>
       <c r="Q17">
-        <v>19.4730395775</v>
+        <v>19.159242216</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1414332759504424</v>
+        <v>0.142473521881738</v>
       </c>
       <c r="T17">
-        <v>1.479416363926964</v>
+        <v>1.495508637646256</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.009602351293193</v>
+        <v>4.696502204337368</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1276409583806599</v>
+        <v>0.1279806322034438</v>
       </c>
       <c r="C18">
-        <v>534.8899729926932</v>
+        <v>526.009716838741</v>
       </c>
       <c r="D18">
-        <v>623.0691729926931</v>
+        <v>620.493866838741</v>
       </c>
       <c r="E18">
-        <v>100.1842</v>
+        <v>106.48915</v>
       </c>
       <c r="F18">
-        <v>100.8792</v>
+        <v>107.18415</v>
       </c>
       <c r="G18">
         <v>12.7</v>
@@ -2888,45 +2888,45 @@
         <v>26.2</v>
       </c>
       <c r="M18">
-        <v>5.57861976</v>
+        <v>6.195243870000001</v>
       </c>
       <c r="N18">
-        <v>20.62138024</v>
+        <v>20.00475613</v>
       </c>
       <c r="O18">
-        <v>2.062138024</v>
+        <v>2.000475613</v>
       </c>
       <c r="P18">
-        <v>18.559242216</v>
+        <v>18.004280517</v>
       </c>
       <c r="Q18">
-        <v>19.159242216</v>
+        <v>18.604280517</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.142473521881738</v>
+        <v>0.1435388339800528</v>
       </c>
       <c r="T18">
-        <v>1.495508637646256</v>
+        <v>1.511988676997339</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.696502204337368</v>
+        <v>4.22905063138378</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1279806322034438</v>
+        <v>0.1285273060262277</v>
       </c>
       <c r="C19">
-        <v>526.009716838741</v>
+        <v>515.6044549768856</v>
       </c>
       <c r="D19">
-        <v>620.493866838741</v>
+        <v>616.3935549768855</v>
       </c>
       <c r="E19">
-        <v>106.48915</v>
+        <v>112.7941</v>
       </c>
       <c r="F19">
-        <v>107.18415</v>
+        <v>113.4891</v>
       </c>
       <c r="G19">
         <v>12.7</v>
@@ -2970,45 +2970,45 @@
         <v>26.2</v>
       </c>
       <c r="M19">
-        <v>6.195243870000001</v>
+        <v>6.95688183</v>
       </c>
       <c r="N19">
-        <v>20.00475613</v>
+        <v>19.24311817</v>
       </c>
       <c r="O19">
-        <v>2.000475613</v>
+        <v>1.924311817</v>
       </c>
       <c r="P19">
-        <v>18.004280517</v>
+        <v>17.318806353</v>
       </c>
       <c r="Q19">
-        <v>18.604280517</v>
+        <v>17.918806353</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1435388339800528</v>
+        <v>0.1446301293002777</v>
       </c>
       <c r="T19">
-        <v>1.511988676997339</v>
+        <v>1.528870668527716</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.22905063138378</v>
+        <v>3.766055057456682</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1285273060262277</v>
+        <v>0.1285384798490116</v>
       </c>
       <c r="C20">
-        <v>515.6044549768853</v>
+        <v>509.2162610937369</v>
       </c>
       <c r="D20">
-        <v>616.3935549768853</v>
+        <v>616.3103110937368</v>
       </c>
       <c r="E20">
-        <v>112.7941</v>
+        <v>119.09905</v>
       </c>
       <c r="F20">
-        <v>113.4891</v>
+        <v>119.79405</v>
       </c>
       <c r="G20">
         <v>12.7</v>
@@ -3052,28 +3052,28 @@
         <v>26.2</v>
       </c>
       <c r="M20">
-        <v>6.956881829999999</v>
+        <v>7.343375265</v>
       </c>
       <c r="N20">
-        <v>19.24311817</v>
+        <v>18.856624735</v>
       </c>
       <c r="O20">
-        <v>1.924311817</v>
+        <v>1.8856624735</v>
       </c>
       <c r="P20">
-        <v>17.318806353</v>
+        <v>16.9709622615</v>
       </c>
       <c r="Q20">
-        <v>17.918806353</v>
+        <v>17.5709622615</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1446301293002777</v>
+        <v>0.1457483701839649</v>
       </c>
       <c r="T20">
-        <v>1.528870668527716</v>
+        <v>1.54616949935514</v>
       </c>
       <c r="U20">
         <v>0.0613</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.766055057456683</v>
+        <v>3.567841633380015</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1285384798490116</v>
+        <v>0.1290536536717955</v>
       </c>
       <c r="C21">
-        <v>509.2162610937369</v>
+        <v>499.0975813055047</v>
       </c>
       <c r="D21">
-        <v>616.3103110937368</v>
+        <v>612.4965813055046</v>
       </c>
       <c r="E21">
-        <v>119.09905</v>
+        <v>125.404</v>
       </c>
       <c r="F21">
-        <v>119.79405</v>
+        <v>126.099</v>
       </c>
       <c r="G21">
         <v>12.7</v>
@@ -3134,45 +3134,45 @@
         <v>26.2</v>
       </c>
       <c r="M21">
-        <v>7.343375265</v>
+        <v>8.0829459</v>
       </c>
       <c r="N21">
-        <v>18.856624735</v>
+        <v>18.1170541</v>
       </c>
       <c r="O21">
-        <v>1.8856624735</v>
+        <v>1.81170541</v>
       </c>
       <c r="P21">
-        <v>16.9709622615</v>
+        <v>16.30534869</v>
       </c>
       <c r="Q21">
-        <v>17.5709622615</v>
+        <v>16.90534869</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1457483701839649</v>
+        <v>0.1468945670897444</v>
       </c>
       <c r="T21">
-        <v>1.54616949935514</v>
+        <v>1.56390080095325</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.567841633380015</v>
+        <v>3.241392473009129</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1290536536717955</v>
+        <v>0.1290900274945794</v>
       </c>
       <c r="C22">
-        <v>499.0975813055047</v>
+        <v>492.5251461962508</v>
       </c>
       <c r="D22">
-        <v>612.4965813055046</v>
+        <v>612.2290961962508</v>
       </c>
       <c r="E22">
-        <v>125.404</v>
+        <v>131.70895</v>
       </c>
       <c r="F22">
-        <v>126.099</v>
+        <v>132.40395</v>
       </c>
       <c r="G22">
         <v>12.7</v>
@@ -3216,28 +3216,28 @@
         <v>26.2</v>
       </c>
       <c r="M22">
-        <v>8.0829459</v>
+        <v>8.487093195000002</v>
       </c>
       <c r="N22">
-        <v>18.1170541</v>
+        <v>17.712906805</v>
       </c>
       <c r="O22">
-        <v>1.81170541</v>
+        <v>1.7712906805</v>
       </c>
       <c r="P22">
-        <v>16.30534869</v>
+        <v>15.9416161245</v>
       </c>
       <c r="Q22">
-        <v>16.90534869</v>
+        <v>16.5416161245</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1468945670897444</v>
+        <v>0.148069781638708</v>
       </c>
       <c r="T22">
-        <v>1.56390080095325</v>
+        <v>1.582080996262704</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.241392473009129</v>
+        <v>3.087040450484884</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1290900274945794</v>
+        <v>0.1306708013173632</v>
       </c>
       <c r="C23">
-        <v>492.5251461962508</v>
+        <v>474.8170314588908</v>
       </c>
       <c r="D23">
-        <v>612.2290961962508</v>
+        <v>600.8259314588908</v>
       </c>
       <c r="E23">
-        <v>131.70895</v>
+        <v>138.0139</v>
       </c>
       <c r="F23">
-        <v>132.40395</v>
+        <v>138.7089</v>
       </c>
       <c r="G23">
         <v>12.7</v>
@@ -3298,45 +3298,45 @@
         <v>26.2</v>
       </c>
       <c r="M23">
-        <v>8.487093195000002</v>
+        <v>9.973169910000001</v>
       </c>
       <c r="N23">
-        <v>17.712906805</v>
+        <v>16.22683009</v>
       </c>
       <c r="O23">
-        <v>1.7712906805</v>
+        <v>1.622683009</v>
       </c>
       <c r="P23">
-        <v>15.9416161245</v>
+        <v>14.604147081</v>
       </c>
       <c r="Q23">
-        <v>16.5416161245</v>
+        <v>15.204147081</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.148069781638708</v>
+        <v>0.1492751298940554</v>
       </c>
       <c r="T23">
-        <v>1.582080996262704</v>
+        <v>1.600727350426246</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.087040450484884</v>
+        <v>2.627048394485841</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1306708013173632</v>
+        <v>0.1307773751401471</v>
       </c>
       <c r="C24">
-        <v>474.8170314588908</v>
+        <v>467.7585595215788</v>
       </c>
       <c r="D24">
-        <v>600.8259314588908</v>
+        <v>600.0724095215788</v>
       </c>
       <c r="E24">
-        <v>138.0139</v>
+        <v>144.31885</v>
       </c>
       <c r="F24">
-        <v>138.7089</v>
+        <v>145.01385</v>
       </c>
       <c r="G24">
         <v>12.7</v>
@@ -3380,28 +3380,28 @@
         <v>26.2</v>
       </c>
       <c r="M24">
-        <v>9.973169910000001</v>
+        <v>10.426495815</v>
       </c>
       <c r="N24">
-        <v>16.22683009</v>
+        <v>15.773504185</v>
       </c>
       <c r="O24">
-        <v>1.622683009</v>
+        <v>1.5773504185</v>
       </c>
       <c r="P24">
-        <v>14.604147081</v>
+        <v>14.1961537665</v>
       </c>
       <c r="Q24">
-        <v>15.204147081</v>
+        <v>14.7961537665</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1492751298940554</v>
+        <v>0.150511785896295</v>
       </c>
       <c r="T24">
-        <v>1.600727350426246</v>
+        <v>1.619858025477153</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.627048394485841</v>
+        <v>2.512828899073412</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1307773751401471</v>
+        <v>0.131726348962931</v>
       </c>
       <c r="C25">
-        <v>467.7585595215788</v>
+        <v>454.8263873099557</v>
       </c>
       <c r="D25">
-        <v>600.0724095215788</v>
+        <v>593.4451873099557</v>
       </c>
       <c r="E25">
-        <v>144.31885</v>
+        <v>150.6238</v>
       </c>
       <c r="F25">
-        <v>145.01385</v>
+        <v>151.3188</v>
       </c>
       <c r="G25">
         <v>12.7</v>
@@ -3462,45 +3462,45 @@
         <v>26.2</v>
       </c>
       <c r="M25">
-        <v>10.426495815</v>
+        <v>11.46996504</v>
       </c>
       <c r="N25">
-        <v>15.773504185</v>
+        <v>14.73003496</v>
       </c>
       <c r="O25">
-        <v>1.5773504185</v>
+        <v>1.473003496</v>
       </c>
       <c r="P25">
-        <v>14.1961537665</v>
+        <v>13.257031464</v>
       </c>
       <c r="Q25">
-        <v>14.7961537665</v>
+        <v>13.857031464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.150511785896295</v>
+        <v>0.1517809854775408</v>
       </c>
       <c r="T25">
-        <v>1.619858025477153</v>
+        <v>1.63949213934519</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.512828899073412</v>
+        <v>2.284226665785896</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.131726348962931</v>
+        <v>0.1318680227857149</v>
       </c>
       <c r="C26">
-        <v>454.8263873099557</v>
+        <v>447.544586145288</v>
       </c>
       <c r="D26">
-        <v>593.4451873099557</v>
+        <v>592.4683361452879</v>
       </c>
       <c r="E26">
-        <v>150.6238</v>
+        <v>156.92875</v>
       </c>
       <c r="F26">
-        <v>151.3188</v>
+        <v>157.62375</v>
       </c>
       <c r="G26">
         <v>12.7</v>
@@ -3544,28 +3544,28 @@
         <v>26.2</v>
       </c>
       <c r="M26">
-        <v>11.46996504</v>
+        <v>11.94788025</v>
       </c>
       <c r="N26">
-        <v>14.73003496</v>
+        <v>14.25211975</v>
       </c>
       <c r="O26">
-        <v>1.473003496</v>
+        <v>1.425211975</v>
       </c>
       <c r="P26">
-        <v>13.257031464</v>
+        <v>12.826907775</v>
       </c>
       <c r="Q26">
-        <v>13.857031464</v>
+        <v>13.426907775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1517809854775408</v>
+        <v>0.1530840303809532</v>
       </c>
       <c r="T26">
-        <v>1.63949213934519</v>
+        <v>1.65964982958304</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.284226665785897</v>
+        <v>2.192857599154461</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1318680227857149</v>
+        <v>0.1320096966084988</v>
       </c>
       <c r="C27">
-        <v>447.544586145288</v>
+        <v>440.265995622676</v>
       </c>
       <c r="D27">
-        <v>592.4683361452879</v>
+        <v>591.494695622676</v>
       </c>
       <c r="E27">
-        <v>156.92875</v>
+        <v>163.2337</v>
       </c>
       <c r="F27">
-        <v>157.62375</v>
+        <v>163.9287</v>
       </c>
       <c r="G27">
         <v>12.7</v>
@@ -3626,28 +3626,28 @@
         <v>26.2</v>
       </c>
       <c r="M27">
-        <v>11.94788025</v>
+        <v>12.42579546</v>
       </c>
       <c r="N27">
-        <v>14.25211975</v>
+        <v>13.77420454</v>
       </c>
       <c r="O27">
-        <v>1.425211975</v>
+        <v>1.377420454</v>
       </c>
       <c r="P27">
-        <v>12.826907775</v>
+        <v>12.396784086</v>
       </c>
       <c r="Q27">
-        <v>13.426907775</v>
+        <v>12.996784086</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1530840303809532</v>
+        <v>0.1544222927141875</v>
       </c>
       <c r="T27">
-        <v>1.65964982958304</v>
+        <v>1.680352322259752</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.192857599154461</v>
+        <v>2.108516922263904</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1320096966084988</v>
+        <v>0.1321513704312827</v>
       </c>
       <c r="C28">
-        <v>440.265995622676</v>
+        <v>432.9905999393391</v>
       </c>
       <c r="D28">
-        <v>591.494695622676</v>
+        <v>590.524249939339</v>
       </c>
       <c r="E28">
-        <v>163.2337</v>
+        <v>169.53865</v>
       </c>
       <c r="F28">
-        <v>163.9287</v>
+        <v>170.23365</v>
       </c>
       <c r="G28">
         <v>12.7</v>
@@ -3708,28 +3708,28 @@
         <v>26.2</v>
       </c>
       <c r="M28">
-        <v>12.42579546</v>
+        <v>12.90371067</v>
       </c>
       <c r="N28">
-        <v>13.77420454</v>
+        <v>13.29628933</v>
       </c>
       <c r="O28">
-        <v>1.377420454</v>
+        <v>1.329628933</v>
       </c>
       <c r="P28">
-        <v>12.396784086</v>
+        <v>11.966660397</v>
       </c>
       <c r="Q28">
-        <v>12.996784086</v>
+        <v>12.566660397</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1544222927141875</v>
+        <v>0.1557972197688804</v>
       </c>
       <c r="T28">
-        <v>1.680352322259752</v>
+        <v>1.701622006516648</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.108516922263904</v>
+        <v>2.030423702920797</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1321513704312827</v>
+        <v>0.1358714442540665</v>
       </c>
       <c r="C29">
-        <v>432.9905999393391</v>
+        <v>402.2961908592574</v>
       </c>
       <c r="D29">
-        <v>590.524249939339</v>
+        <v>566.1347908592574</v>
       </c>
       <c r="E29">
-        <v>169.53865</v>
+        <v>175.8436</v>
       </c>
       <c r="F29">
-        <v>170.23365</v>
+        <v>176.5386</v>
       </c>
       <c r="G29">
         <v>12.7</v>
@@ -3790,45 +3790,45 @@
         <v>26.2</v>
       </c>
       <c r="M29">
-        <v>12.90371067</v>
+        <v>15.888474</v>
       </c>
       <c r="N29">
-        <v>13.29628933</v>
+        <v>10.311526</v>
       </c>
       <c r="O29">
-        <v>1.329628933</v>
+        <v>1.0311526</v>
       </c>
       <c r="P29">
-        <v>11.966660397</v>
+        <v>9.280373399999997</v>
       </c>
       <c r="Q29">
-        <v>12.566660397</v>
+        <v>9.880373399999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1557972197688804</v>
+        <v>0.1572103392417591</v>
       </c>
       <c r="T29">
-        <v>1.701622006516648</v>
+        <v>1.723482515336234</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.030423702920797</v>
+        <v>1.648994107300676</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1358714442540665</v>
+        <v>0.1361409180768504</v>
       </c>
       <c r="C30">
-        <v>402.2961908592574</v>
+        <v>394.302543095814</v>
       </c>
       <c r="D30">
-        <v>566.1347908592574</v>
+        <v>564.446093095814</v>
       </c>
       <c r="E30">
-        <v>175.8436</v>
+        <v>182.14855</v>
       </c>
       <c r="F30">
-        <v>176.5386</v>
+        <v>182.84355</v>
       </c>
       <c r="G30">
         <v>12.7</v>
@@ -3872,28 +3872,28 @@
         <v>26.2</v>
       </c>
       <c r="M30">
-        <v>15.888474</v>
+        <v>16.4559195</v>
       </c>
       <c r="N30">
-        <v>10.311526</v>
+        <v>9.744080499999999</v>
       </c>
       <c r="O30">
-        <v>1.0311526</v>
+        <v>0.97440805</v>
       </c>
       <c r="P30">
-        <v>9.280373399999997</v>
+        <v>8.76967245</v>
       </c>
       <c r="Q30">
-        <v>9.880373399999998</v>
+        <v>9.369672450000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1572103392417591</v>
+        <v>0.1586632648969724</v>
       </c>
       <c r="T30">
-        <v>1.723482515336234</v>
+        <v>1.745958813136655</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.648994107300676</v>
+        <v>1.592132241531687</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1361409180768504</v>
+        <v>0.1364103918996343</v>
       </c>
       <c r="C31">
-        <v>394.3025430958141</v>
+        <v>386.3189396514009</v>
       </c>
       <c r="D31">
-        <v>564.446093095814</v>
+        <v>562.7674396514009</v>
       </c>
       <c r="E31">
-        <v>182.14855</v>
+        <v>188.4535</v>
       </c>
       <c r="F31">
-        <v>182.84355</v>
+        <v>189.1485</v>
       </c>
       <c r="G31">
         <v>12.7</v>
@@ -3954,28 +3954,28 @@
         <v>26.2</v>
       </c>
       <c r="M31">
-        <v>16.4559195</v>
+        <v>17.023365</v>
       </c>
       <c r="N31">
-        <v>9.744080499999999</v>
+        <v>9.176635000000001</v>
       </c>
       <c r="O31">
-        <v>0.97440805</v>
+        <v>0.9176635000000002</v>
       </c>
       <c r="P31">
-        <v>8.76967245</v>
+        <v>8.258971500000001</v>
       </c>
       <c r="Q31">
-        <v>9.369672450000001</v>
+        <v>8.858971500000003</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1586632648969724</v>
+        <v>0.1601577027137633</v>
       </c>
       <c r="T31">
-        <v>1.745958813136655</v>
+        <v>1.76907729087423</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.592132241531687</v>
+        <v>1.539061166813964</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1364103918996343</v>
+        <v>0.1531446449443501</v>
       </c>
       <c r="C32">
-        <v>386.3189396514009</v>
+        <v>292.2826198626647</v>
       </c>
       <c r="D32">
-        <v>562.7674396514009</v>
+        <v>475.0360698626646</v>
       </c>
       <c r="E32">
-        <v>188.4535</v>
+        <v>194.75845</v>
       </c>
       <c r="F32">
-        <v>189.1485</v>
+        <v>195.45345</v>
       </c>
       <c r="G32">
         <v>12.7</v>
@@ -4036,45 +4036,45 @@
         <v>26.2</v>
       </c>
       <c r="M32">
-        <v>17.023365</v>
+        <v>28.69256646</v>
       </c>
       <c r="N32">
-        <v>9.176635000000001</v>
+        <v>-2.492566460000003</v>
       </c>
       <c r="O32">
-        <v>0.9176635000000002</v>
+        <v>-0.2492566460000003</v>
       </c>
       <c r="P32">
-        <v>8.258971500000001</v>
+        <v>-2.243309814000003</v>
       </c>
       <c r="Q32">
-        <v>8.858971500000003</v>
+        <v>-1.643309814000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1601577027137633</v>
+        <v>0.1620175508619533</v>
       </c>
       <c r="T32">
-        <v>1.76907729087423</v>
+        <v>1.797848550224139</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1</v>
+        <v>0.0913128493978576</v>
       </c>
       <c r="W32">
-        <v>0.081</v>
+        <v>0.1333952737083945</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.539061166813964</v>
+        <v>0.9131284939785759</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1531446449443501</v>
+        <v>0.1541546449443501</v>
       </c>
       <c r="C33">
-        <v>292.2826198626647</v>
+        <v>281.5497431151983</v>
       </c>
       <c r="D33">
-        <v>475.0360698626646</v>
+        <v>470.6081431151983</v>
       </c>
       <c r="E33">
-        <v>194.75845</v>
+        <v>201.0634</v>
       </c>
       <c r="F33">
-        <v>195.45345</v>
+        <v>201.7584</v>
       </c>
       <c r="G33">
         <v>12.7</v>
@@ -4118,37 +4118,37 @@
         <v>26.2</v>
       </c>
       <c r="M33">
-        <v>28.69256646</v>
+        <v>29.61813312</v>
       </c>
       <c r="N33">
-        <v>-2.492566460000003</v>
+        <v>-3.418133120000004</v>
       </c>
       <c r="O33">
-        <v>-0.2492566460000003</v>
+        <v>-0.3418133120000004</v>
       </c>
       <c r="P33">
-        <v>-2.243309814000003</v>
+        <v>-3.076319808000004</v>
       </c>
       <c r="Q33">
-        <v>-1.643309814000001</v>
+        <v>-2.476319808000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1620175508619533</v>
+        <v>0.1637266324922762</v>
       </c>
       <c r="T33">
-        <v>1.797848550224139</v>
+        <v>1.824287499492141</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.0913128493978576</v>
+        <v>0.08845932285417454</v>
       </c>
       <c r="W33">
-        <v>0.1333952737083945</v>
+        <v>0.1338141714050072</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9131284939785759</v>
+        <v>0.8845932285417453</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1541546449443501</v>
+        <v>0.1551646449443501</v>
       </c>
       <c r="C34">
-        <v>281.5497431151983</v>
+        <v>270.8986515921475</v>
       </c>
       <c r="D34">
-        <v>470.6081431151983</v>
+        <v>466.2620015921476</v>
       </c>
       <c r="E34">
-        <v>201.0634</v>
+        <v>207.36835</v>
       </c>
       <c r="F34">
-        <v>201.7584</v>
+        <v>208.06335</v>
       </c>
       <c r="G34">
         <v>12.7</v>
@@ -4200,37 +4200,37 @@
         <v>26.2</v>
       </c>
       <c r="M34">
-        <v>29.61813312</v>
+        <v>30.54369978</v>
       </c>
       <c r="N34">
-        <v>-3.418133120000004</v>
+        <v>-4.343699780000005</v>
       </c>
       <c r="O34">
-        <v>-0.3418133120000004</v>
+        <v>-0.4343699780000005</v>
       </c>
       <c r="P34">
-        <v>-3.076319808000004</v>
+        <v>-3.909329802000005</v>
       </c>
       <c r="Q34">
-        <v>-2.476319808000002</v>
+        <v>-3.309329802000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1637266324922762</v>
+        <v>0.1654867314846982</v>
       </c>
       <c r="T34">
-        <v>1.824287499492141</v>
+        <v>1.851515671126352</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.08845932285417454</v>
+        <v>0.08577873731313895</v>
       </c>
       <c r="W34">
-        <v>0.1338141714050072</v>
+        <v>0.1342076813624312</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8845932285417453</v>
+        <v>0.8577873731313894</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1551646449443501</v>
+        <v>0.1561746449443501</v>
       </c>
       <c r="C35">
-        <v>270.8986515921475</v>
+        <v>260.3271001290534</v>
       </c>
       <c r="D35">
-        <v>466.2620015921476</v>
+        <v>461.9954001290534</v>
       </c>
       <c r="E35">
-        <v>207.36835</v>
+        <v>213.6733</v>
       </c>
       <c r="F35">
-        <v>208.06335</v>
+        <v>214.3683</v>
       </c>
       <c r="G35">
         <v>12.7</v>
@@ -4282,37 +4282,37 @@
         <v>26.2</v>
       </c>
       <c r="M35">
-        <v>30.54369978</v>
+        <v>31.46926644</v>
       </c>
       <c r="N35">
-        <v>-4.343699780000005</v>
+        <v>-5.269266440000003</v>
       </c>
       <c r="O35">
-        <v>-0.4343699780000005</v>
+        <v>-0.5269266440000003</v>
       </c>
       <c r="P35">
-        <v>-3.909329802000005</v>
+        <v>-4.742339796000002</v>
       </c>
       <c r="Q35">
-        <v>-3.309329802000003</v>
+        <v>-4.142339796000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1654867314846982</v>
+        <v>0.1673001668102239</v>
       </c>
       <c r="T35">
-        <v>1.851515671126352</v>
+        <v>1.879568938870691</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.08577873731313895</v>
+        <v>0.08325583327451722</v>
       </c>
       <c r="W35">
-        <v>0.1342076813624312</v>
+        <v>0.1345780436753009</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8577873731313894</v>
+        <v>0.8325583327451721</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1561746449443501</v>
+        <v>0.1571846449443501</v>
       </c>
       <c r="C36">
-        <v>260.3271001290534</v>
+        <v>249.8329249951628</v>
       </c>
       <c r="D36">
-        <v>461.9954001290534</v>
+        <v>457.8061749951628</v>
       </c>
       <c r="E36">
-        <v>213.6733</v>
+        <v>219.97825</v>
       </c>
       <c r="F36">
-        <v>214.3683</v>
+        <v>220.67325</v>
       </c>
       <c r="G36">
         <v>12.7</v>
@@ -4364,37 +4364,37 @@
         <v>26.2</v>
       </c>
       <c r="M36">
-        <v>31.46926644</v>
+        <v>32.39483310000001</v>
       </c>
       <c r="N36">
-        <v>-5.269266440000003</v>
+        <v>-6.194833100000007</v>
       </c>
       <c r="O36">
-        <v>-0.5269266440000003</v>
+        <v>-0.6194833100000008</v>
       </c>
       <c r="P36">
-        <v>-4.742339796000002</v>
+        <v>-5.575349790000007</v>
       </c>
       <c r="Q36">
-        <v>-4.142339796000001</v>
+        <v>-4.975349790000005</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1673001668102239</v>
+        <v>0.1691694001457658</v>
       </c>
       <c r="T36">
-        <v>1.879568938870691</v>
+        <v>1.908485384084086</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.08325583327451722</v>
+        <v>0.08087709518095958</v>
       </c>
       <c r="W36">
-        <v>0.1345780436753009</v>
+        <v>0.1349272424274351</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8325583327451721</v>
+        <v>0.8087709518095957</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1571846449443501</v>
+        <v>0.1782628701662325</v>
       </c>
       <c r="C37">
-        <v>249.8329249951628</v>
+        <v>170.6793219921987</v>
       </c>
       <c r="D37">
-        <v>457.8061749951628</v>
+        <v>384.9575219921987</v>
       </c>
       <c r="E37">
-        <v>219.97825</v>
+        <v>226.2832</v>
       </c>
       <c r="F37">
-        <v>220.67325</v>
+        <v>226.9782</v>
       </c>
       <c r="G37">
         <v>12.7</v>
@@ -4446,45 +4446,45 @@
         <v>26.2</v>
       </c>
       <c r="M37">
-        <v>32.39483310000001</v>
+        <v>45.57722256</v>
       </c>
       <c r="N37">
-        <v>-6.194833100000007</v>
+        <v>-19.37722256</v>
       </c>
       <c r="O37">
-        <v>-0.6194833100000008</v>
+        <v>-1.937722256</v>
       </c>
       <c r="P37">
-        <v>-5.575349790000007</v>
+        <v>-17.439500304</v>
       </c>
       <c r="Q37">
-        <v>-4.975349790000005</v>
+        <v>-16.839500304</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1691694001457658</v>
+        <v>0.1720786489322347</v>
       </c>
       <c r="T37">
-        <v>1.908485384084086</v>
+        <v>1.953490537558772</v>
       </c>
       <c r="U37">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.08087709518095958</v>
+        <v>0.05748485433817097</v>
       </c>
       <c r="W37">
-        <v>0.1349272424274351</v>
+        <v>0.1892570412488953</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8087709518095957</v>
+        <v>0.5748485433817097</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1782628701662325</v>
+        <v>0.1798128701662325</v>
       </c>
       <c r="C38">
-        <v>170.6793219921987</v>
+        <v>159.9219327723852</v>
       </c>
       <c r="D38">
-        <v>384.9575219921987</v>
+        <v>380.5050827723853</v>
       </c>
       <c r="E38">
-        <v>226.2832</v>
+        <v>232.58815</v>
       </c>
       <c r="F38">
-        <v>226.9782</v>
+        <v>233.28315</v>
       </c>
       <c r="G38">
         <v>12.7</v>
@@ -4528,37 +4528,37 @@
         <v>26.2</v>
       </c>
       <c r="M38">
-        <v>45.57722256</v>
+        <v>46.84325652</v>
       </c>
       <c r="N38">
-        <v>-19.37722256</v>
+        <v>-20.64325652</v>
       </c>
       <c r="O38">
-        <v>-1.937722256</v>
+        <v>-2.064325652</v>
       </c>
       <c r="P38">
-        <v>-17.439500304</v>
+        <v>-18.578930868</v>
       </c>
       <c r="Q38">
-        <v>-16.83950030399999</v>
+        <v>-17.978930868</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1720786489322347</v>
+        <v>0.174083071931159</v>
       </c>
       <c r="T38">
-        <v>1.953490537558772</v>
+        <v>1.984498323869228</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.05748485433817098</v>
+        <v>0.05593120962632851</v>
       </c>
       <c r="W38">
-        <v>0.1892570412488953</v>
+        <v>0.1895690131070333</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5748485433817098</v>
+        <v>0.5593120962632852</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1798128701662325</v>
+        <v>0.1813628701662325</v>
       </c>
       <c r="C39">
-        <v>159.9219327723852</v>
+        <v>149.2663602341196</v>
       </c>
       <c r="D39">
-        <v>380.5050827723853</v>
+        <v>376.1544602341196</v>
       </c>
       <c r="E39">
-        <v>232.58815</v>
+        <v>238.8931</v>
       </c>
       <c r="F39">
-        <v>233.28315</v>
+        <v>239.5881</v>
       </c>
       <c r="G39">
         <v>12.7</v>
@@ -4610,37 +4610,37 @@
         <v>26.2</v>
       </c>
       <c r="M39">
-        <v>46.84325652</v>
+        <v>48.10929048</v>
       </c>
       <c r="N39">
-        <v>-20.64325652</v>
+        <v>-21.90929048</v>
       </c>
       <c r="O39">
-        <v>-2.064325652</v>
+        <v>-2.190929048</v>
       </c>
       <c r="P39">
-        <v>-18.578930868</v>
+        <v>-19.718361432</v>
       </c>
       <c r="Q39">
-        <v>-17.978930868</v>
+        <v>-19.118361432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.174083071931159</v>
+        <v>0.1761521537365003</v>
       </c>
       <c r="T39">
-        <v>1.984498323869228</v>
+        <v>2.01650636135099</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.05593120962632851</v>
+        <v>0.05445933568879355</v>
       </c>
       <c r="W39">
-        <v>0.1895690131070333</v>
+        <v>0.1898645653936903</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5593120962632852</v>
+        <v>0.5445933568879355</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1813628701662325</v>
+        <v>0.1829128701662325</v>
       </c>
       <c r="C40">
-        <v>149.2663602341196</v>
+        <v>138.7091514005321</v>
       </c>
       <c r="D40">
-        <v>376.1544602341196</v>
+        <v>371.9022014005321</v>
       </c>
       <c r="E40">
-        <v>238.8931</v>
+        <v>245.19805</v>
       </c>
       <c r="F40">
-        <v>239.5881</v>
+        <v>245.89305</v>
       </c>
       <c r="G40">
         <v>12.7</v>
@@ -4692,37 +4692,37 @@
         <v>26.2</v>
       </c>
       <c r="M40">
-        <v>48.10929048</v>
+        <v>49.37532444000001</v>
       </c>
       <c r="N40">
-        <v>-21.90929048</v>
+        <v>-23.17532444000001</v>
       </c>
       <c r="O40">
-        <v>-2.190929048</v>
+        <v>-2.317532444000001</v>
       </c>
       <c r="P40">
-        <v>-19.718361432</v>
+        <v>-20.85779199600001</v>
       </c>
       <c r="Q40">
-        <v>-19.118361432</v>
+        <v>-20.25779199600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1761521537365003</v>
+        <v>0.1782890742895576</v>
       </c>
       <c r="T40">
-        <v>2.01650636135099</v>
+        <v>2.049563842684613</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05445933568879355</v>
+        <v>0.05306294246600397</v>
       </c>
       <c r="W40">
-        <v>0.1898645653936903</v>
+        <v>0.1901449611528264</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5445933568879355</v>
+        <v>0.5306294246600396</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1829128701662325</v>
+        <v>0.1844628701662325</v>
       </c>
       <c r="C41">
-        <v>138.7091514005321</v>
+        <v>128.2470076868887</v>
       </c>
       <c r="D41">
-        <v>371.9022014005321</v>
+        <v>367.7450076868887</v>
       </c>
       <c r="E41">
-        <v>245.19805</v>
+        <v>251.503</v>
       </c>
       <c r="F41">
-        <v>245.89305</v>
+        <v>252.198</v>
       </c>
       <c r="G41">
         <v>12.7</v>
@@ -4774,37 +4774,37 @@
         <v>26.2</v>
       </c>
       <c r="M41">
-        <v>49.37532444000001</v>
+        <v>50.6413584</v>
       </c>
       <c r="N41">
-        <v>-23.17532444000001</v>
+        <v>-24.4413584</v>
       </c>
       <c r="O41">
-        <v>-2.317532444000001</v>
+        <v>-2.44413584</v>
       </c>
       <c r="P41">
-        <v>-20.85779199600001</v>
+        <v>-21.99722256</v>
       </c>
       <c r="Q41">
-        <v>-20.25779199600001</v>
+        <v>-21.39722256</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1782890742895576</v>
+        <v>0.180497225527717</v>
       </c>
       <c r="T41">
-        <v>2.049563842684613</v>
+        <v>2.08372324006269</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05306294246600397</v>
+        <v>0.05173636890435387</v>
       </c>
       <c r="W41">
-        <v>0.1901449611528264</v>
+        <v>0.1904113371240058</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5306294246600396</v>
+        <v>0.5173636890435387</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1844628701662325</v>
+        <v>0.1860128701662325</v>
       </c>
       <c r="C42">
-        <v>128.2470076868887</v>
+        <v>117.876776366858</v>
       </c>
       <c r="D42">
-        <v>367.7450076868887</v>
+        <v>363.679726366858</v>
       </c>
       <c r="E42">
-        <v>251.503</v>
+        <v>257.80795</v>
       </c>
       <c r="F42">
-        <v>252.198</v>
+        <v>258.50295</v>
       </c>
       <c r="G42">
         <v>12.7</v>
@@ -4856,37 +4856,37 @@
         <v>26.2</v>
       </c>
       <c r="M42">
-        <v>50.6413584</v>
+        <v>51.90739236</v>
       </c>
       <c r="N42">
-        <v>-24.4413584</v>
+        <v>-25.70739236</v>
       </c>
       <c r="O42">
-        <v>-2.44413584</v>
+        <v>-2.570739236000001</v>
       </c>
       <c r="P42">
-        <v>-21.99722256</v>
+        <v>-23.136653124</v>
       </c>
       <c r="Q42">
-        <v>-21.39722256</v>
+        <v>-22.536653124</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.180497225527717</v>
+        <v>0.1827802293502206</v>
       </c>
       <c r="T42">
-        <v>2.08372324006269</v>
+        <v>2.1190405831146</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05173636890435387</v>
+        <v>0.05047450624815012</v>
       </c>
       <c r="W42">
-        <v>0.1904113371240058</v>
+        <v>0.1906647191453715</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5173636890435387</v>
+        <v>0.5047450624815012</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1860128701662325</v>
+        <v>0.2025163666313812</v>
       </c>
       <c r="C43">
-        <v>117.876776366858</v>
+        <v>73.27342009599784</v>
       </c>
       <c r="D43">
-        <v>363.679726366858</v>
+        <v>325.3813200959979</v>
       </c>
       <c r="E43">
-        <v>257.80795</v>
+        <v>264.1129</v>
       </c>
       <c r="F43">
-        <v>258.50295</v>
+        <v>264.8079</v>
       </c>
       <c r="G43">
         <v>12.7</v>
@@ -4938,45 +4938,45 @@
         <v>26.2</v>
       </c>
       <c r="M43">
-        <v>51.90739236</v>
+        <v>62.44170282</v>
       </c>
       <c r="N43">
-        <v>-25.70739236</v>
+        <v>-36.24170282</v>
       </c>
       <c r="O43">
-        <v>-2.570739236000001</v>
+        <v>-3.624170282</v>
       </c>
       <c r="P43">
-        <v>-23.136653124</v>
+        <v>-32.617532538</v>
       </c>
       <c r="Q43">
-        <v>-22.536653124</v>
+        <v>-32.017532538</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1827802293502206</v>
+        <v>0.1855790203134119</v>
       </c>
       <c r="T43">
-        <v>2.1190405831146</v>
+        <v>2.162336989192979</v>
       </c>
       <c r="U43">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05047450624815012</v>
+        <v>0.04195913759034799</v>
       </c>
       <c r="W43">
-        <v>0.1906647191453715</v>
+        <v>0.225906035356196</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.5047450624815012</v>
+        <v>0.4195913759034799</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2025163666313812</v>
+        <v>0.2044163666313812</v>
       </c>
       <c r="C44">
-        <v>73.27342009599784</v>
+        <v>63.07086153698248</v>
       </c>
       <c r="D44">
-        <v>325.3813200959979</v>
+        <v>321.4837115369825</v>
       </c>
       <c r="E44">
-        <v>264.1129</v>
+        <v>270.41785</v>
       </c>
       <c r="F44">
-        <v>264.8079</v>
+        <v>271.11285</v>
       </c>
       <c r="G44">
         <v>12.7</v>
@@ -5020,37 +5020,37 @@
         <v>26.2</v>
       </c>
       <c r="M44">
-        <v>62.44170282</v>
+        <v>63.92841002999999</v>
       </c>
       <c r="N44">
-        <v>-36.24170282</v>
+        <v>-37.72841002999999</v>
       </c>
       <c r="O44">
-        <v>-3.624170282</v>
+        <v>-3.772841002999999</v>
       </c>
       <c r="P44">
-        <v>-32.617532538</v>
+        <v>-33.955569027</v>
       </c>
       <c r="Q44">
-        <v>-32.017532538</v>
+        <v>-33.35556902699999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1855790203134119</v>
+        <v>0.1880312838276823</v>
       </c>
       <c r="T44">
-        <v>2.162336989192979</v>
+        <v>2.200272725845487</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04195913759034799</v>
+        <v>0.04098334369289804</v>
       </c>
       <c r="W44">
-        <v>0.225906035356196</v>
+        <v>0.2261361275572147</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4195913759034799</v>
+        <v>0.4098334369289804</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2044163666313812</v>
+        <v>0.2063163666313812</v>
       </c>
       <c r="C45">
-        <v>63.07086153698248</v>
+        <v>52.96057339770732</v>
       </c>
       <c r="D45">
-        <v>321.4837115369825</v>
+        <v>317.6783733977073</v>
       </c>
       <c r="E45">
-        <v>270.41785</v>
+        <v>276.7228</v>
       </c>
       <c r="F45">
-        <v>271.11285</v>
+        <v>277.4178</v>
       </c>
       <c r="G45">
         <v>12.7</v>
@@ -5102,37 +5102,37 @@
         <v>26.2</v>
       </c>
       <c r="M45">
-        <v>63.92841002999999</v>
+        <v>65.41511724</v>
       </c>
       <c r="N45">
-        <v>-37.72841002999999</v>
+        <v>-39.21511724</v>
       </c>
       <c r="O45">
-        <v>-3.772841002999999</v>
+        <v>-3.921511724</v>
       </c>
       <c r="P45">
-        <v>-33.955569027</v>
+        <v>-35.293605516</v>
       </c>
       <c r="Q45">
-        <v>-33.35556902699999</v>
+        <v>-34.693605516</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1880312838276823</v>
+        <v>0.190571128181748</v>
       </c>
       <c r="T45">
-        <v>2.200272725845487</v>
+        <v>2.239563310235585</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04098334369289804</v>
+        <v>0.04005190406351399</v>
       </c>
       <c r="W45">
-        <v>0.2261361275572147</v>
+        <v>0.2263557610218234</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4098334369289804</v>
+        <v>0.4005190406351399</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2063163666313812</v>
+        <v>0.2082163666313812</v>
       </c>
       <c r="C46">
-        <v>52.96057339770732</v>
+        <v>42.93931744914767</v>
       </c>
       <c r="D46">
-        <v>317.6783733977073</v>
+        <v>313.9620674491477</v>
       </c>
       <c r="E46">
-        <v>276.7228</v>
+        <v>283.02775</v>
       </c>
       <c r="F46">
-        <v>277.4178</v>
+        <v>283.72275</v>
       </c>
       <c r="G46">
         <v>12.7</v>
@@ -5184,37 +5184,37 @@
         <v>26.2</v>
       </c>
       <c r="M46">
-        <v>65.41511724</v>
+        <v>66.90182445000001</v>
       </c>
       <c r="N46">
-        <v>-39.21511724</v>
+        <v>-40.70182445</v>
       </c>
       <c r="O46">
-        <v>-3.921511724</v>
+        <v>-4.070182445</v>
       </c>
       <c r="P46">
-        <v>-35.293605516</v>
+        <v>-36.631642005</v>
       </c>
       <c r="Q46">
-        <v>-34.693605516</v>
+        <v>-36.031642005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.190571128181748</v>
+        <v>0.1932033305123252</v>
       </c>
       <c r="T46">
-        <v>2.239563310235585</v>
+        <v>2.280282643148959</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04005190406351399</v>
+        <v>0.03916186175099146</v>
       </c>
       <c r="W46">
-        <v>0.2263557610218234</v>
+        <v>0.2265656329991162</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4005190406351399</v>
+        <v>0.3916186175099146</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2082163666313812</v>
+        <v>0.2101163666313812</v>
       </c>
       <c r="C47">
-        <v>42.93931744914767</v>
+        <v>33.00400523762437</v>
       </c>
       <c r="D47">
-        <v>313.9620674491477</v>
+        <v>310.3317052376244</v>
       </c>
       <c r="E47">
-        <v>283.02775</v>
+        <v>289.3327</v>
       </c>
       <c r="F47">
-        <v>283.72275</v>
+        <v>290.0277</v>
       </c>
       <c r="G47">
         <v>12.7</v>
@@ -5266,37 +5266,37 @@
         <v>26.2</v>
       </c>
       <c r="M47">
-        <v>66.90182445000001</v>
+        <v>68.38853166000001</v>
       </c>
       <c r="N47">
-        <v>-40.70182445</v>
+        <v>-42.18853166000001</v>
       </c>
       <c r="O47">
-        <v>-4.070182445</v>
+        <v>-4.218853166000001</v>
       </c>
       <c r="P47">
-        <v>-36.631642005</v>
+        <v>-37.96967849400001</v>
       </c>
       <c r="Q47">
-        <v>-36.031642005</v>
+        <v>-37.36967849400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1932033305123252</v>
+        <v>0.195933021818109</v>
       </c>
       <c r="T47">
-        <v>2.280282643148959</v>
+        <v>2.32251009950357</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03916186175099146</v>
+        <v>0.03831051693031773</v>
       </c>
       <c r="W47">
-        <v>0.2265656329991162</v>
+        <v>0.2267663801078311</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3916186175099146</v>
+        <v>0.3831051693031773</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2101163666313812</v>
+        <v>0.2120163666313812</v>
       </c>
       <c r="C48">
-        <v>33.00400523762437</v>
+        <v>23.15168952448073</v>
       </c>
       <c r="D48">
-        <v>310.3317052376244</v>
+        <v>306.7843395244807</v>
       </c>
       <c r="E48">
-        <v>289.3327</v>
+        <v>295.63765</v>
       </c>
       <c r="F48">
-        <v>290.0277</v>
+        <v>296.33265</v>
       </c>
       <c r="G48">
         <v>12.7</v>
@@ -5348,37 +5348,37 @@
         <v>26.2</v>
       </c>
       <c r="M48">
-        <v>68.38853166000001</v>
+        <v>69.87523887</v>
       </c>
       <c r="N48">
-        <v>-42.18853166000001</v>
+        <v>-43.67523887</v>
       </c>
       <c r="O48">
-        <v>-4.218853166000001</v>
+        <v>-4.367523887</v>
       </c>
       <c r="P48">
-        <v>-37.96967849400001</v>
+        <v>-39.307714983</v>
       </c>
       <c r="Q48">
-        <v>-37.36967849400001</v>
+        <v>-38.707714983</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.195933021818109</v>
+        <v>0.198765720342979</v>
       </c>
       <c r="T48">
-        <v>2.32251009950357</v>
+        <v>2.366331044777222</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03831051693031773</v>
+        <v>0.0374953995488216</v>
       </c>
       <c r="W48">
-        <v>0.2267663801078311</v>
+        <v>0.2269585847863879</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3831051693031773</v>
+        <v>0.3749539954882161</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2120163666313812</v>
+        <v>0.2139163666313812</v>
       </c>
       <c r="C49">
-        <v>23.15168952448073</v>
+        <v>13.37955630623645</v>
       </c>
       <c r="D49">
-        <v>306.7843395244807</v>
+        <v>303.3171563062365</v>
       </c>
       <c r="E49">
-        <v>295.63765</v>
+        <v>301.9426</v>
       </c>
       <c r="F49">
-        <v>296.33265</v>
+        <v>302.6376</v>
       </c>
       <c r="G49">
         <v>12.7</v>
@@ -5430,37 +5430,37 @@
         <v>26.2</v>
       </c>
       <c r="M49">
-        <v>69.87523887</v>
+        <v>71.36194608000001</v>
       </c>
       <c r="N49">
-        <v>-43.67523887</v>
+        <v>-45.16194608000001</v>
       </c>
       <c r="O49">
-        <v>-4.367523887</v>
+        <v>-4.516194608000001</v>
       </c>
       <c r="P49">
-        <v>-39.307714983</v>
+        <v>-40.64575147200001</v>
       </c>
       <c r="Q49">
-        <v>-38.707714983</v>
+        <v>-40.04575147200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.198765720342979</v>
+        <v>0.2017073688111133</v>
       </c>
       <c r="T49">
-        <v>2.366331044777222</v>
+        <v>2.411837411022938</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0374953995488216</v>
+        <v>0.03671424539155448</v>
       </c>
       <c r="W49">
-        <v>0.2269585847863879</v>
+        <v>0.2271427809366715</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3749539954882161</v>
+        <v>0.3671424539155449</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2139163666313812</v>
+        <v>0.2158163666313812</v>
       </c>
       <c r="C50">
-        <v>13.37955630623657</v>
+        <v>3.684917369809796</v>
       </c>
       <c r="D50">
-        <v>303.3171563062365</v>
+        <v>299.9274673698098</v>
       </c>
       <c r="E50">
-        <v>301.9426</v>
+        <v>308.24755</v>
       </c>
       <c r="F50">
-        <v>302.6376</v>
+        <v>308.94255</v>
       </c>
       <c r="G50">
         <v>12.7</v>
@@ -5512,37 +5512,37 @@
         <v>26.2</v>
       </c>
       <c r="M50">
-        <v>71.36194608</v>
+        <v>72.84865329</v>
       </c>
       <c r="N50">
-        <v>-45.16194607999999</v>
+        <v>-46.64865329</v>
       </c>
       <c r="O50">
-        <v>-4.516194607999999</v>
+        <v>-4.664865329</v>
       </c>
       <c r="P50">
-        <v>-40.64575147199999</v>
+        <v>-41.983787961</v>
       </c>
       <c r="Q50">
-        <v>-40.04575147199999</v>
+        <v>-41.383787961</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2017073688111132</v>
+        <v>0.2047643760427037</v>
       </c>
       <c r="T50">
-        <v>2.411837411022938</v>
+        <v>2.459128340650838</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03671424539155449</v>
+        <v>0.03596497507744113</v>
       </c>
       <c r="W50">
-        <v>0.2271427809366715</v>
+        <v>0.2273194588767394</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.367142453915545</v>
+        <v>0.3596497507744114</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2158163666313812</v>
+        <v>0.2177163666313812</v>
       </c>
       <c r="C51">
-        <v>3.684917369809796</v>
+        <v>-5.934796658588482</v>
       </c>
       <c r="D51">
-        <v>299.9274673698098</v>
+        <v>296.6127033414115</v>
       </c>
       <c r="E51">
-        <v>308.24755</v>
+        <v>314.5525</v>
       </c>
       <c r="F51">
-        <v>308.94255</v>
+        <v>315.2475</v>
       </c>
       <c r="G51">
         <v>12.7</v>
@@ -5594,37 +5594,37 @@
         <v>26.2</v>
       </c>
       <c r="M51">
-        <v>72.84865329</v>
+        <v>74.33536050000001</v>
       </c>
       <c r="N51">
-        <v>-46.64865329</v>
+        <v>-48.1353605</v>
       </c>
       <c r="O51">
-        <v>-4.664865329</v>
+        <v>-4.813536050000001</v>
       </c>
       <c r="P51">
-        <v>-41.983787961</v>
+        <v>-43.32182445</v>
       </c>
       <c r="Q51">
-        <v>-41.383787961</v>
+        <v>-42.72182445</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2047643760427037</v>
+        <v>0.2079436635635578</v>
       </c>
       <c r="T51">
-        <v>2.459128340650838</v>
+        <v>2.508310907463855</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03596497507744113</v>
+        <v>0.0352456755758923</v>
       </c>
       <c r="W51">
-        <v>0.2273194588767394</v>
+        <v>0.2274890696992046</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3596497507744114</v>
+        <v>0.3524567557589231</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2177163666313812</v>
+        <v>0.2196163666313812</v>
       </c>
       <c r="C52">
-        <v>-5.934796658588482</v>
+        <v>-15.4820428086619</v>
       </c>
       <c r="D52">
-        <v>296.6127033414115</v>
+        <v>293.3704071913381</v>
       </c>
       <c r="E52">
-        <v>314.5525</v>
+        <v>320.85745</v>
       </c>
       <c r="F52">
-        <v>315.2475</v>
+        <v>321.55245</v>
       </c>
       <c r="G52">
         <v>12.7</v>
@@ -5676,37 +5676,37 @@
         <v>26.2</v>
       </c>
       <c r="M52">
-        <v>74.33536050000001</v>
+        <v>75.82206771000001</v>
       </c>
       <c r="N52">
-        <v>-48.1353605</v>
+        <v>-49.62206771000001</v>
       </c>
       <c r="O52">
-        <v>-4.813536050000001</v>
+        <v>-4.962206771000002</v>
       </c>
       <c r="P52">
-        <v>-43.32182445</v>
+        <v>-44.65986093900001</v>
       </c>
       <c r="Q52">
-        <v>-42.72182445</v>
+        <v>-44.05986093900001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2079436635635578</v>
+        <v>0.2112527179219977</v>
       </c>
       <c r="T52">
-        <v>2.508310907463855</v>
+        <v>2.559500925983526</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0352456755758923</v>
+        <v>0.03455458389793364</v>
       </c>
       <c r="W52">
-        <v>0.2274890696992046</v>
+        <v>0.2276520291168672</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3524567557589231</v>
+        <v>0.3455458389793363</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2196163666313812</v>
+        <v>0.2215163666313812</v>
       </c>
       <c r="C53">
-        <v>-15.4820428086619</v>
+        <v>-24.95917183984392</v>
       </c>
       <c r="D53">
-        <v>293.3704071913381</v>
+        <v>290.1982281601561</v>
       </c>
       <c r="E53">
-        <v>320.85745</v>
+        <v>327.1624</v>
       </c>
       <c r="F53">
-        <v>321.55245</v>
+        <v>327.8574</v>
       </c>
       <c r="G53">
         <v>12.7</v>
@@ -5758,37 +5758,37 @@
         <v>26.2</v>
       </c>
       <c r="M53">
-        <v>75.82206771000001</v>
+        <v>77.30877492000002</v>
       </c>
       <c r="N53">
-        <v>-49.62206771000001</v>
+        <v>-51.10877492000002</v>
       </c>
       <c r="O53">
-        <v>-4.962206771000002</v>
+        <v>-5.110877492000002</v>
       </c>
       <c r="P53">
-        <v>-44.65986093900001</v>
+        <v>-45.99789742800002</v>
       </c>
       <c r="Q53">
-        <v>-44.05986093900001</v>
+        <v>-45.39789742800001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2112527179219977</v>
+        <v>0.2146996495453727</v>
       </c>
       <c r="T53">
-        <v>2.559500925983526</v>
+        <v>2.612823861941516</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03455458389793364</v>
+        <v>0.03389007266912721</v>
       </c>
       <c r="W53">
-        <v>0.2276520291168672</v>
+        <v>0.2278087208646198</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3455458389793363</v>
+        <v>0.3389007266912721</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2215163666313812</v>
+        <v>0.2234163666313812</v>
       </c>
       <c r="C54">
-        <v>-24.95917183984392</v>
+        <v>-34.36843392527578</v>
       </c>
       <c r="D54">
-        <v>290.1982281601561</v>
+        <v>287.0939160747242</v>
       </c>
       <c r="E54">
-        <v>327.1624</v>
+        <v>333.46735</v>
       </c>
       <c r="F54">
-        <v>327.8574</v>
+        <v>334.16235</v>
       </c>
       <c r="G54">
         <v>12.7</v>
@@ -5840,37 +5840,37 @@
         <v>26.2</v>
       </c>
       <c r="M54">
-        <v>77.30877492000002</v>
+        <v>78.79548213000001</v>
       </c>
       <c r="N54">
-        <v>-51.10877492000002</v>
+        <v>-52.59548213000001</v>
       </c>
       <c r="O54">
-        <v>-5.110877492000002</v>
+        <v>-5.259548213000001</v>
       </c>
       <c r="P54">
-        <v>-45.99789742800002</v>
+        <v>-47.33593391700001</v>
       </c>
       <c r="Q54">
-        <v>-45.39789742800001</v>
+        <v>-46.735933917</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2146996495453727</v>
+        <v>0.2182932591101679</v>
       </c>
       <c r="T54">
-        <v>2.612823861941516</v>
+        <v>2.668415859004102</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03389007266912721</v>
+        <v>0.03325063733574746</v>
       </c>
       <c r="W54">
-        <v>0.2278087208646198</v>
+        <v>0.2279594997162308</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3389007266912721</v>
+        <v>0.3325063733574746</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2234163666313812</v>
+        <v>0.2253163666313812</v>
       </c>
       <c r="C55">
-        <v>-34.36843392527578</v>
+        <v>-43.71198397483039</v>
       </c>
       <c r="D55">
-        <v>287.0939160747242</v>
+        <v>284.0553160251696</v>
       </c>
       <c r="E55">
-        <v>333.46735</v>
+        <v>339.7723</v>
       </c>
       <c r="F55">
-        <v>334.16235</v>
+        <v>340.4673</v>
       </c>
       <c r="G55">
         <v>12.7</v>
@@ -5922,37 +5922,37 @@
         <v>26.2</v>
       </c>
       <c r="M55">
-        <v>78.79548213000001</v>
+        <v>80.28218934</v>
       </c>
       <c r="N55">
-        <v>-52.59548213000001</v>
+        <v>-54.08218934</v>
       </c>
       <c r="O55">
-        <v>-5.259548213000001</v>
+        <v>-5.408218934000001</v>
       </c>
       <c r="P55">
-        <v>-47.33593391700001</v>
+        <v>-48.673970406</v>
       </c>
       <c r="Q55">
-        <v>-46.735933917</v>
+        <v>-48.07397040599999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2182932591101679</v>
+        <v>0.2220431125690846</v>
       </c>
       <c r="T55">
-        <v>2.668415859004102</v>
+        <v>2.726424899417235</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03325063733574746</v>
+        <v>0.03263488479249288</v>
       </c>
       <c r="W55">
-        <v>0.2279594997162308</v>
+        <v>0.2281046941659302</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3325063733574746</v>
+        <v>0.3263488479249288</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2253163666313812</v>
+        <v>0.2272163666313812</v>
       </c>
       <c r="C56">
-        <v>-43.71198397483039</v>
+        <v>-52.99188662364207</v>
       </c>
       <c r="D56">
-        <v>284.0553160251696</v>
+        <v>281.080363376358</v>
       </c>
       <c r="E56">
-        <v>339.7723</v>
+        <v>346.07725</v>
       </c>
       <c r="F56">
-        <v>340.4673</v>
+        <v>346.77225</v>
       </c>
       <c r="G56">
         <v>12.7</v>
@@ -6004,37 +6004,37 @@
         <v>26.2</v>
       </c>
       <c r="M56">
-        <v>80.28218934</v>
+        <v>81.76889655000001</v>
       </c>
       <c r="N56">
-        <v>-54.08218934</v>
+        <v>-55.56889655000001</v>
       </c>
       <c r="O56">
-        <v>-5.408218934000001</v>
+        <v>-5.556889655000001</v>
       </c>
       <c r="P56">
-        <v>-48.673970406</v>
+        <v>-50.01200689500001</v>
       </c>
       <c r="Q56">
-        <v>-48.07397040599999</v>
+        <v>-49.412006895</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2220431125690846</v>
+        <v>0.2259596261817309</v>
       </c>
       <c r="T56">
-        <v>2.726424899417235</v>
+        <v>2.787012119404284</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03263488479249288</v>
+        <v>0.03204152325081119</v>
       </c>
       <c r="W56">
-        <v>0.2281046941659302</v>
+        <v>0.2282446088174587</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3263488479249288</v>
+        <v>0.3204152325081119</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2272163666313812</v>
+        <v>0.2291163666313812</v>
       </c>
       <c r="C57">
-        <v>-52.99188662364207</v>
+        <v>-62.21012091041268</v>
       </c>
       <c r="D57">
-        <v>281.080363376358</v>
+        <v>278.1670790895874</v>
       </c>
       <c r="E57">
-        <v>346.07725</v>
+        <v>352.3822000000001</v>
       </c>
       <c r="F57">
-        <v>346.77225</v>
+        <v>353.0772000000001</v>
       </c>
       <c r="G57">
         <v>12.7</v>
@@ -6086,37 +6086,37 @@
         <v>26.2</v>
       </c>
       <c r="M57">
-        <v>81.76889655000001</v>
+        <v>83.25560376000001</v>
       </c>
       <c r="N57">
-        <v>-55.56889655000001</v>
+        <v>-57.05560376000001</v>
       </c>
       <c r="O57">
-        <v>-5.556889655000001</v>
+        <v>-5.705560376000001</v>
       </c>
       <c r="P57">
-        <v>-50.01200689500001</v>
+        <v>-51.35004338400001</v>
       </c>
       <c r="Q57">
-        <v>-49.412006895</v>
+        <v>-50.75004338400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2259596261817309</v>
+        <v>0.2300541631404066</v>
       </c>
       <c r="T57">
-        <v>2.787012119404284</v>
+        <v>2.850353303936199</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03204152325081119</v>
+        <v>0.03146935319276099</v>
       </c>
       <c r="W57">
-        <v>0.2282446088174587</v>
+        <v>0.228379526517147</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3204152325081119</v>
+        <v>0.3146935319276098</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2291163666313812</v>
+        <v>0.2310163666313812</v>
       </c>
       <c r="C58">
-        <v>-62.21012091041268</v>
+        <v>-71.36858466776908</v>
       </c>
       <c r="D58">
-        <v>278.1670790895874</v>
+        <v>275.313565332231</v>
       </c>
       <c r="E58">
-        <v>352.3822000000001</v>
+        <v>358.68715</v>
       </c>
       <c r="F58">
-        <v>353.0772000000001</v>
+        <v>359.38215</v>
       </c>
       <c r="G58">
         <v>12.7</v>
@@ -6168,37 +6168,37 @@
         <v>26.2</v>
       </c>
       <c r="M58">
-        <v>83.25560376000001</v>
+        <v>84.74231097000001</v>
       </c>
       <c r="N58">
-        <v>-57.05560376000001</v>
+        <v>-58.54231097</v>
       </c>
       <c r="O58">
-        <v>-5.705560376000001</v>
+        <v>-5.854231097</v>
       </c>
       <c r="P58">
-        <v>-51.35004338400001</v>
+        <v>-52.688079873</v>
       </c>
       <c r="Q58">
-        <v>-50.75004338400001</v>
+        <v>-52.088079873</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2300541631404066</v>
+        <v>0.2343391436785556</v>
       </c>
       <c r="T58">
-        <v>2.850353303936199</v>
+        <v>2.916640590074251</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03146935319276099</v>
+        <v>0.03091725927709851</v>
       </c>
       <c r="W58">
-        <v>0.228379526517147</v>
+        <v>0.2285097102624602</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3146935319276098</v>
+        <v>0.3091725927709852</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2310163666313812</v>
+        <v>0.2329163666313812</v>
       </c>
       <c r="C59">
-        <v>-71.36858466776908</v>
+        <v>-80.46909864514015</v>
       </c>
       <c r="D59">
-        <v>275.313565332231</v>
+        <v>272.5180013548599</v>
       </c>
       <c r="E59">
-        <v>358.68715</v>
+        <v>364.9921000000001</v>
       </c>
       <c r="F59">
-        <v>359.38215</v>
+        <v>365.6871</v>
       </c>
       <c r="G59">
         <v>12.7</v>
@@ -6250,37 +6250,37 @@
         <v>26.2</v>
       </c>
       <c r="M59">
-        <v>84.74231097000001</v>
+        <v>86.22901818000001</v>
       </c>
       <c r="N59">
-        <v>-58.54231097</v>
+        <v>-60.02901818000001</v>
       </c>
       <c r="O59">
-        <v>-5.854231097</v>
+        <v>-6.002901818000002</v>
       </c>
       <c r="P59">
-        <v>-52.688079873</v>
+        <v>-54.02611636200001</v>
       </c>
       <c r="Q59">
-        <v>-52.088079873</v>
+        <v>-53.42611636200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2343391436785556</v>
+        <v>0.2388281709089974</v>
       </c>
       <c r="T59">
-        <v>2.916640590074251</v>
+        <v>2.986084413647448</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03091725927709851</v>
+        <v>0.03038420308266578</v>
       </c>
       <c r="W59">
-        <v>0.2285097102624602</v>
+        <v>0.2286354049131074</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3091725927709852</v>
+        <v>0.3038420308266578</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2329163666313812</v>
+        <v>0.2348163666313812</v>
       </c>
       <c r="C60">
-        <v>-80.46909864514004</v>
+        <v>-89.51341038297312</v>
       </c>
       <c r="D60">
-        <v>272.51800135486</v>
+        <v>269.7786396170269</v>
       </c>
       <c r="E60">
-        <v>364.9921</v>
+        <v>371.29705</v>
       </c>
       <c r="F60">
-        <v>365.6871</v>
+        <v>371.99205</v>
       </c>
       <c r="G60">
         <v>12.7</v>
@@ -6332,37 +6332,37 @@
         <v>26.2</v>
       </c>
       <c r="M60">
-        <v>86.22901818</v>
+        <v>87.71572539</v>
       </c>
       <c r="N60">
-        <v>-60.02901817999999</v>
+        <v>-61.51572539</v>
       </c>
       <c r="O60">
-        <v>-6.002901818</v>
+        <v>-6.151572539</v>
       </c>
       <c r="P60">
-        <v>-54.026116362</v>
+        <v>-55.364152851</v>
       </c>
       <c r="Q60">
-        <v>-53.42611636199999</v>
+        <v>-54.764152851</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2388281709089974</v>
+        <v>0.2435361750775095</v>
       </c>
       <c r="T60">
-        <v>2.986084413647447</v>
+        <v>3.058915740809579</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03038420308266579</v>
+        <v>0.02986921658973925</v>
       </c>
       <c r="W60">
-        <v>0.2286354049131074</v>
+        <v>0.2287568387281395</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3038420308266578</v>
+        <v>0.2986921658973924</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2348163666313812</v>
+        <v>0.2367163666313812</v>
       </c>
       <c r="C61">
-        <v>-89.51341038297312</v>
+        <v>-98.50319785561385</v>
       </c>
       <c r="D61">
-        <v>269.7786396170269</v>
+        <v>267.0938021443861</v>
       </c>
       <c r="E61">
-        <v>371.29705</v>
+        <v>377.602</v>
       </c>
       <c r="F61">
-        <v>371.99205</v>
+        <v>378.297</v>
       </c>
       <c r="G61">
         <v>12.7</v>
@@ -6414,37 +6414,37 @@
         <v>26.2</v>
       </c>
       <c r="M61">
-        <v>87.71572539</v>
+        <v>89.20243259999999</v>
       </c>
       <c r="N61">
-        <v>-61.51572539</v>
+        <v>-63.00243259999999</v>
       </c>
       <c r="O61">
-        <v>-6.151572539</v>
+        <v>-6.300243259999999</v>
       </c>
       <c r="P61">
-        <v>-55.364152851</v>
+        <v>-56.70218933999999</v>
       </c>
       <c r="Q61">
-        <v>-54.764152851</v>
+        <v>-56.10218933999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2435361750775095</v>
+        <v>0.2484795794544472</v>
       </c>
       <c r="T61">
-        <v>3.058915740809579</v>
+        <v>3.13538863432982</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02986921658973925</v>
+        <v>0.02937139631324359</v>
       </c>
       <c r="W61">
-        <v>0.2287568387281395</v>
+        <v>0.2288742247493372</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2986921658973924</v>
+        <v>0.2937139631324359</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2367163666313812</v>
+        <v>0.2386163666313812</v>
       </c>
       <c r="C62">
-        <v>-98.50319785561385</v>
+        <v>-107.4400728988055</v>
       </c>
       <c r="D62">
-        <v>267.0938021443861</v>
+        <v>264.4618771011945</v>
       </c>
       <c r="E62">
-        <v>377.602</v>
+        <v>383.90695</v>
       </c>
       <c r="F62">
-        <v>378.297</v>
+        <v>384.60195</v>
       </c>
       <c r="G62">
         <v>12.7</v>
@@ -6496,37 +6496,37 @@
         <v>26.2</v>
       </c>
       <c r="M62">
-        <v>89.20243259999999</v>
+        <v>90.68913981</v>
       </c>
       <c r="N62">
-        <v>-63.00243259999999</v>
+        <v>-64.48913981</v>
       </c>
       <c r="O62">
-        <v>-6.300243259999999</v>
+        <v>-6.448913981</v>
       </c>
       <c r="P62">
-        <v>-56.70218933999999</v>
+        <v>-58.04022582899999</v>
       </c>
       <c r="Q62">
-        <v>-56.10218933999999</v>
+        <v>-57.44022582899999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2484795794544472</v>
+        <v>0.253676491748151</v>
       </c>
       <c r="T62">
-        <v>3.13538863432982</v>
+        <v>3.215783214697251</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02937139631324359</v>
+        <v>0.02888989801302648</v>
       </c>
       <c r="W62">
-        <v>0.2288742247493372</v>
+        <v>0.2289877620485284</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2937139631324359</v>
+        <v>0.2888989801302648</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2386163666313812</v>
+        <v>0.2405163666313812</v>
       </c>
       <c r="C63">
-        <v>-107.4400728988055</v>
+        <v>-116.3255844365189</v>
       </c>
       <c r="D63">
-        <v>264.4618771011945</v>
+        <v>261.8813155634811</v>
       </c>
       <c r="E63">
-        <v>383.90695</v>
+        <v>390.2119</v>
       </c>
       <c r="F63">
-        <v>384.60195</v>
+        <v>390.9069</v>
       </c>
       <c r="G63">
         <v>12.7</v>
@@ -6578,37 +6578,37 @@
         <v>26.2</v>
       </c>
       <c r="M63">
-        <v>90.68913981</v>
+        <v>92.17584702000001</v>
       </c>
       <c r="N63">
-        <v>-64.48913981</v>
+        <v>-65.97584702</v>
       </c>
       <c r="O63">
-        <v>-6.448913981</v>
+        <v>-6.597584702000001</v>
       </c>
       <c r="P63">
-        <v>-58.04022582899999</v>
+        <v>-59.378262318</v>
       </c>
       <c r="Q63">
-        <v>-57.44022582899999</v>
+        <v>-58.778262318</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.253676491748151</v>
+        <v>0.2591469257415234</v>
       </c>
       <c r="T63">
-        <v>3.215783214697251</v>
+        <v>3.300409088768231</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02888989801302648</v>
+        <v>0.02842393191604219</v>
       </c>
       <c r="W63">
-        <v>0.2289877620485284</v>
+        <v>0.2290976368541973</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2888989801302648</v>
+        <v>0.2842393191604219</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2405163666313812</v>
+        <v>0.2424163666313812</v>
       </c>
       <c r="C64">
-        <v>-116.3255844365189</v>
+        <v>-125.1612215206898</v>
       </c>
       <c r="D64">
-        <v>261.8813155634811</v>
+        <v>259.3506284793103</v>
       </c>
       <c r="E64">
-        <v>390.2119</v>
+        <v>396.51685</v>
       </c>
       <c r="F64">
-        <v>390.9069</v>
+        <v>397.21185</v>
       </c>
       <c r="G64">
         <v>12.7</v>
@@ -6660,37 +6660,37 @@
         <v>26.2</v>
       </c>
       <c r="M64">
-        <v>92.17584702000001</v>
+        <v>93.66255423000001</v>
       </c>
       <c r="N64">
-        <v>-65.97584702</v>
+        <v>-67.46255423000001</v>
       </c>
       <c r="O64">
-        <v>-6.597584702000001</v>
+        <v>-6.746255423000001</v>
       </c>
       <c r="P64">
-        <v>-59.378262318</v>
+        <v>-60.71629880700001</v>
       </c>
       <c r="Q64">
-        <v>-58.778262318</v>
+        <v>-60.11629880700001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2591469257415234</v>
+        <v>0.2649130588696727</v>
       </c>
       <c r="T64">
-        <v>3.300409088768231</v>
+        <v>3.389609334410616</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02842393191604219</v>
+        <v>0.02797275839356532</v>
       </c>
       <c r="W64">
-        <v>0.2290976368541973</v>
+        <v>0.2292040235707973</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2842393191604219</v>
+        <v>0.2797275839356532</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2424163666313812</v>
+        <v>0.2443163666313812</v>
       </c>
       <c r="C65">
-        <v>-125.1612215206898</v>
+        <v>-133.9484161963928</v>
       </c>
       <c r="D65">
-        <v>259.3506284793103</v>
+        <v>256.8683838036072</v>
       </c>
       <c r="E65">
-        <v>396.51685</v>
+        <v>402.8218</v>
       </c>
       <c r="F65">
-        <v>397.21185</v>
+        <v>403.5168</v>
       </c>
       <c r="G65">
         <v>12.7</v>
@@ -6742,37 +6742,37 @@
         <v>26.2</v>
       </c>
       <c r="M65">
-        <v>93.66255423000001</v>
+        <v>95.14926144</v>
       </c>
       <c r="N65">
-        <v>-67.46255423000001</v>
+        <v>-68.94926144</v>
       </c>
       <c r="O65">
-        <v>-6.746255423000001</v>
+        <v>-6.894926144</v>
       </c>
       <c r="P65">
-        <v>-60.71629880700001</v>
+        <v>-62.054335296</v>
       </c>
       <c r="Q65">
-        <v>-60.11629880700001</v>
+        <v>-61.454335296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2649130588696727</v>
+        <v>0.2709995327271635</v>
       </c>
       <c r="T65">
-        <v>3.389609334410616</v>
+        <v>3.483765149255355</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02797275839356532</v>
+        <v>0.02753568404366587</v>
       </c>
       <c r="W65">
-        <v>0.2292040235707973</v>
+        <v>0.2293070857025036</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2797275839356532</v>
+        <v>0.2753568404366586</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2443163666313812</v>
+        <v>0.2462163666313812</v>
       </c>
       <c r="C66">
-        <v>-133.9484161963928</v>
+        <v>-142.6885462040442</v>
       </c>
       <c r="D66">
-        <v>256.8683838036072</v>
+        <v>254.4332037959558</v>
       </c>
       <c r="E66">
-        <v>402.8218</v>
+        <v>409.12675</v>
       </c>
       <c r="F66">
-        <v>403.5168</v>
+        <v>409.82175</v>
       </c>
       <c r="G66">
         <v>12.7</v>
@@ -6824,37 +6824,37 @@
         <v>26.2</v>
       </c>
       <c r="M66">
-        <v>95.14926144</v>
+        <v>96.63596865000001</v>
       </c>
       <c r="N66">
-        <v>-68.94926144</v>
+        <v>-70.43596865000001</v>
       </c>
       <c r="O66">
-        <v>-6.894926144</v>
+        <v>-7.043596865000001</v>
       </c>
       <c r="P66">
-        <v>-62.054335296</v>
+        <v>-63.39237178500001</v>
       </c>
       <c r="Q66">
-        <v>-61.454335296</v>
+        <v>-62.79237178500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2709995327271635</v>
+        <v>0.2774338050907968</v>
       </c>
       <c r="T66">
-        <v>3.483765149255355</v>
+        <v>3.583301296376936</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02753568404366587</v>
+        <v>0.02711205813530178</v>
       </c>
       <c r="W66">
-        <v>0.2293070857025036</v>
+        <v>0.2294069766916959</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2753568404366586</v>
+        <v>0.2711205813530178</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2462163666313812</v>
+        <v>0.2481163666313812</v>
       </c>
       <c r="C67">
-        <v>-142.6885462040442</v>
+        <v>-151.3829375293381</v>
       </c>
       <c r="D67">
-        <v>254.4332037959558</v>
+        <v>252.043762470662</v>
       </c>
       <c r="E67">
-        <v>409.12675</v>
+        <v>415.4317</v>
       </c>
       <c r="F67">
-        <v>409.82175</v>
+        <v>416.1267</v>
       </c>
       <c r="G67">
         <v>12.7</v>
@@ -6906,37 +6906,37 @@
         <v>26.2</v>
       </c>
       <c r="M67">
-        <v>96.63596865000001</v>
+        <v>98.12267586000002</v>
       </c>
       <c r="N67">
-        <v>-70.43596865000001</v>
+        <v>-71.92267586000001</v>
       </c>
       <c r="O67">
-        <v>-7.043596865000001</v>
+        <v>-7.192267586000002</v>
       </c>
       <c r="P67">
-        <v>-63.39237178500001</v>
+        <v>-64.73040827400001</v>
       </c>
       <c r="Q67">
-        <v>-62.79237178500001</v>
+        <v>-64.13040827400002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2774338050907968</v>
+        <v>0.2842465640640556</v>
       </c>
       <c r="T67">
-        <v>3.583301296376936</v>
+        <v>3.688692510976258</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02711205813530178</v>
+        <v>0.02670126937567599</v>
       </c>
       <c r="W67">
-        <v>0.2294069766916959</v>
+        <v>0.2295038406812156</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2711205813530178</v>
+        <v>0.26701269375676</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2481163666313812</v>
+        <v>0.2500163666313812</v>
       </c>
       <c r="C68">
-        <v>-151.3829375293381</v>
+        <v>-160.0328668108403</v>
       </c>
       <c r="D68">
-        <v>252.043762470662</v>
+        <v>249.6987831891597</v>
       </c>
       <c r="E68">
-        <v>415.4317</v>
+        <v>421.7366500000001</v>
       </c>
       <c r="F68">
-        <v>416.1267</v>
+        <v>422.43165</v>
       </c>
       <c r="G68">
         <v>12.7</v>
@@ -6988,37 +6988,37 @@
         <v>26.2</v>
       </c>
       <c r="M68">
-        <v>98.12267586000002</v>
+        <v>99.60938307000002</v>
       </c>
       <c r="N68">
-        <v>-71.92267586000001</v>
+        <v>-73.40938307000002</v>
       </c>
       <c r="O68">
-        <v>-7.192267586000002</v>
+        <v>-7.340938307000002</v>
       </c>
       <c r="P68">
-        <v>-64.73040827400001</v>
+        <v>-66.06844476300002</v>
       </c>
       <c r="Q68">
-        <v>-64.13040827400002</v>
+        <v>-65.46844476300001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2842465640640556</v>
+        <v>0.2914722175205421</v>
       </c>
       <c r="T68">
-        <v>3.688692510976258</v>
+        <v>3.800471071914933</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02670126937567599</v>
+        <v>0.02630274296708381</v>
       </c>
       <c r="W68">
-        <v>0.2295038406812156</v>
+        <v>0.2295978132083616</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.26701269375676</v>
+        <v>0.2630274296708381</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2500163666313812</v>
+        <v>0.2519163666313812</v>
       </c>
       <c r="C69">
-        <v>-160.0328668108403</v>
+        <v>-168.6395636144208</v>
       </c>
       <c r="D69">
-        <v>249.6987831891597</v>
+        <v>247.3970363855792</v>
       </c>
       <c r="E69">
-        <v>421.7366500000001</v>
+        <v>428.0416</v>
       </c>
       <c r="F69">
-        <v>422.43165</v>
+        <v>428.7366</v>
       </c>
       <c r="G69">
         <v>12.7</v>
@@ -7070,37 +7070,37 @@
         <v>26.2</v>
       </c>
       <c r="M69">
-        <v>99.60938307000002</v>
+        <v>101.09609028</v>
       </c>
       <c r="N69">
-        <v>-73.40938307000002</v>
+        <v>-74.89609028000001</v>
       </c>
       <c r="O69">
-        <v>-7.340938307000002</v>
+        <v>-7.489609028000001</v>
       </c>
       <c r="P69">
-        <v>-66.06844476300002</v>
+        <v>-67.40648125200001</v>
       </c>
       <c r="Q69">
-        <v>-65.46844476300001</v>
+        <v>-66.806481252</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2914722175205421</v>
+        <v>0.2991494743180591</v>
       </c>
       <c r="T69">
-        <v>3.800471071914933</v>
+        <v>3.919235792912275</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02630274296708381</v>
+        <v>0.02591593792345022</v>
       </c>
       <c r="W69">
-        <v>0.2295978132083616</v>
+        <v>0.2296890218376504</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2630274296708381</v>
+        <v>0.2591593792345023</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2519163666313812</v>
+        <v>0.2538163666313812</v>
       </c>
       <c r="C70">
-        <v>-168.6395636144208</v>
+        <v>-177.2042125830388</v>
       </c>
       <c r="D70">
-        <v>247.3970363855792</v>
+        <v>245.1373374169613</v>
       </c>
       <c r="E70">
-        <v>428.0416</v>
+        <v>434.34655</v>
       </c>
       <c r="F70">
-        <v>428.7366</v>
+        <v>435.04155</v>
       </c>
       <c r="G70">
         <v>12.7</v>
@@ -7152,37 +7152,37 @@
         <v>26.2</v>
       </c>
       <c r="M70">
-        <v>101.09609028</v>
+        <v>102.58279749</v>
       </c>
       <c r="N70">
-        <v>-74.89609028000001</v>
+        <v>-76.38279749</v>
       </c>
       <c r="O70">
-        <v>-7.489609028000001</v>
+        <v>-7.638279749000001</v>
       </c>
       <c r="P70">
-        <v>-67.40648125200001</v>
+        <v>-68.744517741</v>
       </c>
       <c r="Q70">
-        <v>-66.806481252</v>
+        <v>-68.14451774099999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2991494743180591</v>
+        <v>0.3073220380057384</v>
       </c>
       <c r="T70">
-        <v>3.919235792912275</v>
+        <v>4.045662753973962</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02591593792345022</v>
+        <v>0.02554034462021182</v>
       </c>
       <c r="W70">
-        <v>0.2296890218376504</v>
+        <v>0.2297775867385541</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2591593792345023</v>
+        <v>0.2554034462021182</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2538163666313812</v>
+        <v>0.2557163666313812</v>
       </c>
       <c r="C71">
-        <v>-177.2042125830388</v>
+        <v>-185.7279554697798</v>
       </c>
       <c r="D71">
-        <v>245.1373374169613</v>
+        <v>242.9185445302203</v>
       </c>
       <c r="E71">
-        <v>434.34655</v>
+        <v>440.6515000000001</v>
       </c>
       <c r="F71">
-        <v>435.04155</v>
+        <v>441.3465</v>
       </c>
       <c r="G71">
         <v>12.7</v>
@@ -7234,37 +7234,37 @@
         <v>26.2</v>
       </c>
       <c r="M71">
-        <v>102.58279749</v>
+        <v>104.0695047</v>
       </c>
       <c r="N71">
-        <v>-76.38279749</v>
+        <v>-77.86950470000001</v>
       </c>
       <c r="O71">
-        <v>-7.638279749000001</v>
+        <v>-7.786950470000001</v>
       </c>
       <c r="P71">
-        <v>-68.744517741</v>
+        <v>-70.08255423</v>
       </c>
       <c r="Q71">
-        <v>-68.14451774099999</v>
+        <v>-69.48255423000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3073220380057384</v>
+        <v>0.3160394392725964</v>
       </c>
       <c r="T71">
-        <v>4.045662753973962</v>
+        <v>4.180518179106427</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02554034462021182</v>
+        <v>0.02517548255420879</v>
       </c>
       <c r="W71">
-        <v>0.2297775867385541</v>
+        <v>0.2298636212137176</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2554034462021182</v>
+        <v>0.2517548255420879</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2557163666313812</v>
+        <v>0.2576163666313812</v>
       </c>
       <c r="C72">
-        <v>-185.7279554697798</v>
+        <v>-194.2118930614736</v>
       </c>
       <c r="D72">
-        <v>242.9185445302203</v>
+        <v>240.7395569385265</v>
       </c>
       <c r="E72">
-        <v>440.6515000000001</v>
+        <v>446.9564500000001</v>
       </c>
       <c r="F72">
-        <v>441.3465</v>
+        <v>447.6514500000001</v>
       </c>
       <c r="G72">
         <v>12.7</v>
@@ -7316,37 +7316,37 @@
         <v>26.2</v>
       </c>
       <c r="M72">
-        <v>104.0695047</v>
+        <v>105.55621191</v>
       </c>
       <c r="N72">
-        <v>-77.86950470000001</v>
+        <v>-79.35621191000001</v>
       </c>
       <c r="O72">
-        <v>-7.786950470000001</v>
+        <v>-7.935621191000002</v>
       </c>
       <c r="P72">
-        <v>-70.08255423</v>
+        <v>-71.42059071900002</v>
       </c>
       <c r="Q72">
-        <v>-69.48255423000001</v>
+        <v>-70.82059071900002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3160394392725964</v>
+        <v>0.3253580406268239</v>
       </c>
       <c r="T72">
-        <v>4.180518179106427</v>
+        <v>4.32467397838596</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02517548255420879</v>
+        <v>0.02482089829288191</v>
       </c>
       <c r="W72">
-        <v>0.2298636212137176</v>
+        <v>0.2299472321825385</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2517548255420879</v>
+        <v>0.2482089829288191</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2576163666313812</v>
+        <v>0.2595163666313812</v>
       </c>
       <c r="C73">
-        <v>-194.2118930614735</v>
+        <v>-202.6570869997027</v>
       </c>
       <c r="D73">
-        <v>240.7395569385265</v>
+        <v>238.5993130002973</v>
       </c>
       <c r="E73">
-        <v>446.95645</v>
+        <v>453.2614</v>
       </c>
       <c r="F73">
-        <v>447.65145</v>
+        <v>453.9564</v>
       </c>
       <c r="G73">
         <v>12.7</v>
@@ -7398,37 +7398,37 @@
         <v>26.2</v>
       </c>
       <c r="M73">
-        <v>105.55621191</v>
+        <v>107.04291912</v>
       </c>
       <c r="N73">
-        <v>-79.35621190999998</v>
+        <v>-80.84291911999999</v>
       </c>
       <c r="O73">
-        <v>-7.935621190999999</v>
+        <v>-8.084291911999999</v>
       </c>
       <c r="P73">
-        <v>-71.42059071899999</v>
+        <v>-72.75862720799999</v>
       </c>
       <c r="Q73">
-        <v>-70.82059071899999</v>
+        <v>-72.15862720799998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3253580406268238</v>
+        <v>0.335342256363496</v>
       </c>
       <c r="T73">
-        <v>4.324673978385958</v>
+        <v>4.47912662047117</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02482089829288191</v>
+        <v>0.02447616359436966</v>
       </c>
       <c r="W73">
-        <v>0.2299472321825385</v>
+        <v>0.2300285206244476</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2482089829288191</v>
+        <v>0.2447616359436966</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2595163666313812</v>
+        <v>0.2614163666313812</v>
       </c>
       <c r="C74">
-        <v>-202.6570869997027</v>
+        <v>-211.064561505533</v>
       </c>
       <c r="D74">
-        <v>238.5993130002973</v>
+        <v>236.496788494467</v>
       </c>
       <c r="E74">
-        <v>453.2614</v>
+        <v>459.56635</v>
       </c>
       <c r="F74">
-        <v>453.9564</v>
+        <v>460.26135</v>
       </c>
       <c r="G74">
         <v>12.7</v>
@@ -7480,37 +7480,37 @@
         <v>26.2</v>
       </c>
       <c r="M74">
-        <v>107.04291912</v>
+        <v>108.52962633</v>
       </c>
       <c r="N74">
-        <v>-80.84291911999999</v>
+        <v>-82.32962633</v>
       </c>
       <c r="O74">
-        <v>-8.084291911999999</v>
+        <v>-8.232962633</v>
       </c>
       <c r="P74">
-        <v>-72.75862720799999</v>
+        <v>-74.096663697</v>
       </c>
       <c r="Q74">
-        <v>-72.15862720799998</v>
+        <v>-73.496663697</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.335342256363496</v>
+        <v>0.3460660436362181</v>
       </c>
       <c r="T74">
-        <v>4.47912662047117</v>
+        <v>4.645020199007139</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02447616359436966</v>
+        <v>0.02414087368211802</v>
       </c>
       <c r="W74">
-        <v>0.2300285206244476</v>
+        <v>0.2301075819857566</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2447616359436966</v>
+        <v>0.2414087368211802</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2614163666313812</v>
+        <v>0.2633163666313811</v>
       </c>
       <c r="C75">
-        <v>-211.064561505533</v>
+        <v>-219.4353050138484</v>
       </c>
       <c r="D75">
-        <v>236.496788494467</v>
+        <v>234.4309949861516</v>
       </c>
       <c r="E75">
-        <v>459.56635</v>
+        <v>465.8713</v>
       </c>
       <c r="F75">
-        <v>460.26135</v>
+        <v>466.5663</v>
       </c>
       <c r="G75">
         <v>12.7</v>
@@ -7562,37 +7562,37 @@
         <v>26.2</v>
       </c>
       <c r="M75">
-        <v>108.52962633</v>
+        <v>110.01633354</v>
       </c>
       <c r="N75">
-        <v>-82.32962633</v>
+        <v>-83.81633354</v>
       </c>
       <c r="O75">
-        <v>-8.232962633</v>
+        <v>-8.381633354</v>
       </c>
       <c r="P75">
-        <v>-74.096663697</v>
+        <v>-75.434700186</v>
       </c>
       <c r="Q75">
-        <v>-73.496663697</v>
+        <v>-74.83470018599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3460660436362181</v>
+        <v>0.3576147376222265</v>
       </c>
       <c r="T75">
-        <v>4.645020199007139</v>
+        <v>4.823674822045875</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02414087368211802</v>
+        <v>0.02381464565938669</v>
       </c>
       <c r="W75">
-        <v>0.2301075819857566</v>
+        <v>0.2301845065535166</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2414087368211802</v>
+        <v>0.238146456593867</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2633163666313811</v>
+        <v>0.2652163666313812</v>
       </c>
       <c r="C76">
-        <v>-219.4353050138484</v>
+        <v>-227.7702717227752</v>
       </c>
       <c r="D76">
-        <v>234.4309949861516</v>
+        <v>232.4009782772249</v>
       </c>
       <c r="E76">
-        <v>465.8713</v>
+        <v>472.17625</v>
       </c>
       <c r="F76">
-        <v>466.5663</v>
+        <v>472.87125</v>
       </c>
       <c r="G76">
         <v>12.7</v>
@@ -7644,37 +7644,37 @@
         <v>26.2</v>
       </c>
       <c r="M76">
-        <v>110.01633354</v>
+        <v>111.50304075</v>
       </c>
       <c r="N76">
-        <v>-83.81633354</v>
+        <v>-85.30304075000001</v>
       </c>
       <c r="O76">
-        <v>-8.381633354</v>
+        <v>-8.530304075000002</v>
       </c>
       <c r="P76">
-        <v>-75.434700186</v>
+        <v>-76.772736675</v>
       </c>
       <c r="Q76">
-        <v>-74.83470018599999</v>
+        <v>-76.17273667500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3576147376222265</v>
+        <v>0.3700873271271156</v>
       </c>
       <c r="T76">
-        <v>4.823674822045875</v>
+        <v>5.016621814927711</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02381464565938669</v>
+        <v>0.02349711705059487</v>
       </c>
       <c r="W76">
-        <v>0.2301845065535166</v>
+        <v>0.2302593797994697</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.238146456593867</v>
+        <v>0.2349711705059487</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2652163666313812</v>
+        <v>0.2671163666313812</v>
       </c>
       <c r="C77">
-        <v>-227.7702717227752</v>
+        <v>-236.0703830632927</v>
       </c>
       <c r="D77">
-        <v>232.4009782772249</v>
+        <v>230.4058169367073</v>
       </c>
       <c r="E77">
-        <v>472.17625</v>
+        <v>478.4812</v>
       </c>
       <c r="F77">
-        <v>472.87125</v>
+        <v>479.1762</v>
       </c>
       <c r="G77">
         <v>12.7</v>
@@ -7726,37 +7726,37 @@
         <v>26.2</v>
       </c>
       <c r="M77">
-        <v>111.50304075</v>
+        <v>112.98974796</v>
       </c>
       <c r="N77">
-        <v>-85.30304075000001</v>
+        <v>-86.78974796</v>
       </c>
       <c r="O77">
-        <v>-8.530304075000002</v>
+        <v>-8.678974796</v>
       </c>
       <c r="P77">
-        <v>-76.772736675</v>
+        <v>-78.11077316399999</v>
       </c>
       <c r="Q77">
-        <v>-76.17273667500001</v>
+        <v>-77.510773164</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3700873271271156</v>
+        <v>0.3835992990907454</v>
       </c>
       <c r="T77">
-        <v>5.016621814927711</v>
+        <v>5.225647723883032</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02349711705059487</v>
+        <v>0.02318794445782389</v>
       </c>
       <c r="W77">
-        <v>0.2302593797994697</v>
+        <v>0.2303322826968451</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2349711705059487</v>
+        <v>0.2318794445782389</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2671163666313812</v>
+        <v>0.2690163666313812</v>
       </c>
       <c r="C78">
-        <v>-236.0703830632927</v>
+        <v>-244.3365290937911</v>
       </c>
       <c r="D78">
-        <v>230.4058169367073</v>
+        <v>228.4446209062089</v>
       </c>
       <c r="E78">
-        <v>478.4812</v>
+        <v>484.78615</v>
       </c>
       <c r="F78">
-        <v>479.1762</v>
+        <v>485.48115</v>
       </c>
       <c r="G78">
         <v>12.7</v>
@@ -7808,37 +7808,37 @@
         <v>26.2</v>
       </c>
       <c r="M78">
-        <v>112.98974796</v>
+        <v>114.47645517</v>
       </c>
       <c r="N78">
-        <v>-86.78974796</v>
+        <v>-88.27645517000001</v>
       </c>
       <c r="O78">
-        <v>-8.678974796</v>
+        <v>-8.827645517000001</v>
       </c>
       <c r="P78">
-        <v>-78.11077316399999</v>
+        <v>-79.44880965300001</v>
       </c>
       <c r="Q78">
-        <v>-77.510773164</v>
+        <v>-78.84880965300002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3835992990907454</v>
+        <v>0.3982862251381691</v>
       </c>
       <c r="T78">
-        <v>5.225647723883032</v>
+        <v>5.452849798834469</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02318794445782389</v>
+        <v>0.02288680232200799</v>
       </c>
       <c r="W78">
-        <v>0.2303322826968451</v>
+        <v>0.2304032920124705</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2318794445782389</v>
+        <v>0.2288680232200799</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2690163666313812</v>
+        <v>0.2709163666313812</v>
       </c>
       <c r="C79">
-        <v>-244.3365290937911</v>
+        <v>-252.5695698240068</v>
       </c>
       <c r="D79">
-        <v>228.4446209062089</v>
+        <v>226.5165301759932</v>
       </c>
       <c r="E79">
-        <v>484.78615</v>
+        <v>491.0911</v>
       </c>
       <c r="F79">
-        <v>485.48115</v>
+        <v>491.7861</v>
       </c>
       <c r="G79">
         <v>12.7</v>
@@ -7890,37 +7890,37 @@
         <v>26.2</v>
       </c>
       <c r="M79">
-        <v>114.47645517</v>
+        <v>115.96316238</v>
       </c>
       <c r="N79">
-        <v>-88.27645517000001</v>
+        <v>-89.76316238000001</v>
       </c>
       <c r="O79">
-        <v>-8.827645517000001</v>
+        <v>-8.976316238000001</v>
       </c>
       <c r="P79">
-        <v>-79.44880965300001</v>
+        <v>-80.78684614200002</v>
       </c>
       <c r="Q79">
-        <v>-78.84880965300002</v>
+        <v>-80.18684614200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3982862251381691</v>
+        <v>0.4143083262808131</v>
       </c>
       <c r="T79">
-        <v>5.452849798834469</v>
+        <v>5.700706607872398</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02288680232200799</v>
+        <v>0.02259338177941815</v>
       </c>
       <c r="W79">
-        <v>0.2304032920124705</v>
+        <v>0.2304724805764132</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2288680232200799</v>
+        <v>0.2259338177941814</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2709163666313812</v>
+        <v>0.2728163666313812</v>
       </c>
       <c r="C80">
-        <v>-252.5695698240068</v>
+        <v>-260.7703364724744</v>
       </c>
       <c r="D80">
-        <v>226.5165301759932</v>
+        <v>224.6207135275257</v>
       </c>
       <c r="E80">
-        <v>491.0911</v>
+        <v>497.3960500000001</v>
       </c>
       <c r="F80">
-        <v>491.7861</v>
+        <v>498.0910500000001</v>
       </c>
       <c r="G80">
         <v>12.7</v>
@@ -7972,37 +7972,37 @@
         <v>26.2</v>
       </c>
       <c r="M80">
-        <v>115.96316238</v>
+        <v>117.44986959</v>
       </c>
       <c r="N80">
-        <v>-89.76316238000001</v>
+        <v>-91.24986959000002</v>
       </c>
       <c r="O80">
-        <v>-8.976316238000001</v>
+        <v>-9.124986959000003</v>
       </c>
       <c r="P80">
-        <v>-80.78684614200002</v>
+        <v>-82.12488263100002</v>
       </c>
       <c r="Q80">
-        <v>-80.18684614200001</v>
+        <v>-81.52488263100003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4143083262808131</v>
+        <v>0.4318563418179947</v>
       </c>
       <c r="T80">
-        <v>5.700706607872398</v>
+        <v>5.972168827294894</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02259338177941815</v>
+        <v>0.02230738960499513</v>
       </c>
       <c r="W80">
-        <v>0.2304724805764132</v>
+        <v>0.2305399175311422</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2259338177941814</v>
+        <v>0.2230738960499513</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2728163666313812</v>
+        <v>0.2747163666313812</v>
       </c>
       <c r="C81">
-        <v>-260.7703364724744</v>
+        <v>-268.939632661358</v>
       </c>
       <c r="D81">
-        <v>224.6207135275257</v>
+        <v>222.7563673386421</v>
       </c>
       <c r="E81">
-        <v>497.3960500000001</v>
+        <v>503.701</v>
       </c>
       <c r="F81">
-        <v>498.0910500000001</v>
+        <v>504.396</v>
       </c>
       <c r="G81">
         <v>12.7</v>
@@ -8054,37 +8054,37 @@
         <v>26.2</v>
       </c>
       <c r="M81">
-        <v>117.44986959</v>
+        <v>118.9365768</v>
       </c>
       <c r="N81">
-        <v>-91.24986959000002</v>
+        <v>-92.73657680000001</v>
       </c>
       <c r="O81">
-        <v>-9.124986959000003</v>
+        <v>-9.273657680000001</v>
       </c>
       <c r="P81">
-        <v>-82.12488263100002</v>
+        <v>-83.46291912000001</v>
       </c>
       <c r="Q81">
-        <v>-81.52488263100003</v>
+        <v>-82.86291912000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4318563418179947</v>
+        <v>0.4511591589088945</v>
       </c>
       <c r="T81">
-        <v>5.972168827294894</v>
+        <v>6.27077726865964</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02230738960499513</v>
+        <v>0.02202854723493269</v>
       </c>
       <c r="W81">
-        <v>0.2305399175311422</v>
+        <v>0.2306056685620029</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2230738960499513</v>
+        <v>0.2202854723493269</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2747163666313812</v>
+        <v>0.2766163666313812</v>
       </c>
       <c r="C82">
-        <v>-268.939632661358</v>
+        <v>-277.0782355522699</v>
       </c>
       <c r="D82">
-        <v>222.7563673386421</v>
+        <v>220.9227144477301</v>
       </c>
       <c r="E82">
-        <v>503.701</v>
+        <v>510.00595</v>
       </c>
       <c r="F82">
-        <v>504.396</v>
+        <v>510.70095</v>
       </c>
       <c r="G82">
         <v>12.7</v>
@@ -8136,37 +8136,37 @@
         <v>26.2</v>
       </c>
       <c r="M82">
-        <v>118.9365768</v>
+        <v>120.42328401</v>
       </c>
       <c r="N82">
-        <v>-92.73657680000001</v>
+        <v>-94.22328401000001</v>
       </c>
       <c r="O82">
-        <v>-9.273657680000001</v>
+        <v>-9.422328401000001</v>
       </c>
       <c r="P82">
-        <v>-83.46291912000001</v>
+        <v>-84.80095560900001</v>
       </c>
       <c r="Q82">
-        <v>-82.86291912000002</v>
+        <v>-84.200955609</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4511591589088945</v>
+        <v>0.4724938514830468</v>
       </c>
       <c r="T82">
-        <v>6.27077726865964</v>
+        <v>6.600818177536462</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02202854723493269</v>
+        <v>0.02175658986166192</v>
       </c>
       <c r="W82">
-        <v>0.2306056685620029</v>
+        <v>0.2306697961106201</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2202854723493269</v>
+        <v>0.2175658986166192</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2766163666313812</v>
+        <v>0.2785163666313812</v>
       </c>
       <c r="C83">
-        <v>-277.0782355522699</v>
+        <v>-285.1868969264492</v>
       </c>
       <c r="D83">
-        <v>220.9227144477301</v>
+        <v>219.1190030735509</v>
       </c>
       <c r="E83">
-        <v>510.00595</v>
+        <v>516.3108999999999</v>
       </c>
       <c r="F83">
-        <v>510.70095</v>
+        <v>517.0059</v>
       </c>
       <c r="G83">
         <v>12.7</v>
@@ -8218,37 +8218,37 @@
         <v>26.2</v>
       </c>
       <c r="M83">
-        <v>120.42328401</v>
+        <v>121.90999122</v>
       </c>
       <c r="N83">
-        <v>-94.22328401000001</v>
+        <v>-95.70999122000001</v>
       </c>
       <c r="O83">
-        <v>-9.422328401000001</v>
+        <v>-9.570999122000002</v>
       </c>
       <c r="P83">
-        <v>-84.80095560900001</v>
+        <v>-86.138992098</v>
       </c>
       <c r="Q83">
-        <v>-84.200955609</v>
+        <v>-85.53899209799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4724938514830468</v>
+        <v>0.4961990654543272</v>
       </c>
       <c r="T83">
-        <v>6.600818177536462</v>
+        <v>6.967530298510711</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02175658986166192</v>
+        <v>0.02149126559505629</v>
       </c>
       <c r="W83">
-        <v>0.2306697961106201</v>
+        <v>0.2307323595726857</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2175658986166192</v>
+        <v>0.2149126559505629</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2785163666313812</v>
+        <v>0.2804163666313813</v>
       </c>
       <c r="C84">
-        <v>-285.1868969264492</v>
+        <v>-293.2663442124543</v>
       </c>
       <c r="D84">
-        <v>219.1190030735509</v>
+        <v>217.3445057875458</v>
       </c>
       <c r="E84">
-        <v>516.3108999999999</v>
+        <v>522.61585</v>
       </c>
       <c r="F84">
-        <v>517.0059</v>
+        <v>523.3108500000001</v>
       </c>
       <c r="G84">
         <v>12.7</v>
@@ -8300,37 +8300,37 @@
         <v>26.2</v>
       </c>
       <c r="M84">
-        <v>121.90999122</v>
+        <v>123.39669843</v>
       </c>
       <c r="N84">
-        <v>-95.70999122000001</v>
+        <v>-97.19669843000003</v>
       </c>
       <c r="O84">
-        <v>-9.570999122000002</v>
+        <v>-9.719669843000004</v>
       </c>
       <c r="P84">
-        <v>-86.138992098</v>
+        <v>-87.47702858700002</v>
       </c>
       <c r="Q84">
-        <v>-85.53899209799999</v>
+        <v>-86.87702858700001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4961990654543272</v>
+        <v>0.5226931281281113</v>
       </c>
       <c r="T84">
-        <v>6.967530298510711</v>
+        <v>7.377385021952519</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02149126559505629</v>
+        <v>0.02123233468427247</v>
       </c>
       <c r="W84">
-        <v>0.2307323595726857</v>
+        <v>0.2307934154814486</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2149126559505629</v>
+        <v>0.2123233468427247</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2804163666313813</v>
+        <v>0.2823163666313812</v>
       </c>
       <c r="C85">
-        <v>-293.2663442124543</v>
+        <v>-301.3172814643214</v>
       </c>
       <c r="D85">
-        <v>217.3445057875458</v>
+        <v>215.5985185356787</v>
       </c>
       <c r="E85">
-        <v>522.61585</v>
+        <v>528.9208</v>
       </c>
       <c r="F85">
-        <v>523.3108500000001</v>
+        <v>529.6158</v>
       </c>
       <c r="G85">
         <v>12.7</v>
@@ -8382,37 +8382,37 @@
         <v>26.2</v>
       </c>
       <c r="M85">
-        <v>123.39669843</v>
+        <v>124.88340564</v>
       </c>
       <c r="N85">
-        <v>-97.19669843000003</v>
+        <v>-98.68340564</v>
       </c>
       <c r="O85">
-        <v>-9.719669843000004</v>
+        <v>-9.868340564</v>
       </c>
       <c r="P85">
-        <v>-87.47702858700002</v>
+        <v>-88.815065076</v>
       </c>
       <c r="Q85">
-        <v>-86.87702858700001</v>
+        <v>-88.215065076</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5226931281281113</v>
+        <v>0.5524989486361183</v>
       </c>
       <c r="T85">
-        <v>7.377385021952519</v>
+        <v>7.838471585824552</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02123233468427247</v>
+        <v>0.02097956879517399</v>
       </c>
       <c r="W85">
-        <v>0.2307934154814486</v>
+        <v>0.230853017678098</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2123233468427247</v>
+        <v>0.20979568795174</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2823163666313812</v>
+        <v>0.2842163666313812</v>
       </c>
       <c r="C86">
-        <v>-301.3172814643214</v>
+        <v>-309.3403902929522</v>
       </c>
       <c r="D86">
-        <v>215.5985185356787</v>
+        <v>213.8803597070479</v>
       </c>
       <c r="E86">
-        <v>528.9208</v>
+        <v>535.2257499999999</v>
       </c>
       <c r="F86">
-        <v>529.6158</v>
+        <v>535.92075</v>
       </c>
       <c r="G86">
         <v>12.7</v>
@@ -8464,37 +8464,37 @@
         <v>26.2</v>
       </c>
       <c r="M86">
-        <v>124.88340564</v>
+        <v>126.37011285</v>
       </c>
       <c r="N86">
-        <v>-98.68340564</v>
+        <v>-100.17011285</v>
       </c>
       <c r="O86">
-        <v>-9.868340564</v>
+        <v>-10.017011285</v>
       </c>
       <c r="P86">
-        <v>-88.815065076</v>
+        <v>-90.153101565</v>
       </c>
       <c r="Q86">
-        <v>-88.215065076</v>
+        <v>-89.55310156499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5524989486361178</v>
+        <v>0.5862788785451925</v>
       </c>
       <c r="T86">
-        <v>7.838471585824546</v>
+        <v>8.36103635821285</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02097956879517399</v>
+        <v>0.02073275033876018</v>
       </c>
       <c r="W86">
-        <v>0.230853017678098</v>
+        <v>0.2309112174701204</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.20979568795174</v>
+        <v>0.2073275033876019</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2842163666313812</v>
+        <v>0.2861163666313812</v>
       </c>
       <c r="C87">
-        <v>-309.3403902929522</v>
+        <v>-317.3363307533177</v>
       </c>
       <c r="D87">
-        <v>213.8803597070479</v>
+        <v>212.1893692466822</v>
       </c>
       <c r="E87">
-        <v>535.2257499999999</v>
+        <v>541.5306999999999</v>
       </c>
       <c r="F87">
-        <v>535.92075</v>
+        <v>542.2257</v>
       </c>
       <c r="G87">
         <v>12.7</v>
@@ -8546,37 +8546,37 @@
         <v>26.2</v>
       </c>
       <c r="M87">
-        <v>126.37011285</v>
+        <v>127.85682006</v>
       </c>
       <c r="N87">
-        <v>-100.17011285</v>
+        <v>-101.65682006</v>
       </c>
       <c r="O87">
-        <v>-10.017011285</v>
+        <v>-10.165682006</v>
       </c>
       <c r="P87">
-        <v>-90.153101565</v>
+        <v>-91.49113805399999</v>
       </c>
       <c r="Q87">
-        <v>-89.55310156499999</v>
+        <v>-90.89113805399998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5862788785451925</v>
+        <v>0.624884512726992</v>
       </c>
       <c r="T87">
-        <v>8.36103635821285</v>
+        <v>8.958253240942341</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02073275033876018</v>
+        <v>0.02049167184644902</v>
       </c>
       <c r="W87">
-        <v>0.2309112174701204</v>
+        <v>0.2309680637786073</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2073275033876019</v>
+        <v>0.2049167184644902</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2861163666313812</v>
+        <v>0.2880163666313812</v>
       </c>
       <c r="C88">
-        <v>-317.3363307533177</v>
+        <v>-325.3057421899071</v>
       </c>
       <c r="D88">
-        <v>212.1893692466822</v>
+        <v>210.524907810093</v>
       </c>
       <c r="E88">
-        <v>541.5306999999999</v>
+        <v>547.83565</v>
       </c>
       <c r="F88">
-        <v>542.2257</v>
+        <v>548.53065</v>
       </c>
       <c r="G88">
         <v>12.7</v>
@@ -8628,37 +8628,37 @@
         <v>26.2</v>
       </c>
       <c r="M88">
-        <v>127.85682006</v>
+        <v>129.34352727</v>
       </c>
       <c r="N88">
-        <v>-101.65682006</v>
+        <v>-103.14352727</v>
       </c>
       <c r="O88">
-        <v>-10.165682006</v>
+        <v>-10.314352727</v>
       </c>
       <c r="P88">
-        <v>-91.49113805399999</v>
+        <v>-92.82917454300001</v>
       </c>
       <c r="Q88">
-        <v>-90.89113805399998</v>
+        <v>-92.229174543</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.624884512726992</v>
+        <v>0.6694294752444528</v>
       </c>
       <c r="T88">
-        <v>8.958253240942341</v>
+        <v>9.647349644091751</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02049167184644902</v>
+        <v>0.02025613538844385</v>
       </c>
       <c r="W88">
-        <v>0.2309680637786073</v>
+        <v>0.2310236032754049</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2049167184644902</v>
+        <v>0.2025613538844385</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2880163666313812</v>
+        <v>0.2899163666313812</v>
       </c>
       <c r="C89">
-        <v>-325.3057421899071</v>
+        <v>-333.2492440426928</v>
       </c>
       <c r="D89">
-        <v>210.524907810093</v>
+        <v>208.8863559573072</v>
       </c>
       <c r="E89">
-        <v>547.83565</v>
+        <v>554.1405999999999</v>
       </c>
       <c r="F89">
-        <v>548.53065</v>
+        <v>554.8356</v>
       </c>
       <c r="G89">
         <v>12.7</v>
@@ -8710,37 +8710,37 @@
         <v>26.2</v>
       </c>
       <c r="M89">
-        <v>129.34352727</v>
+        <v>130.83023448</v>
       </c>
       <c r="N89">
-        <v>-103.14352727</v>
+        <v>-104.63023448</v>
       </c>
       <c r="O89">
-        <v>-10.314352727</v>
+        <v>-10.463023448</v>
       </c>
       <c r="P89">
-        <v>-92.82917454300001</v>
+        <v>-94.167211032</v>
       </c>
       <c r="Q89">
-        <v>-92.229174543</v>
+        <v>-93.56721103199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6694294752444528</v>
+        <v>0.7213985981814907</v>
       </c>
       <c r="T89">
-        <v>9.647349644091751</v>
+        <v>10.45129544776606</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02025613538844385</v>
+        <v>0.020025952031757</v>
       </c>
       <c r="W89">
-        <v>0.2310236032754049</v>
+        <v>0.2310778805109117</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2025613538844385</v>
+        <v>0.20025952031757</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2899163666313812</v>
+        <v>0.2918163666313812</v>
       </c>
       <c r="C90">
-        <v>-333.2492440426928</v>
+        <v>-341.1674366157511</v>
       </c>
       <c r="D90">
-        <v>208.8863559573072</v>
+        <v>207.2731133842489</v>
       </c>
       <c r="E90">
-        <v>554.1405999999999</v>
+        <v>560.4455499999999</v>
       </c>
       <c r="F90">
-        <v>554.8356</v>
+        <v>561.14055</v>
       </c>
       <c r="G90">
         <v>12.7</v>
@@ -8792,37 +8792,37 @@
         <v>26.2</v>
       </c>
       <c r="M90">
-        <v>130.83023448</v>
+        <v>132.31694169</v>
       </c>
       <c r="N90">
-        <v>-104.63023448</v>
+        <v>-106.11694169</v>
       </c>
       <c r="O90">
-        <v>-10.463023448</v>
+        <v>-10.611694169</v>
       </c>
       <c r="P90">
-        <v>-94.167211032</v>
+        <v>-95.50524752099999</v>
       </c>
       <c r="Q90">
-        <v>-93.56721103199999</v>
+        <v>-94.90524752099998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7213985981814907</v>
+        <v>0.7828166525616264</v>
       </c>
       <c r="T90">
-        <v>10.45129544776606</v>
+        <v>11.4014132157448</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.020025952031757</v>
+        <v>0.01980094133477096</v>
       </c>
       <c r="W90">
-        <v>0.2310778805109117</v>
+        <v>0.231130938033261</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.20025952031757</v>
+        <v>0.1980094133477096</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2918163666313812</v>
+        <v>0.2937163666313812</v>
       </c>
       <c r="C91">
-        <v>-341.1674366157511</v>
+        <v>-349.0609018105372</v>
       </c>
       <c r="D91">
-        <v>207.2731133842489</v>
+        <v>205.6845981894629</v>
       </c>
       <c r="E91">
-        <v>560.4455499999999</v>
+        <v>566.7505</v>
       </c>
       <c r="F91">
-        <v>561.14055</v>
+        <v>567.4455</v>
       </c>
       <c r="G91">
         <v>12.7</v>
@@ -8874,37 +8874,37 @@
         <v>26.2</v>
       </c>
       <c r="M91">
-        <v>132.31694169</v>
+        <v>133.8036489</v>
       </c>
       <c r="N91">
-        <v>-106.11694169</v>
+        <v>-107.6036489</v>
       </c>
       <c r="O91">
-        <v>-10.611694169</v>
+        <v>-10.76036489</v>
       </c>
       <c r="P91">
-        <v>-95.50524752099999</v>
+        <v>-96.84328401</v>
       </c>
       <c r="Q91">
-        <v>-94.90524752099998</v>
+        <v>-96.24328401</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7828166525616264</v>
+        <v>0.856518317817789</v>
       </c>
       <c r="T91">
-        <v>11.4014132157448</v>
+        <v>12.54155453731928</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01980094133477096</v>
+        <v>0.01958093087549573</v>
       </c>
       <c r="W91">
-        <v>0.231130938033261</v>
+        <v>0.2311828164995581</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1980094133477096</v>
+        <v>0.1958093087549573</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2937163666313812</v>
+        <v>0.2956163666313812</v>
       </c>
       <c r="C92">
-        <v>-349.0609018105372</v>
+        <v>-356.930203825698</v>
       </c>
       <c r="D92">
-        <v>205.6845981894629</v>
+        <v>204.120246174302</v>
       </c>
       <c r="E92">
-        <v>566.7505</v>
+        <v>573.05545</v>
       </c>
       <c r="F92">
-        <v>567.4455</v>
+        <v>573.75045</v>
       </c>
       <c r="G92">
         <v>12.7</v>
@@ -8956,37 +8956,37 @@
         <v>26.2</v>
       </c>
       <c r="M92">
-        <v>133.8036489</v>
+        <v>135.29035611</v>
       </c>
       <c r="N92">
-        <v>-107.6036489</v>
+        <v>-109.09035611</v>
       </c>
       <c r="O92">
-        <v>-10.76036489</v>
+        <v>-10.909035611</v>
       </c>
       <c r="P92">
-        <v>-96.84328401</v>
+        <v>-98.18132049900001</v>
       </c>
       <c r="Q92">
-        <v>-96.24328401</v>
+        <v>-97.58132049900001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.856518317817789</v>
+        <v>0.9465981309086545</v>
       </c>
       <c r="T92">
-        <v>12.54155453731928</v>
+        <v>13.93506059702142</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01958093087549573</v>
+        <v>0.01936575581092984</v>
       </c>
       <c r="W92">
-        <v>0.2311828164995581</v>
+        <v>0.2312335547797828</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1958093087549573</v>
+        <v>0.1936575581092984</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2956163666313812</v>
+        <v>0.2975163666313812</v>
       </c>
       <c r="C93">
-        <v>-356.930203825698</v>
+        <v>-364.7758898251936</v>
       </c>
       <c r="D93">
-        <v>204.120246174302</v>
+        <v>202.5795101748065</v>
       </c>
       <c r="E93">
-        <v>573.05545</v>
+        <v>579.3604</v>
       </c>
       <c r="F93">
-        <v>573.75045</v>
+        <v>580.0554000000001</v>
       </c>
       <c r="G93">
         <v>12.7</v>
@@ -9038,37 +9038,37 @@
         <v>26.2</v>
       </c>
       <c r="M93">
-        <v>135.29035611</v>
+        <v>136.77706332</v>
       </c>
       <c r="N93">
-        <v>-109.09035611</v>
+        <v>-110.57706332</v>
       </c>
       <c r="O93">
-        <v>-10.909035611</v>
+        <v>-11.057706332</v>
       </c>
       <c r="P93">
-        <v>-98.18132049900001</v>
+        <v>-99.51935698800003</v>
       </c>
       <c r="Q93">
-        <v>-97.58132049900001</v>
+        <v>-98.91935698800003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9465981309086545</v>
+        <v>1.059197897272237</v>
       </c>
       <c r="T93">
-        <v>13.93506059702142</v>
+        <v>15.67694317164911</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01936575581092984</v>
+        <v>0.01915525846515886</v>
       </c>
       <c r="W93">
-        <v>0.2312335547797828</v>
+        <v>0.2312831900539155</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1936575581092984</v>
+        <v>0.1915525846515886</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2975163666313812</v>
+        <v>0.2994163666313812</v>
       </c>
       <c r="C94">
-        <v>-364.7758898251936</v>
+        <v>-372.5984905763833</v>
       </c>
       <c r="D94">
-        <v>202.5795101748065</v>
+        <v>201.0618594236168</v>
       </c>
       <c r="E94">
-        <v>579.3604</v>
+        <v>585.66535</v>
       </c>
       <c r="F94">
-        <v>580.0554000000001</v>
+        <v>586.36035</v>
       </c>
       <c r="G94">
         <v>12.7</v>
@@ -9120,37 +9120,37 @@
         <v>26.2</v>
       </c>
       <c r="M94">
-        <v>136.77706332</v>
+        <v>138.26377053</v>
       </c>
       <c r="N94">
-        <v>-110.57706332</v>
+        <v>-112.06377053</v>
       </c>
       <c r="O94">
-        <v>-11.057706332</v>
+        <v>-11.206377053</v>
       </c>
       <c r="P94">
-        <v>-99.51935698800003</v>
+        <v>-100.857393477</v>
       </c>
       <c r="Q94">
-        <v>-98.91935698800003</v>
+        <v>-100.257393477</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.059197897272237</v>
+        <v>1.203969025453985</v>
       </c>
       <c r="T94">
-        <v>15.67694317164911</v>
+        <v>17.91650648188469</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01915525846515886</v>
+        <v>0.01894928794402812</v>
       </c>
       <c r="W94">
-        <v>0.2312831900539155</v>
+        <v>0.2313317579027982</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1915525846515886</v>
+        <v>0.1894928794402813</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2994163666313812</v>
+        <v>0.3013163666313812</v>
       </c>
       <c r="C95">
-        <v>-372.5984905763833</v>
+        <v>-380.3985210596463</v>
       </c>
       <c r="D95">
-        <v>201.0618594236168</v>
+        <v>199.5667789403537</v>
       </c>
       <c r="E95">
-        <v>585.66535</v>
+        <v>591.9703</v>
       </c>
       <c r="F95">
-        <v>586.36035</v>
+        <v>592.6653</v>
       </c>
       <c r="G95">
         <v>12.7</v>
@@ -9202,37 +9202,37 @@
         <v>26.2</v>
       </c>
       <c r="M95">
-        <v>138.26377053</v>
+        <v>139.75047774</v>
       </c>
       <c r="N95">
-        <v>-112.06377053</v>
+        <v>-113.55047774</v>
       </c>
       <c r="O95">
-        <v>-11.206377053</v>
+        <v>-11.355047774</v>
       </c>
       <c r="P95">
-        <v>-100.857393477</v>
+        <v>-102.195429966</v>
       </c>
       <c r="Q95">
-        <v>-100.257393477</v>
+        <v>-101.595429966</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.203969025453985</v>
+        <v>1.396997196362983</v>
       </c>
       <c r="T95">
-        <v>17.91650648188469</v>
+        <v>20.90259089553215</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01894928794402812</v>
+        <v>0.0187476997744108</v>
       </c>
       <c r="W95">
-        <v>0.2313317579027982</v>
+        <v>0.2313792923931939</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1894928794402813</v>
+        <v>0.1874769977441081</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3013163666313812</v>
+        <v>0.3032163666313812</v>
       </c>
       <c r="C96">
-        <v>-380.3985210596463</v>
+        <v>-388.1764810510028</v>
       </c>
       <c r="D96">
-        <v>199.5667789403537</v>
+        <v>198.0937689489973</v>
       </c>
       <c r="E96">
-        <v>591.9703</v>
+        <v>598.27525</v>
       </c>
       <c r="F96">
-        <v>592.6653</v>
+        <v>598.9702500000001</v>
       </c>
       <c r="G96">
         <v>12.7</v>
@@ -9284,37 +9284,37 @@
         <v>26.2</v>
       </c>
       <c r="M96">
-        <v>139.75047774</v>
+        <v>141.23718495</v>
       </c>
       <c r="N96">
-        <v>-113.55047774</v>
+        <v>-115.03718495</v>
       </c>
       <c r="O96">
-        <v>-11.355047774</v>
+        <v>-11.503718495</v>
       </c>
       <c r="P96">
-        <v>-102.195429966</v>
+        <v>-103.533466455</v>
       </c>
       <c r="Q96">
-        <v>-101.595429966</v>
+        <v>-102.933466455</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.396997196362983</v>
+        <v>1.66723663563558</v>
       </c>
       <c r="T96">
-        <v>20.90259089553215</v>
+        <v>25.08310907463859</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0187476997744108</v>
+        <v>0.01855035556625911</v>
       </c>
       <c r="W96">
-        <v>0.2313792923931939</v>
+        <v>0.2314258261574761</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1874769977441081</v>
+        <v>0.1855035556625911</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3032163666313812</v>
+        <v>0.3051163666313812</v>
       </c>
       <c r="C97">
-        <v>-388.1764810510028</v>
+        <v>-395.9328556791216</v>
       </c>
       <c r="D97">
-        <v>198.0937689489973</v>
+        <v>196.6423443208784</v>
       </c>
       <c r="E97">
-        <v>598.27525</v>
+        <v>604.5802</v>
       </c>
       <c r="F97">
-        <v>598.9702500000001</v>
+        <v>605.2752</v>
       </c>
       <c r="G97">
         <v>12.7</v>
@@ -9366,37 +9366,37 @@
         <v>26.2</v>
       </c>
       <c r="M97">
-        <v>141.23718495</v>
+        <v>142.72389216</v>
       </c>
       <c r="N97">
-        <v>-115.03718495</v>
+        <v>-116.52389216</v>
       </c>
       <c r="O97">
-        <v>-11.503718495</v>
+        <v>-11.652389216</v>
       </c>
       <c r="P97">
-        <v>-103.533466455</v>
+        <v>-104.871502944</v>
       </c>
       <c r="Q97">
-        <v>-102.933466455</v>
+        <v>-104.271502944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.66723663563558</v>
+        <v>2.072595794544476</v>
       </c>
       <c r="T97">
-        <v>25.08310907463859</v>
+        <v>31.35388634329825</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01855035556625911</v>
+        <v>0.01835712269577724</v>
       </c>
       <c r="W97">
-        <v>0.2314258261574761</v>
+        <v>0.2314713904683357</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1855035556625911</v>
+        <v>0.1835712269577724</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3051163666313812</v>
+        <v>0.3070163666313812</v>
       </c>
       <c r="C98">
-        <v>-395.9328556791215</v>
+        <v>-403.6681159580212</v>
       </c>
       <c r="D98">
-        <v>196.6423443208784</v>
+        <v>195.2120340419788</v>
       </c>
       <c r="E98">
-        <v>604.5801999999999</v>
+        <v>610.88515</v>
       </c>
       <c r="F98">
-        <v>605.2751999999999</v>
+        <v>611.58015</v>
       </c>
       <c r="G98">
         <v>12.7</v>
@@ -9448,37 +9448,37 @@
         <v>26.2</v>
       </c>
       <c r="M98">
-        <v>142.72389216</v>
+        <v>144.21059937</v>
       </c>
       <c r="N98">
-        <v>-116.52389216</v>
+        <v>-118.01059937</v>
       </c>
       <c r="O98">
-        <v>-11.652389216</v>
+        <v>-11.801059937</v>
       </c>
       <c r="P98">
-        <v>-104.871502944</v>
+        <v>-106.209539433</v>
       </c>
       <c r="Q98">
-        <v>-104.271502944</v>
+        <v>-105.609539433</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.07259579454447</v>
+        <v>2.74819439272596</v>
       </c>
       <c r="T98">
-        <v>31.35388634329817</v>
+        <v>41.80518179106422</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01835712269577724</v>
+        <v>0.01816787400819191</v>
       </c>
       <c r="W98">
-        <v>0.2314713904683357</v>
+        <v>0.2315160153088684</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1835712269577725</v>
+        <v>0.1816787400819191</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3070163666313812</v>
+        <v>0.3089163666313812</v>
       </c>
       <c r="C99">
-        <v>-403.6681159580212</v>
+        <v>-411.3827192966877</v>
       </c>
       <c r="D99">
-        <v>195.2120340419788</v>
+        <v>193.8023807033123</v>
       </c>
       <c r="E99">
-        <v>610.88515</v>
+        <v>617.1900999999999</v>
       </c>
       <c r="F99">
-        <v>611.58015</v>
+        <v>617.8851</v>
       </c>
       <c r="G99">
         <v>12.7</v>
@@ -9530,37 +9530,37 @@
         <v>26.2</v>
       </c>
       <c r="M99">
-        <v>144.21059937</v>
+        <v>145.69730658</v>
       </c>
       <c r="N99">
-        <v>-118.01059937</v>
+        <v>-119.49730658</v>
       </c>
       <c r="O99">
-        <v>-11.801059937</v>
+        <v>-11.949730658</v>
       </c>
       <c r="P99">
-        <v>-106.209539433</v>
+        <v>-107.547575922</v>
       </c>
       <c r="Q99">
-        <v>-105.609539433</v>
+        <v>-106.947575922</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.74819439272596</v>
+        <v>4.099391589088941</v>
       </c>
       <c r="T99">
-        <v>41.80518179106422</v>
+        <v>62.70777268659634</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01816787400819191</v>
+        <v>0.01798248753872057</v>
       </c>
       <c r="W99">
-        <v>0.2315160153088684</v>
+        <v>0.2315597294383697</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1816787400819191</v>
+        <v>0.1798248753872057</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3089163666313812</v>
+        <v>0.3108163666313812</v>
       </c>
       <c r="C100">
-        <v>-411.3827192966877</v>
+        <v>-419.0771099867735</v>
       </c>
       <c r="D100">
-        <v>193.8023807033123</v>
+        <v>192.4129400132266</v>
       </c>
       <c r="E100">
-        <v>617.1900999999999</v>
+        <v>623.49505</v>
       </c>
       <c r="F100">
-        <v>617.8851</v>
+        <v>624.19005</v>
       </c>
       <c r="G100">
         <v>12.7</v>
@@ -9612,37 +9612,37 @@
         <v>26.2</v>
       </c>
       <c r="M100">
-        <v>145.69730658</v>
+        <v>147.18401379</v>
       </c>
       <c r="N100">
-        <v>-119.49730658</v>
+        <v>-120.98401379</v>
       </c>
       <c r="O100">
-        <v>-11.949730658</v>
+        <v>-12.098401379</v>
       </c>
       <c r="P100">
-        <v>-107.547575922</v>
+        <v>-108.885612411</v>
       </c>
       <c r="Q100">
-        <v>-106.947575922</v>
+        <v>-108.285612411</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.099391589088941</v>
+        <v>8.152983178177882</v>
       </c>
       <c r="T100">
-        <v>62.70777268659634</v>
+        <v>125.4155453731927</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01798248753872057</v>
+        <v>0.01780084625045066</v>
       </c>
       <c r="W100">
-        <v>0.2315597294383697</v>
+        <v>0.2316025604541437</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1798248753872057</v>
+        <v>0.1780084625045066</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3108163666313812</v>
-      </c>
-      <c r="C101">
-        <v>-419.0771099867735</v>
-      </c>
-      <c r="D101">
-        <v>192.4129400132266</v>
-      </c>
-      <c r="E101">
-        <v>623.49505</v>
-      </c>
-      <c r="F101">
-        <v>624.19005</v>
-      </c>
-      <c r="G101">
-        <v>12.7</v>
-      </c>
-      <c r="H101">
-        <v>629.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>26.8</v>
-      </c>
-      <c r="K101">
-        <v>0.6000000000000014</v>
-      </c>
-      <c r="L101">
-        <v>26.2</v>
-      </c>
-      <c r="M101">
-        <v>147.18401379</v>
-      </c>
-      <c r="N101">
-        <v>-120.98401379</v>
-      </c>
-      <c r="O101">
-        <v>-12.098401379</v>
-      </c>
-      <c r="P101">
-        <v>-108.885612411</v>
-      </c>
-      <c r="Q101">
-        <v>-108.285612411</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.152983178177882</v>
-      </c>
-      <c r="T101">
-        <v>125.4155453731927</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01780084625045066</v>
-      </c>
-      <c r="W101">
-        <v>0.2316025604541437</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1780084625045066</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
